--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -911,7 +911,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.46"/>
@@ -1478,6 +1478,20 @@
       </c>
       <c r="D40" s="2" t="n">
         <v>11.909083</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.907796</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0.287892</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>14.208727</v>
       </c>
     </row>
   </sheetData>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="maas_kat_sayilari" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="maas_kat_sayilari" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="59">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -118,6 +118,9 @@
     <t xml:space="preserve">Din Hz.Uzm</t>
   </si>
   <si>
+    <t xml:space="preserve">Eğt.Uzmanı</t>
+  </si>
+  <si>
     <t xml:space="preserve">Memur</t>
   </si>
   <si>
@@ -187,9 +190,6 @@
     <t xml:space="preserve">ogrenim</t>
   </si>
   <si>
-    <t xml:space="preserve">Eğitim Uzmanı</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yüksek Okul</t>
   </si>
   <si>
@@ -211,7 +211,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -238,6 +238,13 @@
       <sz val="12"/>
       <name val="Times New Roman Tur"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -283,7 +290,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -328,6 +335,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -338,112 +349,6 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1510,7 +1415,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="35.58"/>
@@ -2066,100 +1971,127 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>1</v>
@@ -2170,7 +2102,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>1</v>
@@ -2181,7 +2113,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>1</v>
@@ -2192,7 +2124,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>1</v>
@@ -2200,13 +2132,10 @@
       <c r="C50" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="D50" s="1" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>1</v>
@@ -2217,7 +2146,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="1" t="n">
         <v>1</v>
@@ -2228,7 +2157,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>1</v>
@@ -2239,7 +2168,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="n">
         <v>1</v>
@@ -2250,7 +2179,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B55" s="1" t="n">
         <v>1</v>
@@ -2261,64 +2190,166 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B64" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C64" s="1" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2357,16 +2388,16 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2972,9 +3003,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
-        <v>54</v>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>1</v>
@@ -2986,9 +3017,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
-        <v>54</v>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>2</v>
@@ -3000,9 +3031,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
-        <v>54</v>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>3</v>
@@ -3014,9 +3045,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>54</v>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>4</v>
@@ -3028,9 +3059,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>54</v>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>5</v>
@@ -4838,7 +4869,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B158" s="1" t="n">
         <v>1</v>
@@ -4858,7 +4889,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B159" s="1" t="n">
         <v>2</v>
@@ -4878,7 +4909,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B160" s="1" t="n">
         <v>3</v>
@@ -4898,7 +4929,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B161" s="1" t="n">
         <v>4</v>
@@ -4918,7 +4949,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B162" s="1" t="n">
         <v>1</v>
@@ -4938,7 +4969,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B163" s="1" t="n">
         <v>2</v>
@@ -4958,7 +4989,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B164" s="1" t="n">
         <v>3</v>
@@ -4978,7 +5009,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B165" s="1" t="n">
         <v>4</v>
@@ -4998,7 +5029,7 @@
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B166" s="1" t="n">
         <v>5</v>
@@ -5018,7 +5049,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B167" s="1" t="n">
         <v>6</v>
@@ -5038,7 +5069,7 @@
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B168" s="1" t="n">
         <v>1</v>
@@ -5055,7 +5086,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B169" s="1" t="n">
         <v>2</v>
@@ -5072,7 +5103,7 @@
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B170" s="1" t="n">
         <v>3</v>
@@ -5089,7 +5120,7 @@
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B171" s="1" t="n">
         <v>4</v>
@@ -5106,7 +5137,7 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B172" s="1" t="n">
         <v>5</v>
@@ -5123,7 +5154,7 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B173" s="1" t="n">
         <v>6</v>
@@ -5140,7 +5171,7 @@
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B174" s="1" t="n">
         <v>7</v>
@@ -5157,7 +5188,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B175" s="1" t="n">
         <v>8</v>
@@ -5174,7 +5205,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B176" s="1" t="n">
         <v>9</v>
@@ -5191,7 +5222,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B177" s="1" t="n">
         <v>10</v>
@@ -5208,7 +5239,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B178" s="1" t="n">
         <v>11</v>
@@ -5225,7 +5256,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B179" s="1" t="n">
         <v>12</v>
@@ -5242,7 +5273,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B180" s="1" t="n">
         <v>13</v>
@@ -5259,7 +5290,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B181" s="1" t="n">
         <v>14</v>
@@ -5276,7 +5307,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B182" s="1" t="n">
         <v>15</v>
@@ -5293,7 +5324,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B183" s="1" t="n">
         <v>1</v>
@@ -5310,7 +5341,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B184" s="1" t="n">
         <v>2</v>
@@ -5327,7 +5358,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B185" s="1" t="n">
         <v>3</v>
@@ -5344,7 +5375,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B186" s="1" t="n">
         <v>4</v>
@@ -5361,7 +5392,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B187" s="1" t="n">
         <v>5</v>
@@ -5378,7 +5409,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B188" s="1" t="n">
         <v>6</v>
@@ -5395,7 +5426,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B189" s="1" t="n">
         <v>7</v>
@@ -5412,7 +5443,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B190" s="1" t="n">
         <v>8</v>
@@ -5429,7 +5460,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B191" s="1" t="n">
         <v>9</v>
@@ -5446,7 +5477,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B192" s="1" t="n">
         <v>10</v>
@@ -5463,7 +5494,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B193" s="1" t="n">
         <v>11</v>
@@ -5480,7 +5511,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B194" s="1" t="n">
         <v>12</v>
@@ -5497,7 +5528,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B195" s="1" t="n">
         <v>13</v>
@@ -5514,7 +5545,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B196" s="1" t="n">
         <v>14</v>
@@ -5531,7 +5562,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B197" s="1" t="n">
         <v>15</v>
@@ -5548,7 +5579,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B198" s="1" t="n">
         <v>1</v>
@@ -5565,7 +5596,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B199" s="1" t="n">
         <v>2</v>
@@ -5582,7 +5613,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B200" s="1" t="n">
         <v>3</v>
@@ -5599,7 +5630,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B201" s="1" t="n">
         <v>4</v>
@@ -5616,7 +5647,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B202" s="1" t="n">
         <v>5</v>
@@ -5633,7 +5664,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B203" s="1" t="n">
         <v>6</v>
@@ -5650,7 +5681,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B204" s="1" t="n">
         <v>7</v>
@@ -5667,7 +5698,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B205" s="1" t="n">
         <v>8</v>
@@ -5684,7 +5715,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B206" s="1" t="n">
         <v>9</v>
@@ -5701,7 +5732,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B207" s="1" t="n">
         <v>10</v>
@@ -5718,7 +5749,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B208" s="1" t="n">
         <v>11</v>
@@ -5735,7 +5766,7 @@
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B209" s="1" t="n">
         <v>12</v>
@@ -5752,7 +5783,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B210" s="1" t="n">
         <v>13</v>
@@ -5769,7 +5800,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B211" s="1" t="n">
         <v>14</v>
@@ -5786,7 +5817,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B212" s="1" t="n">
         <v>15</v>
@@ -5803,7 +5834,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B213" s="1" t="n">
         <v>1</v>
@@ -5823,7 +5854,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B214" s="1" t="n">
         <v>2</v>
@@ -5843,7 +5874,7 @@
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B215" s="1" t="n">
         <v>3</v>
@@ -5863,7 +5894,7 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B216" s="1" t="n">
         <v>4</v>
@@ -5883,7 +5914,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B217" s="1" t="n">
         <v>1</v>
@@ -5900,7 +5931,7 @@
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B218" s="1" t="n">
         <v>2</v>
@@ -5917,7 +5948,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B219" s="1" t="n">
         <v>3</v>
@@ -5934,7 +5965,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B220" s="1" t="n">
         <v>4</v>
@@ -5951,7 +5982,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B221" s="1" t="n">
         <v>5</v>
@@ -5968,7 +5999,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B222" s="1" t="n">
         <v>6</v>
@@ -5985,7 +6016,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B223" s="1" t="n">
         <v>7</v>
@@ -6002,7 +6033,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B224" s="1" t="n">
         <v>8</v>
@@ -6019,7 +6050,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B225" s="1" t="n">
         <v>9</v>
@@ -6036,7 +6067,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B226" s="1" t="n">
         <v>10</v>
@@ -6053,7 +6084,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B227" s="1" t="n">
         <v>11</v>
@@ -6070,7 +6101,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B228" s="1" t="n">
         <v>12</v>
@@ -6087,7 +6118,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B229" s="1" t="n">
         <v>13</v>
@@ -6104,7 +6135,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B230" s="1" t="n">
         <v>14</v>
@@ -6121,7 +6152,7 @@
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B231" s="1" t="n">
         <v>15</v>
@@ -6138,7 +6169,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B232" s="1" t="n">
         <v>1</v>
@@ -6155,7 +6186,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B233" s="1" t="n">
         <v>2</v>
@@ -6172,7 +6203,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B234" s="1" t="n">
         <v>3</v>
@@ -6189,7 +6220,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B235" s="1" t="n">
         <v>4</v>
@@ -6206,7 +6237,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B236" s="1" t="n">
         <v>5</v>
@@ -6223,7 +6254,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B237" s="1" t="n">
         <v>6</v>
@@ -6240,7 +6271,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B238" s="1" t="n">
         <v>7</v>
@@ -6257,7 +6288,7 @@
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B239" s="1" t="n">
         <v>8</v>
@@ -6274,7 +6305,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B240" s="1" t="n">
         <v>9</v>
@@ -6291,7 +6322,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B241" s="1" t="n">
         <v>10</v>
@@ -6308,7 +6339,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B242" s="1" t="n">
         <v>11</v>
@@ -6325,7 +6356,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B243" s="1" t="n">
         <v>12</v>
@@ -6342,7 +6373,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B244" s="1" t="n">
         <v>13</v>
@@ -6359,7 +6390,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>14</v>
@@ -6376,7 +6407,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B246" s="1" t="n">
         <v>15</v>
@@ -6393,7 +6424,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B247" s="1" t="n">
         <v>1</v>
@@ -6410,7 +6441,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B248" s="1" t="n">
         <v>2</v>
@@ -6427,7 +6458,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B249" s="1" t="n">
         <v>3</v>
@@ -6444,7 +6475,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B250" s="1" t="n">
         <v>4</v>
@@ -6461,7 +6492,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B251" s="1" t="n">
         <v>5</v>
@@ -6478,7 +6509,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B252" s="1" t="n">
         <v>6</v>
@@ -6495,7 +6526,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B253" s="1" t="n">
         <v>7</v>
@@ -6512,7 +6543,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B254" s="1" t="n">
         <v>8</v>
@@ -6529,7 +6560,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B255" s="1" t="n">
         <v>9</v>
@@ -6546,7 +6577,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B256" s="1" t="n">
         <v>10</v>
@@ -6563,7 +6594,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B257" s="1" t="n">
         <v>11</v>
@@ -6580,7 +6611,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B258" s="1" t="n">
         <v>12</v>
@@ -6597,7 +6628,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B259" s="1" t="n">
         <v>13</v>
@@ -6614,7 +6645,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B260" s="1" t="n">
         <v>14</v>
@@ -6631,7 +6662,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B261" s="1" t="n">
         <v>15</v>
@@ -6648,7 +6679,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B262" s="1" t="n">
         <v>1</v>
@@ -6668,7 +6699,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B263" s="1" t="n">
         <v>2</v>
@@ -6688,7 +6719,7 @@
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B264" s="1" t="n">
         <v>3</v>
@@ -6708,7 +6739,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B265" s="1" t="n">
         <v>4</v>
@@ -6728,7 +6759,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B266" s="1" t="n">
         <v>1</v>
@@ -6748,7 +6779,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B267" s="1" t="n">
         <v>2</v>
@@ -6768,7 +6799,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>3</v>
@@ -6788,7 +6819,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B269" s="1" t="n">
         <v>4</v>
@@ -6808,7 +6839,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B270" s="1" t="n">
         <v>5</v>
@@ -6828,7 +6859,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B271" s="1" t="n">
         <v>6</v>
@@ -6848,7 +6879,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B272" s="1" t="n">
         <v>7</v>
@@ -6868,7 +6899,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B273" s="1" t="n">
         <v>8</v>
@@ -6888,7 +6919,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B274" s="1" t="n">
         <v>1</v>
@@ -6905,7 +6936,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B275" s="1" t="n">
         <v>2</v>
@@ -6922,7 +6953,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B276" s="1" t="n">
         <v>3</v>
@@ -6939,7 +6970,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B277" s="1" t="n">
         <v>4</v>
@@ -6956,7 +6987,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B278" s="1" t="n">
         <v>5</v>
@@ -6973,7 +7004,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B279" s="1" t="n">
         <v>6</v>
@@ -6990,7 +7021,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B280" s="1" t="n">
         <v>7</v>
@@ -7007,7 +7038,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B281" s="1" t="n">
         <v>8</v>
@@ -7024,7 +7055,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B282" s="1" t="n">
         <v>9</v>
@@ -7041,7 +7072,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B283" s="1" t="n">
         <v>10</v>
@@ -7058,7 +7089,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B284" s="1" t="n">
         <v>11</v>
@@ -7075,7 +7106,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B285" s="1" t="n">
         <v>12</v>
@@ -7092,7 +7123,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B286" s="1" t="n">
         <v>13</v>
@@ -7109,7 +7140,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B287" s="1" t="n">
         <v>14</v>
@@ -7126,7 +7157,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B288" s="1" t="n">
         <v>15</v>
@@ -7143,7 +7174,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B289" s="1" t="n">
         <v>1</v>
@@ -7160,7 +7191,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>2</v>
@@ -7177,7 +7208,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B291" s="1" t="n">
         <v>3</v>
@@ -7194,7 +7225,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B292" s="1" t="n">
         <v>4</v>
@@ -7211,7 +7242,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B293" s="1" t="n">
         <v>5</v>
@@ -7228,7 +7259,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B294" s="1" t="n">
         <v>6</v>
@@ -7245,7 +7276,7 @@
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B295" s="1" t="n">
         <v>7</v>
@@ -7262,7 +7293,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B296" s="1" t="n">
         <v>8</v>
@@ -7279,7 +7310,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B297" s="1" t="n">
         <v>9</v>
@@ -7296,7 +7327,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B298" s="1" t="n">
         <v>10</v>
@@ -7313,7 +7344,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B299" s="1" t="n">
         <v>11</v>
@@ -7330,7 +7361,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B300" s="1" t="n">
         <v>12</v>
@@ -7347,7 +7378,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B301" s="1" t="n">
         <v>13</v>
@@ -7364,7 +7395,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B302" s="1" t="n">
         <v>14</v>
@@ -7381,7 +7412,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B303" s="1" t="n">
         <v>15</v>
@@ -7398,7 +7429,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B304" s="1" t="n">
         <v>1</v>
@@ -7415,7 +7446,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B305" s="1" t="n">
         <v>2</v>
@@ -7432,7 +7463,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B306" s="1" t="n">
         <v>3</v>
@@ -7449,7 +7480,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B307" s="1" t="n">
         <v>4</v>
@@ -7466,7 +7497,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B308" s="1" t="n">
         <v>5</v>
@@ -7483,7 +7514,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B309" s="1" t="n">
         <v>6</v>
@@ -7500,7 +7531,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B310" s="1" t="n">
         <v>7</v>
@@ -7517,7 +7548,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B311" s="1" t="n">
         <v>8</v>
@@ -7534,7 +7565,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>9</v>
@@ -7551,7 +7582,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B313" s="1" t="n">
         <v>10</v>
@@ -7568,7 +7599,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B314" s="1" t="n">
         <v>11</v>
@@ -7585,7 +7616,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B315" s="1" t="n">
         <v>12</v>
@@ -7602,7 +7633,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B316" s="1" t="n">
         <v>13</v>
@@ -7619,7 +7650,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B317" s="1" t="n">
         <v>14</v>
@@ -7636,7 +7667,7 @@
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B318" s="1" t="n">
         <v>15</v>
@@ -7653,7 +7684,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B319" s="1" t="n">
         <v>1</v>
@@ -7667,7 +7698,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B320" s="1" t="n">
         <v>2</v>
@@ -7681,7 +7712,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B321" s="1" t="n">
         <v>3</v>
@@ -7695,7 +7726,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B322" s="1" t="n">
         <v>4</v>
@@ -7709,7 +7740,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B323" s="1" t="n">
         <v>5</v>
@@ -7723,7 +7754,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B324" s="1" t="n">
         <v>6</v>
@@ -7737,7 +7768,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B325" s="1" t="n">
         <v>7</v>
@@ -7751,7 +7782,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B326" s="1" t="n">
         <v>8</v>
@@ -7765,7 +7796,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B327" s="1" t="n">
         <v>9</v>
@@ -7779,7 +7810,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B328" s="1" t="n">
         <v>10</v>
@@ -7793,7 +7824,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B329" s="1" t="n">
         <v>11</v>
@@ -7807,7 +7838,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B330" s="1" t="n">
         <v>12</v>
@@ -7821,7 +7852,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B331" s="1" t="n">
         <v>1</v>
@@ -7835,7 +7866,7 @@
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B332" s="1" t="n">
         <v>2</v>
@@ -7849,7 +7880,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B333" s="1" t="n">
         <v>3</v>
@@ -7863,7 +7894,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B334" s="1" t="n">
         <v>4</v>
@@ -7877,7 +7908,7 @@
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B335" s="1" t="n">
         <v>5</v>
@@ -7891,7 +7922,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B336" s="1" t="n">
         <v>6</v>
@@ -7905,7 +7936,7 @@
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B337" s="1" t="n">
         <v>7</v>
@@ -7919,7 +7950,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B338" s="1" t="n">
         <v>8</v>
@@ -7933,7 +7964,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B339" s="1" t="n">
         <v>9</v>
@@ -7947,7 +7978,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B340" s="1" t="n">
         <v>10</v>
@@ -7961,7 +7992,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B341" s="1" t="n">
         <v>11</v>
@@ -7975,7 +8006,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B342" s="1" t="n">
         <v>12</v>
@@ -7989,7 +8020,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B343" s="1" t="n">
         <v>13</v>
@@ -8003,7 +8034,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B344" s="1" t="n">
         <v>14</v>
@@ -8017,7 +8048,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B345" s="1" t="n">
         <v>15</v>
@@ -8143,7 +8174,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B354" s="1" t="n">
         <v>1</v>
@@ -8157,7 +8188,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B355" s="1" t="n">
         <v>2</v>
@@ -8171,7 +8202,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>3</v>
@@ -8185,7 +8216,7 @@
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B357" s="1" t="n">
         <v>4</v>
@@ -8199,7 +8230,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B358" s="1" t="n">
         <v>5</v>
@@ -8213,7 +8244,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B359" s="1" t="n">
         <v>6</v>
@@ -8227,7 +8258,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B360" s="1" t="n">
         <v>7</v>
@@ -8241,7 +8272,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B361" s="1" t="n">
         <v>8</v>
@@ -8255,7 +8286,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B362" s="1" t="n">
         <v>1</v>
@@ -8269,7 +8300,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B363" s="1" t="n">
         <v>2</v>
@@ -8283,7 +8314,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B364" s="1" t="n">
         <v>3</v>
@@ -8297,7 +8328,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B365" s="1" t="n">
         <v>4</v>
@@ -8311,7 +8342,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B366" s="1" t="n">
         <v>5</v>
@@ -8325,7 +8356,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B367" s="1" t="n">
         <v>6</v>
@@ -8339,7 +8370,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B368" s="1" t="n">
         <v>7</v>
@@ -8353,7 +8384,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B369" s="1" t="n">
         <v>8</v>
@@ -8367,7 +8398,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B370" s="1" t="n">
         <v>9</v>
@@ -8381,7 +8412,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B371" s="1" t="n">
         <v>10</v>
@@ -8395,7 +8426,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B372" s="1" t="n">
         <v>11</v>
@@ -8409,7 +8440,7 @@
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B373" s="1" t="n">
         <v>12</v>
@@ -8423,7 +8454,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B374" s="1" t="n">
         <v>13</v>
@@ -8437,7 +8468,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B375" s="1" t="n">
         <v>14</v>
@@ -8451,7 +8482,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B376" s="1" t="n">
         <v>1</v>
@@ -8465,7 +8496,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B377" s="1" t="n">
         <v>2</v>
@@ -8479,7 +8510,7 @@
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B378" s="1" t="n">
         <v>3</v>
@@ -8493,7 +8524,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B379" s="1" t="n">
         <v>4</v>
@@ -8507,7 +8538,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B380" s="1" t="n">
         <v>5</v>
@@ -8521,7 +8552,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B381" s="1" t="n">
         <v>6</v>
@@ -8535,7 +8566,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B382" s="1" t="n">
         <v>7</v>
@@ -8549,7 +8580,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B383" s="1" t="n">
         <v>8</v>
@@ -8563,7 +8594,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B384" s="1" t="n">
         <v>9</v>
@@ -8577,7 +8608,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B385" s="1" t="n">
         <v>10</v>
@@ -8591,7 +8622,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B386" s="1" t="n">
         <v>11</v>
@@ -8605,7 +8636,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B387" s="1" t="n">
         <v>12</v>
@@ -8619,7 +8650,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B388" s="1" t="n">
         <v>13</v>
@@ -8633,7 +8664,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B389" s="1" t="n">
         <v>14</v>
@@ -8647,7 +8678,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B390" s="1" t="n">
         <v>15</v>
@@ -8661,7 +8692,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B391" s="1" t="n">
         <v>1</v>
@@ -8675,7 +8706,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B392" s="1" t="n">
         <v>2</v>
@@ -8689,7 +8720,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B393" s="1" t="n">
         <v>3</v>
@@ -8703,7 +8734,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B394" s="1" t="n">
         <v>4</v>
@@ -8717,7 +8748,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B395" s="1" t="n">
         <v>5</v>
@@ -8731,7 +8762,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B396" s="1" t="n">
         <v>6</v>
@@ -8745,7 +8776,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B397" s="1" t="n">
         <v>7</v>
@@ -8759,7 +8790,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B398" s="1" t="n">
         <v>8</v>
@@ -8773,7 +8804,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B399" s="1" t="n">
         <v>1</v>
@@ -8787,7 +8818,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B400" s="1" t="n">
         <v>2</v>
@@ -8801,7 +8832,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B401" s="1" t="n">
         <v>3</v>
@@ -8815,7 +8846,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B402" s="1" t="n">
         <v>4</v>
@@ -8829,7 +8860,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B403" s="1" t="n">
         <v>5</v>
@@ -8843,7 +8874,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B404" s="1" t="n">
         <v>6</v>
@@ -8857,7 +8888,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B405" s="1" t="n">
         <v>7</v>
@@ -8871,7 +8902,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B406" s="1" t="n">
         <v>8</v>
@@ -8885,7 +8916,7 @@
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B407" s="1" t="n">
         <v>1</v>
@@ -8899,7 +8930,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B408" s="1" t="n">
         <v>2</v>
@@ -8913,7 +8944,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B409" s="1" t="n">
         <v>3</v>
@@ -8927,7 +8958,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B410" s="1" t="n">
         <v>4</v>
@@ -8941,7 +8972,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B411" s="1" t="n">
         <v>5</v>
@@ -8955,7 +8986,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B412" s="1" t="n">
         <v>6</v>
@@ -8969,7 +9000,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B413" s="1" t="n">
         <v>7</v>
@@ -8983,7 +9014,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B414" s="1" t="n">
         <v>8</v>
@@ -8997,7 +9028,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B415" s="1" t="n">
         <v>1</v>
@@ -9011,7 +9042,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B416" s="1" t="n">
         <v>2</v>
@@ -9025,7 +9056,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B417" s="1" t="n">
         <v>3</v>
@@ -9039,7 +9070,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B418" s="1" t="n">
         <v>4</v>
@@ -9053,7 +9084,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B419" s="1" t="n">
         <v>5</v>
@@ -9067,7 +9098,7 @@
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B420" s="1" t="n">
         <v>6</v>
@@ -9081,7 +9112,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B421" s="1" t="n">
         <v>7</v>
@@ -9095,7 +9126,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B422" s="1" t="n">
         <v>8</v>
@@ -9109,7 +9140,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B423" s="1" t="n">
         <v>9</v>
@@ -9123,7 +9154,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B424" s="1" t="n">
         <v>10</v>
@@ -9137,7 +9168,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B425" s="1" t="n">
         <v>11</v>
@@ -9151,7 +9182,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B426" s="1" t="n">
         <v>12</v>
@@ -9165,7 +9196,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B427" s="1" t="n">
         <v>13</v>
@@ -9179,7 +9210,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B428" s="1" t="n">
         <v>14</v>
@@ -9193,7 +9224,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B429" s="1" t="n">
         <v>15</v>
@@ -9207,7 +9238,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B430" s="1" t="n">
         <v>1</v>
@@ -9221,7 +9252,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B431" s="1" t="n">
         <v>2</v>
@@ -9235,7 +9266,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B432" s="1" t="n">
         <v>3</v>
@@ -9249,7 +9280,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B433" s="1" t="n">
         <v>4</v>
@@ -9263,7 +9294,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B434" s="1" t="n">
         <v>5</v>
@@ -9277,7 +9308,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B435" s="1" t="n">
         <v>6</v>
@@ -9291,7 +9322,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B436" s="1" t="n">
         <v>7</v>
@@ -9305,7 +9336,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B437" s="1" t="n">
         <v>8</v>
@@ -9319,7 +9350,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B438" s="1" t="n">
         <v>9</v>
@@ -9333,7 +9364,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B439" s="1" t="n">
         <v>10</v>
@@ -9347,7 +9378,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B440" s="1" t="n">
         <v>11</v>
@@ -9361,7 +9392,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B441" s="1" t="n">
         <v>12</v>
@@ -9375,7 +9406,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B442" s="1" t="n">
         <v>13</v>
@@ -9389,7 +9420,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B443" s="1" t="n">
         <v>14</v>
@@ -9403,7 +9434,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B444" s="1" t="n">
         <v>15</v>
@@ -9417,7 +9448,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B445" s="1" t="n">
         <v>1</v>
@@ -9431,7 +9462,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B446" s="1" t="n">
         <v>2</v>
@@ -9445,7 +9476,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B447" s="1" t="n">
         <v>3</v>
@@ -9459,7 +9490,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B448" s="1" t="n">
         <v>4</v>
@@ -9473,7 +9504,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B449" s="1" t="n">
         <v>5</v>
@@ -9487,7 +9518,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B450" s="1" t="n">
         <v>6</v>
@@ -9501,7 +9532,7 @@
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B451" s="1" t="n">
         <v>7</v>
@@ -9515,7 +9546,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B452" s="1" t="n">
         <v>8</v>
@@ -9529,7 +9560,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B453" s="1" t="n">
         <v>9</v>
@@ -9543,7 +9574,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B454" s="1" t="n">
         <v>10</v>
@@ -9557,7 +9588,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B455" s="1" t="n">
         <v>11</v>
@@ -9571,7 +9602,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B456" s="1" t="n">
         <v>12</v>
@@ -9585,7 +9616,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B457" s="1" t="n">
         <v>13</v>
@@ -9599,7 +9630,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B458" s="1" t="n">
         <v>14</v>
@@ -9613,7 +9644,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B459" s="1" t="n">
         <v>15</v>
@@ -9627,7 +9658,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B460" s="1" t="n">
         <v>1</v>
@@ -9641,7 +9672,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B461" s="1" t="n">
         <v>2</v>
@@ -9655,7 +9686,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B462" s="1" t="n">
         <v>3</v>
@@ -9669,7 +9700,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B463" s="1" t="n">
         <v>4</v>
@@ -9683,7 +9714,7 @@
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B464" s="1" t="n">
         <v>5</v>
@@ -9697,7 +9728,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B465" s="1" t="n">
         <v>6</v>
@@ -9711,7 +9742,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B466" s="1" t="n">
         <v>7</v>
@@ -9725,7 +9756,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B467" s="1" t="n">
         <v>8</v>
@@ -9739,7 +9770,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B468" s="1" t="n">
         <v>9</v>
@@ -9753,7 +9784,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B469" s="1" t="n">
         <v>10</v>
@@ -9767,7 +9798,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B470" s="1" t="n">
         <v>11</v>
@@ -9781,7 +9812,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B471" s="1" t="n">
         <v>12</v>
@@ -9795,7 +9826,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B472" s="1" t="n">
         <v>13</v>
@@ -9809,7 +9840,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B473" s="1" t="n">
         <v>14</v>
@@ -9823,7 +9854,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B474" s="1" t="n">
         <v>15</v>
@@ -9837,7 +9868,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B475" s="1" t="n">
         <v>1</v>
@@ -9851,7 +9882,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B476" s="1" t="n">
         <v>2</v>
@@ -9865,7 +9896,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B477" s="1" t="n">
         <v>3</v>
@@ -9879,7 +9910,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B478" s="1" t="n">
         <v>4</v>
@@ -9893,7 +9924,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B479" s="1" t="n">
         <v>5</v>
@@ -9907,7 +9938,7 @@
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B480" s="1" t="n">
         <v>6</v>
@@ -9921,7 +9952,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B481" s="1" t="n">
         <v>7</v>
@@ -9935,7 +9966,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B482" s="1" t="n">
         <v>8</v>
@@ -9949,7 +9980,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B483" s="1" t="n">
         <v>9</v>
@@ -9963,7 +9994,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B484" s="1" t="n">
         <v>10</v>
@@ -9977,7 +10008,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B485" s="1" t="n">
         <v>11</v>
@@ -9991,7 +10022,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B486" s="1" t="n">
         <v>12</v>
@@ -10005,7 +10036,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B487" s="1" t="n">
         <v>13</v>
@@ -10019,7 +10050,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B488" s="1" t="n">
         <v>14</v>
@@ -10033,7 +10064,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B489" s="1" t="n">
         <v>15</v>
@@ -10047,7 +10078,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B490" s="1" t="n">
         <v>1</v>
@@ -10061,7 +10092,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B491" s="1" t="n">
         <v>2</v>
@@ -10075,7 +10106,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B492" s="1" t="n">
         <v>3</v>
@@ -10089,7 +10120,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B493" s="1" t="n">
         <v>4</v>
@@ -10103,7 +10134,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B494" s="1" t="n">
         <v>5</v>
@@ -10117,7 +10148,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B495" s="1" t="n">
         <v>6</v>
@@ -10131,7 +10162,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B496" s="1" t="n">
         <v>7</v>
@@ -10145,7 +10176,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B497" s="1" t="n">
         <v>8</v>
@@ -10159,7 +10190,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B498" s="1" t="n">
         <v>9</v>
@@ -10173,7 +10204,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B499" s="1" t="n">
         <v>10</v>
@@ -10187,7 +10218,7 @@
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B500" s="1" t="n">
         <v>11</v>
@@ -10201,7 +10232,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B501" s="1" t="n">
         <v>12</v>
@@ -10215,7 +10246,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B502" s="1" t="n">
         <v>13</v>
@@ -10229,7 +10260,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B503" s="1" t="n">
         <v>14</v>
@@ -10243,7 +10274,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B504" s="1" t="n">
         <v>15</v>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="maas_kat_sayilari" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="maas_kat_sayilari" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -351,6 +351,112 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -816,7 +922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.46"/>
@@ -1397,6 +1503,20 @@
       </c>
       <c r="D41" s="2" t="n">
         <v>14.208727</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1.012556</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0.321115</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>15.848415</v>
       </c>
     </row>
   </sheetData>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -206,10 +206,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="&quot;DOĞRU&quot;;&quot;DOĞRU&quot;;&quot;YANLIŞ&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -290,7 +291,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -337,6 +338,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2487,7 +2492,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H504"/>
+  <dimension ref="A1:M504"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="14.74"/>
@@ -9159,6 +9164,7 @@
       <c r="F415" s="7" t="s">
         <v>55</v>
       </c>
+      <c r="M415" s="12"/>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="7" t="s">

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -12,6 +12,7 @@
     <sheet name="maas_kat_sayilari" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="kadro_unvan_sira_no" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="80">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -172,10 +173,7 @@
     <t xml:space="preserve">Kaloriferc</t>
   </si>
   <si>
-    <t xml:space="preserve">Vekil M.K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vekil İ-H</t>
+    <t xml:space="preserve">Vekil</t>
   </si>
   <si>
     <t xml:space="preserve">oht_orani</t>
@@ -200,6 +198,72 @@
   </si>
   <si>
     <t xml:space="preserve">Mutemet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unvan_sira_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kadro_unvan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unvan_sinifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personel_tipi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İlçe Müftüsü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genel İdare Hizmetleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Şube Müdürü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Din Hizmetleri Uzmanı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Din Hizmetleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuran Kursu Öğreticisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzman İmam Hatip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İmam-Hatip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müezzin-Kayyım</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veri Haz.ve Kont.İşl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yardımcı Hizmetler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B M.K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4B Sözleşmeli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B K.K.Ö.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B Destek Personeli - Temizlik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memur (Ş) (5-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B Koruma ve Güvenlik Görevlisi</t>
   </si>
 </sst>
 </file>
@@ -317,10 +381,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,6 +401,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1540,7 +1604,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="35.58"/>
@@ -2416,15 +2480,8 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>500</v>
-      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="2"/>
@@ -2442,9 +2499,11 @@
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="2"/>
@@ -2469,12 +2528,6 @@
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2492,41 +2545,41 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M504"/>
+  <dimension ref="A1:M459"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="18.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="18.46"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1021" min="7" style="1" width="11.52"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1022" style="8" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1022" style="7" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1" t="n">
@@ -2537,7 +2590,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -2549,11 +2602,11 @@
       <c r="D3" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -2565,11 +2618,11 @@
       <c r="D4" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -2583,7 +2636,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1" t="n">
@@ -2597,7 +2650,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1" t="n">
@@ -2611,7 +2664,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -2625,7 +2678,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -2639,7 +2692,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1" t="n">
@@ -2653,7 +2706,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="n">
@@ -2667,7 +2720,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
@@ -2681,7 +2734,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="n">
@@ -2695,7 +2748,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="n">
@@ -2709,7 +2762,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -2723,7 +2776,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -2737,7 +2790,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="n">
@@ -2751,7 +2804,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="n">
@@ -2765,7 +2818,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="1" t="n">
@@ -2779,7 +2832,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="1" t="n">
@@ -2793,7 +2846,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="1" t="n">
@@ -2807,7 +2860,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="1" t="n">
@@ -2821,7 +2874,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="1" t="n">
@@ -2835,7 +2888,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="1" t="n">
@@ -2849,7 +2902,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="1" t="n">
@@ -2863,7 +2916,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -2877,7 +2930,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -2891,7 +2944,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="1" t="n">
@@ -2905,7 +2958,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B29" s="1" t="n">
@@ -2919,7 +2972,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B30" s="1" t="n">
@@ -2933,7 +2986,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="n">
@@ -2947,7 +3000,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B32" s="1" t="n">
@@ -2961,7 +3014,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="1" t="n">
@@ -2975,7 +3028,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="1" t="n">
@@ -2989,7 +3042,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B35" s="1" t="n">
@@ -3003,7 +3056,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="1" t="n">
@@ -3017,7 +3070,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B37" s="1" t="n">
@@ -3031,7 +3084,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B38" s="1" t="n">
@@ -3045,7 +3098,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="1" t="n">
@@ -3059,7 +3112,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="1" t="n">
@@ -3073,7 +3126,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="1" t="n">
@@ -3087,7 +3140,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="1" t="n">
@@ -3101,7 +3154,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="1" t="n">
@@ -3115,7 +3168,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="1" t="n">
@@ -3129,7 +3182,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="1" t="n">
@@ -3143,7 +3196,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B46" s="1" t="n">
@@ -3157,7 +3210,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="1" t="n">
@@ -3171,7 +3224,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B48" s="1" t="n">
@@ -3185,7 +3238,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B49" s="1" t="n">
@@ -3199,7 +3252,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B50" s="1" t="n">
@@ -3213,7 +3266,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B51" s="1" t="n">
@@ -3227,7 +3280,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B52" s="1" t="n">
@@ -3241,7 +3294,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B53" s="1" t="n">
@@ -3255,7 +3308,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B54" s="1" t="n">
@@ -3269,7 +3322,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B55" s="1" t="n">
@@ -3283,7 +3336,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B56" s="1" t="n">
@@ -3297,7 +3350,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B57" s="1" t="n">
@@ -3311,7 +3364,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B58" s="1" t="n">
@@ -3325,7 +3378,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B59" s="1" t="n">
@@ -3339,7 +3392,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B60" s="1" t="n">
@@ -3353,7 +3406,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B61" s="1" t="n">
@@ -3367,7 +3420,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B62" s="1" t="n">
@@ -3381,7 +3434,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B63" s="1" t="n">
@@ -3395,7 +3448,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B64" s="1" t="n">
@@ -3409,7 +3462,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="1" t="n">
@@ -3423,7 +3476,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="1" t="n">
@@ -3437,7 +3490,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="1" t="n">
@@ -3451,7 +3504,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="1" t="n">
@@ -3465,7 +3518,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B69" s="1" t="n">
@@ -3479,7 +3532,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="1" t="n">
@@ -3493,7 +3546,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B71" s="1" t="n">
@@ -3507,7 +3560,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="1" t="n">
@@ -3521,7 +3574,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B73" s="1" t="n">
@@ -3535,7 +3588,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B74" s="1" t="n">
@@ -3550,12 +3603,12 @@
       <c r="E74" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>55</v>
+      <c r="F74" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B75" s="1" t="n">
@@ -3570,12 +3623,12 @@
       <c r="E75" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>55</v>
+      <c r="F75" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B76" s="1" t="n">
@@ -3590,12 +3643,12 @@
       <c r="E76" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F76" s="7" t="s">
-        <v>55</v>
+      <c r="F76" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B77" s="1" t="n">
@@ -3610,12 +3663,12 @@
       <c r="E77" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>55</v>
+      <c r="F77" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B78" s="1" t="n">
@@ -3630,12 +3683,12 @@
       <c r="E78" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>55</v>
+      <c r="F78" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B79" s="1" t="n">
@@ -3650,12 +3703,12 @@
       <c r="E79" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>55</v>
+      <c r="F79" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B80" s="1" t="n">
@@ -3670,12 +3723,12 @@
       <c r="E80" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>55</v>
+      <c r="F80" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B81" s="1" t="n">
@@ -3690,12 +3743,12 @@
       <c r="E81" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>55</v>
+      <c r="F81" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B82" s="1" t="n">
@@ -3710,12 +3763,12 @@
       <c r="E82" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>55</v>
+      <c r="F82" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B83" s="1" t="n">
@@ -3730,12 +3783,12 @@
       <c r="E83" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>55</v>
+      <c r="F83" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B84" s="1" t="n">
@@ -3747,12 +3800,12 @@
       <c r="D84" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>55</v>
+      <c r="F84" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B85" s="1" t="n">
@@ -3764,12 +3817,12 @@
       <c r="D85" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>55</v>
+      <c r="F85" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B86" s="1" t="n">
@@ -3781,12 +3834,12 @@
       <c r="D86" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>55</v>
+      <c r="F86" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B87" s="1" t="n">
@@ -3798,12 +3851,12 @@
       <c r="D87" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F87" s="7" t="s">
-        <v>55</v>
+      <c r="F87" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B88" s="1" t="n">
@@ -3815,12 +3868,12 @@
       <c r="D88" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>55</v>
+      <c r="F88" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B89" s="1" t="n">
@@ -3832,12 +3885,12 @@
       <c r="D89" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>55</v>
+      <c r="F89" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B90" s="1" t="n">
@@ -3849,12 +3902,12 @@
       <c r="D90" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>55</v>
+      <c r="F90" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B91" s="1" t="n">
@@ -3866,12 +3919,12 @@
       <c r="D91" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F91" s="7" t="s">
-        <v>55</v>
+      <c r="F91" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B92" s="1" t="n">
@@ -3883,12 +3936,12 @@
       <c r="D92" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>55</v>
+      <c r="F92" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B93" s="1" t="n">
@@ -3900,12 +3953,12 @@
       <c r="D93" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>55</v>
+      <c r="F93" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B94" s="1" t="n">
@@ -3917,12 +3970,12 @@
       <c r="D94" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>55</v>
+      <c r="F94" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B95" s="1" t="n">
@@ -3934,12 +3987,12 @@
       <c r="D95" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F95" s="7" t="s">
-        <v>55</v>
+      <c r="F95" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B96" s="1" t="n">
@@ -3951,12 +4004,12 @@
       <c r="D96" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>55</v>
+      <c r="F96" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B97" s="1" t="n">
@@ -3968,12 +4021,12 @@
       <c r="D97" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>55</v>
+      <c r="F97" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B98" s="1" t="n">
@@ -3985,12 +4038,12 @@
       <c r="D98" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>55</v>
+      <c r="F98" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B99" s="1" t="n">
@@ -4002,12 +4055,12 @@
       <c r="D99" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F99" s="7" t="s">
-        <v>55</v>
+      <c r="F99" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B100" s="1" t="n">
@@ -4019,12 +4072,12 @@
       <c r="D100" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>55</v>
+      <c r="F100" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B101" s="1" t="n">
@@ -4036,12 +4089,12 @@
       <c r="D101" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>55</v>
+      <c r="F101" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B102" s="1" t="n">
@@ -4053,12 +4106,12 @@
       <c r="D102" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F102" s="7" t="s">
-        <v>55</v>
+      <c r="F102" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B103" s="1" t="n">
@@ -4070,12 +4123,12 @@
       <c r="D103" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>55</v>
+      <c r="F103" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B104" s="1" t="n">
@@ -4087,12 +4140,12 @@
       <c r="D104" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>55</v>
+      <c r="F104" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B105" s="1" t="n">
@@ -4104,12 +4157,12 @@
       <c r="D105" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>55</v>
+      <c r="F105" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B106" s="1" t="n">
@@ -4121,12 +4174,12 @@
       <c r="D106" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>55</v>
+      <c r="F106" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B107" s="1" t="n">
@@ -4138,12 +4191,12 @@
       <c r="D107" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F107" s="7" t="s">
-        <v>55</v>
+      <c r="F107" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B108" s="1" t="n">
@@ -4155,12 +4208,12 @@
       <c r="D108" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F108" s="7" t="s">
-        <v>56</v>
+      <c r="F108" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B109" s="1" t="n">
@@ -4172,12 +4225,12 @@
       <c r="D109" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>56</v>
+      <c r="F109" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B110" s="1" t="n">
@@ -4189,12 +4242,12 @@
       <c r="D110" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>56</v>
+      <c r="F110" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B111" s="1" t="n">
@@ -4206,12 +4259,12 @@
       <c r="D111" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>56</v>
+      <c r="F111" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B112" s="1" t="n">
@@ -4223,12 +4276,12 @@
       <c r="D112" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F112" s="7" t="s">
-        <v>56</v>
+      <c r="F112" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="s">
+      <c r="A113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B113" s="1" t="n">
@@ -4240,12 +4293,12 @@
       <c r="D113" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>56</v>
+      <c r="F113" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="7" t="s">
+      <c r="A114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B114" s="1" t="n">
@@ -4257,12 +4310,12 @@
       <c r="D114" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>56</v>
+      <c r="F114" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B115" s="1" t="n">
@@ -4274,12 +4327,12 @@
       <c r="D115" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F115" s="7" t="s">
-        <v>56</v>
+      <c r="F115" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="7" t="s">
+      <c r="A116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B116" s="1" t="n">
@@ -4291,12 +4344,12 @@
       <c r="D116" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>56</v>
+      <c r="F116" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B117" s="1" t="n">
@@ -4308,12 +4361,12 @@
       <c r="D117" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>56</v>
+      <c r="F117" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7" t="s">
+      <c r="A118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B118" s="1" t="n">
@@ -4325,12 +4378,12 @@
       <c r="D118" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F118" s="7" t="s">
-        <v>55</v>
+      <c r="F118" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="s">
+      <c r="A119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B119" s="1" t="n">
@@ -4342,12 +4395,12 @@
       <c r="D119" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>55</v>
+      <c r="F119" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7" t="s">
+      <c r="A120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B120" s="1" t="n">
@@ -4359,12 +4412,12 @@
       <c r="D120" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F120" s="7" t="s">
-        <v>55</v>
+      <c r="F120" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7" t="s">
+      <c r="A121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B121" s="1" t="n">
@@ -4376,12 +4429,12 @@
       <c r="D121" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F121" s="7" t="s">
-        <v>55</v>
+      <c r="F121" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B122" s="1" t="n">
@@ -4393,12 +4446,12 @@
       <c r="D122" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>55</v>
+      <c r="F122" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="s">
+      <c r="A123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B123" s="1" t="n">
@@ -4410,12 +4463,12 @@
       <c r="D123" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>55</v>
+      <c r="F123" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B124" s="1" t="n">
@@ -4427,12 +4480,12 @@
       <c r="D124" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>55</v>
+      <c r="F124" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7" t="s">
+      <c r="A125" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B125" s="1" t="n">
@@ -4444,12 +4497,12 @@
       <c r="D125" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F125" s="7" t="s">
-        <v>55</v>
+      <c r="F125" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B126" s="1" t="n">
@@ -4461,12 +4514,12 @@
       <c r="D126" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>55</v>
+      <c r="F126" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B127" s="1" t="n">
@@ -4478,12 +4531,12 @@
       <c r="D127" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>55</v>
+      <c r="F127" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7" t="s">
+      <c r="A128" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B128" s="1" t="n">
@@ -4495,12 +4548,12 @@
       <c r="D128" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F128" s="7" t="s">
-        <v>56</v>
+      <c r="F128" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7" t="s">
+      <c r="A129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B129" s="1" t="n">
@@ -4512,12 +4565,12 @@
       <c r="D129" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>56</v>
+      <c r="F129" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B130" s="1" t="n">
@@ -4529,12 +4582,12 @@
       <c r="D130" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>56</v>
+      <c r="F130" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B131" s="1" t="n">
@@ -4546,12 +4599,12 @@
       <c r="D131" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="F131" s="7" t="s">
-        <v>56</v>
+      <c r="F131" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B132" s="1" t="n">
@@ -4563,12 +4616,12 @@
       <c r="D132" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>56</v>
+      <c r="F132" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B133" s="1" t="n">
@@ -4580,12 +4633,12 @@
       <c r="D133" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>56</v>
+      <c r="F133" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="7" t="s">
+      <c r="A134" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B134" s="1" t="n">
@@ -4597,12 +4650,12 @@
       <c r="D134" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>56</v>
+      <c r="F134" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B135" s="1" t="n">
@@ -4614,12 +4667,12 @@
       <c r="D135" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>56</v>
+      <c r="F135" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B136" s="1" t="n">
@@ -4631,12 +4684,12 @@
       <c r="D136" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>56</v>
+      <c r="F136" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7" t="s">
+      <c r="A137" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B137" s="1" t="n">
@@ -4648,12 +4701,12 @@
       <c r="D137" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>56</v>
+      <c r="F137" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B138" s="1" t="n">
@@ -4665,12 +4718,12 @@
       <c r="D138" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F138" s="7" t="s">
-        <v>55</v>
+      <c r="F138" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B139" s="1" t="n">
@@ -4682,12 +4735,12 @@
       <c r="D139" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F139" s="7" t="s">
-        <v>55</v>
+      <c r="F139" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B140" s="1" t="n">
@@ -4699,12 +4752,12 @@
       <c r="D140" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>55</v>
+      <c r="F140" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7" t="s">
+      <c r="A141" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B141" s="1" t="n">
@@ -4716,12 +4769,12 @@
       <c r="D141" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F141" s="7" t="s">
-        <v>55</v>
+      <c r="F141" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B142" s="1" t="n">
@@ -4733,12 +4786,12 @@
       <c r="D142" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F142" s="7" t="s">
-        <v>55</v>
+      <c r="F142" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B143" s="1" t="n">
@@ -4750,12 +4803,12 @@
       <c r="D143" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F143" s="7" t="s">
-        <v>55</v>
+      <c r="F143" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="7" t="s">
+      <c r="A144" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B144" s="1" t="n">
@@ -4767,12 +4820,12 @@
       <c r="D144" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F144" s="7" t="s">
-        <v>55</v>
+      <c r="F144" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7" t="s">
+      <c r="A145" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B145" s="1" t="n">
@@ -4784,12 +4837,12 @@
       <c r="D145" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F145" s="7" t="s">
-        <v>55</v>
+      <c r="F145" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="7" t="s">
+      <c r="A146" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B146" s="1" t="n">
@@ -4801,12 +4854,12 @@
       <c r="D146" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F146" s="7" t="s">
-        <v>55</v>
+      <c r="F146" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7" t="s">
+      <c r="A147" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B147" s="1" t="n">
@@ -4818,12 +4871,12 @@
       <c r="D147" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F147" s="7" t="s">
-        <v>55</v>
+      <c r="F147" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="7" t="s">
+      <c r="A148" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B148" s="1" t="n">
@@ -4835,12 +4888,12 @@
       <c r="D148" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F148" s="7" t="s">
-        <v>57</v>
+      <c r="F148" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B149" s="1" t="n">
@@ -4852,12 +4905,12 @@
       <c r="D149" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F149" s="7" t="s">
-        <v>57</v>
+      <c r="F149" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B150" s="1" t="n">
@@ -4869,12 +4922,12 @@
       <c r="D150" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F150" s="7" t="s">
-        <v>57</v>
+      <c r="F150" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B151" s="1" t="n">
@@ -4886,12 +4939,12 @@
       <c r="D151" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F151" s="7" t="s">
-        <v>57</v>
+      <c r="F151" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B152" s="1" t="n">
@@ -4903,12 +4956,12 @@
       <c r="D152" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F152" s="7" t="s">
-        <v>57</v>
+      <c r="F152" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B153" s="1" t="n">
@@ -4920,12 +4973,12 @@
       <c r="D153" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F153" s="7" t="s">
-        <v>57</v>
+      <c r="F153" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B154" s="1" t="n">
@@ -4937,12 +4990,12 @@
       <c r="D154" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F154" s="7" t="s">
-        <v>57</v>
+      <c r="F154" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B155" s="1" t="n">
@@ -4954,12 +5007,12 @@
       <c r="D155" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F155" s="7" t="s">
-        <v>57</v>
+      <c r="F155" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B156" s="1" t="n">
@@ -4971,12 +5024,12 @@
       <c r="D156" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F156" s="7" t="s">
-        <v>57</v>
+      <c r="F156" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B157" s="1" t="n">
@@ -4988,12 +5041,12 @@
       <c r="D157" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F157" s="7" t="s">
-        <v>57</v>
+      <c r="F157" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B158" s="1" t="n">
@@ -5008,12 +5061,12 @@
       <c r="E158" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F158" s="7" t="s">
-        <v>55</v>
+      <c r="F158" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="10" t="s">
+      <c r="A159" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B159" s="1" t="n">
@@ -5028,12 +5081,12 @@
       <c r="E159" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F159" s="7" t="s">
-        <v>55</v>
+      <c r="F159" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="10" t="s">
+      <c r="A160" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B160" s="1" t="n">
@@ -5048,12 +5101,12 @@
       <c r="E160" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>55</v>
+      <c r="F160" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="10" t="s">
+      <c r="A161" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B161" s="1" t="n">
@@ -5068,12 +5121,12 @@
       <c r="E161" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F161" s="7" t="s">
-        <v>55</v>
+      <c r="F161" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="7" t="s">
+      <c r="A162" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B162" s="1" t="n">
@@ -5088,12 +5141,12 @@
       <c r="E162" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F162" s="7" t="s">
-        <v>55</v>
+      <c r="F162" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7" t="s">
+      <c r="A163" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B163" s="1" t="n">
@@ -5108,12 +5161,12 @@
       <c r="E163" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F163" s="7" t="s">
-        <v>55</v>
+      <c r="F163" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B164" s="1" t="n">
@@ -5128,12 +5181,12 @@
       <c r="E164" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F164" s="7" t="s">
-        <v>55</v>
+      <c r="F164" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B165" s="1" t="n">
@@ -5148,12 +5201,12 @@
       <c r="E165" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F165" s="7" t="s">
-        <v>55</v>
+      <c r="F165" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="7" t="s">
+      <c r="A166" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B166" s="1" t="n">
@@ -5168,12 +5221,12 @@
       <c r="E166" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F166" s="7" t="s">
-        <v>55</v>
+      <c r="F166" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="s">
+      <c r="A167" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B167" s="1" t="n">
@@ -5188,12 +5241,12 @@
       <c r="E167" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F167" s="7" t="s">
-        <v>55</v>
+      <c r="F167" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="7" t="s">
+      <c r="A168" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B168" s="1" t="n">
@@ -5205,12 +5258,12 @@
       <c r="D168" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F168" s="7" t="s">
-        <v>55</v>
+      <c r="F168" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="s">
+      <c r="A169" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B169" s="1" t="n">
@@ -5222,12 +5275,12 @@
       <c r="D169" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F169" s="7" t="s">
-        <v>55</v>
+      <c r="F169" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="7" t="s">
+      <c r="A170" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B170" s="1" t="n">
@@ -5239,12 +5292,12 @@
       <c r="D170" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F170" s="7" t="s">
-        <v>55</v>
+      <c r="F170" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="s">
+      <c r="A171" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B171" s="1" t="n">
@@ -5256,12 +5309,12 @@
       <c r="D171" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F171" s="7" t="s">
-        <v>55</v>
+      <c r="F171" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="7" t="s">
+      <c r="A172" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B172" s="1" t="n">
@@ -5273,12 +5326,12 @@
       <c r="D172" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F172" s="7" t="s">
-        <v>55</v>
+      <c r="F172" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="s">
+      <c r="A173" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B173" s="1" t="n">
@@ -5290,12 +5343,12 @@
       <c r="D173" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F173" s="7" t="s">
-        <v>55</v>
+      <c r="F173" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="7" t="s">
+      <c r="A174" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B174" s="1" t="n">
@@ -5307,12 +5360,12 @@
       <c r="D174" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F174" s="7" t="s">
-        <v>55</v>
+      <c r="F174" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="s">
+      <c r="A175" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B175" s="1" t="n">
@@ -5324,12 +5377,12 @@
       <c r="D175" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F175" s="7" t="s">
-        <v>55</v>
+      <c r="F175" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="7" t="s">
+      <c r="A176" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B176" s="1" t="n">
@@ -5341,12 +5394,12 @@
       <c r="D176" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F176" s="7" t="s">
-        <v>55</v>
+      <c r="F176" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="s">
+      <c r="A177" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B177" s="1" t="n">
@@ -5358,12 +5411,12 @@
       <c r="D177" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F177" s="7" t="s">
-        <v>55</v>
+      <c r="F177" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="7" t="s">
+      <c r="A178" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B178" s="1" t="n">
@@ -5375,12 +5428,12 @@
       <c r="D178" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F178" s="7" t="s">
-        <v>55</v>
+      <c r="F178" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="s">
+      <c r="A179" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B179" s="1" t="n">
@@ -5392,12 +5445,12 @@
       <c r="D179" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F179" s="7" t="s">
-        <v>55</v>
+      <c r="F179" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="7" t="s">
+      <c r="A180" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B180" s="1" t="n">
@@ -5409,12 +5462,12 @@
       <c r="D180" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F180" s="7" t="s">
-        <v>55</v>
+      <c r="F180" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="s">
+      <c r="A181" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B181" s="1" t="n">
@@ -5426,12 +5479,12 @@
       <c r="D181" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F181" s="7" t="s">
-        <v>55</v>
+      <c r="F181" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="7" t="s">
+      <c r="A182" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B182" s="1" t="n">
@@ -5443,12 +5496,12 @@
       <c r="D182" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F182" s="7" t="s">
-        <v>55</v>
+      <c r="F182" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="s">
+      <c r="A183" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B183" s="1" t="n">
@@ -5460,12 +5513,12 @@
       <c r="D183" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F183" s="7" t="s">
-        <v>57</v>
+      <c r="F183" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="7" t="s">
+      <c r="A184" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B184" s="1" t="n">
@@ -5477,12 +5530,12 @@
       <c r="D184" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F184" s="7" t="s">
-        <v>57</v>
+      <c r="F184" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="s">
+      <c r="A185" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B185" s="1" t="n">
@@ -5494,12 +5547,12 @@
       <c r="D185" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F185" s="7" t="s">
-        <v>57</v>
+      <c r="F185" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="7" t="s">
+      <c r="A186" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B186" s="1" t="n">
@@ -5511,12 +5564,12 @@
       <c r="D186" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F186" s="7" t="s">
-        <v>57</v>
+      <c r="F186" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="s">
+      <c r="A187" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B187" s="1" t="n">
@@ -5528,12 +5581,12 @@
       <c r="D187" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F187" s="7" t="s">
-        <v>57</v>
+      <c r="F187" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="7" t="s">
+      <c r="A188" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B188" s="1" t="n">
@@ -5545,12 +5598,12 @@
       <c r="D188" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F188" s="7" t="s">
-        <v>57</v>
+      <c r="F188" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7" t="s">
+      <c r="A189" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B189" s="1" t="n">
@@ -5562,12 +5615,12 @@
       <c r="D189" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F189" s="7" t="s">
-        <v>57</v>
+      <c r="F189" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="s">
+      <c r="A190" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B190" s="1" t="n">
@@ -5579,12 +5632,12 @@
       <c r="D190" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F190" s="7" t="s">
-        <v>57</v>
+      <c r="F190" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7" t="s">
+      <c r="A191" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B191" s="1" t="n">
@@ -5596,12 +5649,12 @@
       <c r="D191" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F191" s="7" t="s">
-        <v>57</v>
+      <c r="F191" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="7" t="s">
+      <c r="A192" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B192" s="1" t="n">
@@ -5613,12 +5666,12 @@
       <c r="D192" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F192" s="7" t="s">
-        <v>57</v>
+      <c r="F192" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7" t="s">
+      <c r="A193" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B193" s="1" t="n">
@@ -5630,12 +5683,12 @@
       <c r="D193" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F193" s="7" t="s">
-        <v>57</v>
+      <c r="F193" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="7" t="s">
+      <c r="A194" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B194" s="1" t="n">
@@ -5647,12 +5700,12 @@
       <c r="D194" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F194" s="7" t="s">
-        <v>57</v>
+      <c r="F194" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7" t="s">
+      <c r="A195" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B195" s="1" t="n">
@@ -5664,12 +5717,12 @@
       <c r="D195" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F195" s="7" t="s">
-        <v>57</v>
+      <c r="F195" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="7" t="s">
+      <c r="A196" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B196" s="1" t="n">
@@ -5681,12 +5734,12 @@
       <c r="D196" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F196" s="7" t="s">
-        <v>57</v>
+      <c r="F196" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7" t="s">
+      <c r="A197" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B197" s="1" t="n">
@@ -5698,12 +5751,12 @@
       <c r="D197" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F197" s="7" t="s">
-        <v>57</v>
+      <c r="F197" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="7" t="s">
+      <c r="A198" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B198" s="1" t="n">
@@ -5715,12 +5768,12 @@
       <c r="D198" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F198" s="7" t="s">
-        <v>56</v>
+      <c r="F198" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="7" t="s">
+      <c r="A199" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B199" s="1" t="n">
@@ -5732,12 +5785,12 @@
       <c r="D199" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F199" s="7" t="s">
-        <v>56</v>
+      <c r="F199" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="7" t="s">
+      <c r="A200" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B200" s="1" t="n">
@@ -5749,12 +5802,12 @@
       <c r="D200" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F200" s="7" t="s">
-        <v>56</v>
+      <c r="F200" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="7" t="s">
+      <c r="A201" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B201" s="1" t="n">
@@ -5766,12 +5819,12 @@
       <c r="D201" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F201" s="7" t="s">
-        <v>56</v>
+      <c r="F201" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="7" t="s">
+      <c r="A202" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B202" s="1" t="n">
@@ -5783,12 +5836,12 @@
       <c r="D202" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F202" s="7" t="s">
-        <v>56</v>
+      <c r="F202" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="7" t="s">
+      <c r="A203" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B203" s="1" t="n">
@@ -5800,12 +5853,12 @@
       <c r="D203" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F203" s="7" t="s">
-        <v>56</v>
+      <c r="F203" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="7" t="s">
+      <c r="A204" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B204" s="1" t="n">
@@ -5817,12 +5870,12 @@
       <c r="D204" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F204" s="7" t="s">
-        <v>56</v>
+      <c r="F204" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="7" t="s">
+      <c r="A205" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B205" s="1" t="n">
@@ -5834,12 +5887,12 @@
       <c r="D205" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F205" s="7" t="s">
-        <v>56</v>
+      <c r="F205" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="7" t="s">
+      <c r="A206" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B206" s="1" t="n">
@@ -5851,12 +5904,12 @@
       <c r="D206" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F206" s="7" t="s">
-        <v>56</v>
+      <c r="F206" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7" t="s">
+      <c r="A207" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B207" s="1" t="n">
@@ -5868,12 +5921,12 @@
       <c r="D207" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F207" s="7" t="s">
-        <v>56</v>
+      <c r="F207" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="7" t="s">
+      <c r="A208" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B208" s="1" t="n">
@@ -5885,12 +5938,12 @@
       <c r="D208" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F208" s="7" t="s">
-        <v>56</v>
+      <c r="F208" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="7" t="s">
+      <c r="A209" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B209" s="1" t="n">
@@ -5902,12 +5955,12 @@
       <c r="D209" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F209" s="7" t="s">
-        <v>56</v>
+      <c r="F209" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="7" t="s">
+      <c r="A210" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B210" s="1" t="n">
@@ -5919,12 +5972,12 @@
       <c r="D210" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F210" s="7" t="s">
-        <v>56</v>
+      <c r="F210" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="7" t="s">
+      <c r="A211" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B211" s="1" t="n">
@@ -5936,12 +5989,12 @@
       <c r="D211" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F211" s="7" t="s">
-        <v>56</v>
+      <c r="F211" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="7" t="s">
+      <c r="A212" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B212" s="1" t="n">
@@ -5953,12 +6006,12 @@
       <c r="D212" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F212" s="7" t="s">
-        <v>56</v>
+      <c r="F212" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="7" t="s">
+      <c r="A213" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B213" s="1" t="n">
@@ -5973,12 +6026,12 @@
       <c r="E213" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F213" s="7" t="s">
-        <v>55</v>
+      <c r="F213" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="7" t="s">
+      <c r="A214" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B214" s="1" t="n">
@@ -5993,12 +6046,12 @@
       <c r="E214" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F214" s="7" t="s">
-        <v>55</v>
+      <c r="F214" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="7" t="s">
+      <c r="A215" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B215" s="1" t="n">
@@ -6013,12 +6066,12 @@
       <c r="E215" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F215" s="7" t="s">
-        <v>55</v>
+      <c r="F215" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="7" t="s">
+      <c r="A216" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B216" s="1" t="n">
@@ -6033,12 +6086,12 @@
       <c r="E216" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F216" s="7" t="s">
-        <v>55</v>
+      <c r="F216" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="7" t="s">
+      <c r="A217" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B217" s="1" t="n">
@@ -6050,12 +6103,12 @@
       <c r="D217" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F217" s="7" t="s">
-        <v>55</v>
+      <c r="F217" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="7" t="s">
+      <c r="A218" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B218" s="1" t="n">
@@ -6067,12 +6120,12 @@
       <c r="D218" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F218" s="7" t="s">
-        <v>55</v>
+      <c r="F218" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="7" t="s">
+      <c r="A219" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B219" s="1" t="n">
@@ -6084,12 +6137,12 @@
       <c r="D219" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F219" s="7" t="s">
-        <v>55</v>
+      <c r="F219" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="7" t="s">
+      <c r="A220" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B220" s="1" t="n">
@@ -6101,12 +6154,12 @@
       <c r="D220" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F220" s="7" t="s">
-        <v>55</v>
+      <c r="F220" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="7" t="s">
+      <c r="A221" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B221" s="1" t="n">
@@ -6118,12 +6171,12 @@
       <c r="D221" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F221" s="7" t="s">
-        <v>55</v>
+      <c r="F221" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="7" t="s">
+      <c r="A222" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B222" s="1" t="n">
@@ -6135,12 +6188,12 @@
       <c r="D222" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F222" s="7" t="s">
-        <v>55</v>
+      <c r="F222" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="7" t="s">
+      <c r="A223" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B223" s="1" t="n">
@@ -6152,12 +6205,12 @@
       <c r="D223" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F223" s="7" t="s">
-        <v>55</v>
+      <c r="F223" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="7" t="s">
+      <c r="A224" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B224" s="1" t="n">
@@ -6169,12 +6222,12 @@
       <c r="D224" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F224" s="7" t="s">
-        <v>55</v>
+      <c r="F224" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="7" t="s">
+      <c r="A225" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B225" s="1" t="n">
@@ -6186,12 +6239,12 @@
       <c r="D225" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F225" s="7" t="s">
-        <v>55</v>
+      <c r="F225" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="7" t="s">
+      <c r="A226" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B226" s="1" t="n">
@@ -6203,12 +6256,12 @@
       <c r="D226" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F226" s="7" t="s">
-        <v>55</v>
+      <c r="F226" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="7" t="s">
+      <c r="A227" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B227" s="1" t="n">
@@ -6220,12 +6273,12 @@
       <c r="D227" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F227" s="7" t="s">
-        <v>55</v>
+      <c r="F227" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="7" t="s">
+      <c r="A228" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B228" s="1" t="n">
@@ -6237,12 +6290,12 @@
       <c r="D228" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F228" s="7" t="s">
-        <v>55</v>
+      <c r="F228" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="7" t="s">
+      <c r="A229" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B229" s="1" t="n">
@@ -6254,12 +6307,12 @@
       <c r="D229" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F229" s="7" t="s">
-        <v>55</v>
+      <c r="F229" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="7" t="s">
+      <c r="A230" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B230" s="1" t="n">
@@ -6271,12 +6324,12 @@
       <c r="D230" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F230" s="7" t="s">
-        <v>55</v>
+      <c r="F230" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="7" t="s">
+      <c r="A231" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B231" s="1" t="n">
@@ -6288,12 +6341,12 @@
       <c r="D231" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F231" s="7" t="s">
-        <v>55</v>
+      <c r="F231" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="7" t="s">
+      <c r="A232" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B232" s="1" t="n">
@@ -6305,12 +6358,12 @@
       <c r="D232" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F232" s="7" t="s">
-        <v>57</v>
+      <c r="F232" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="7" t="s">
+      <c r="A233" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B233" s="1" t="n">
@@ -6322,12 +6375,12 @@
       <c r="D233" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F233" s="7" t="s">
-        <v>57</v>
+      <c r="F233" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="7" t="s">
+      <c r="A234" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B234" s="1" t="n">
@@ -6339,12 +6392,12 @@
       <c r="D234" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F234" s="7" t="s">
-        <v>57</v>
+      <c r="F234" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="7" t="s">
+      <c r="A235" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B235" s="1" t="n">
@@ -6356,12 +6409,12 @@
       <c r="D235" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F235" s="7" t="s">
-        <v>57</v>
+      <c r="F235" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="7" t="s">
+      <c r="A236" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B236" s="1" t="n">
@@ -6373,12 +6426,12 @@
       <c r="D236" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F236" s="7" t="s">
-        <v>57</v>
+      <c r="F236" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="7" t="s">
+      <c r="A237" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B237" s="1" t="n">
@@ -6390,12 +6443,12 @@
       <c r="D237" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F237" s="7" t="s">
-        <v>57</v>
+      <c r="F237" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="7" t="s">
+      <c r="A238" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B238" s="1" t="n">
@@ -6407,12 +6460,12 @@
       <c r="D238" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F238" s="7" t="s">
-        <v>57</v>
+      <c r="F238" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="7" t="s">
+      <c r="A239" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B239" s="1" t="n">
@@ -6424,12 +6477,12 @@
       <c r="D239" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F239" s="7" t="s">
-        <v>57</v>
+      <c r="F239" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="7" t="s">
+      <c r="A240" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B240" s="1" t="n">
@@ -6441,12 +6494,12 @@
       <c r="D240" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F240" s="7" t="s">
-        <v>57</v>
+      <c r="F240" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="7" t="s">
+      <c r="A241" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B241" s="1" t="n">
@@ -6458,12 +6511,12 @@
       <c r="D241" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F241" s="7" t="s">
-        <v>57</v>
+      <c r="F241" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="7" t="s">
+      <c r="A242" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B242" s="1" t="n">
@@ -6475,12 +6528,12 @@
       <c r="D242" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F242" s="7" t="s">
-        <v>57</v>
+      <c r="F242" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="7" t="s">
+      <c r="A243" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B243" s="1" t="n">
@@ -6492,12 +6545,12 @@
       <c r="D243" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F243" s="7" t="s">
-        <v>57</v>
+      <c r="F243" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="7" t="s">
+      <c r="A244" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B244" s="1" t="n">
@@ -6509,12 +6562,12 @@
       <c r="D244" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F244" s="7" t="s">
-        <v>57</v>
+      <c r="F244" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="7" t="s">
+      <c r="A245" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B245" s="1" t="n">
@@ -6526,12 +6579,12 @@
       <c r="D245" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F245" s="7" t="s">
-        <v>57</v>
+      <c r="F245" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="7" t="s">
+      <c r="A246" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B246" s="1" t="n">
@@ -6543,12 +6596,12 @@
       <c r="D246" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F246" s="7" t="s">
-        <v>57</v>
+      <c r="F246" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="7" t="s">
+      <c r="A247" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B247" s="1" t="n">
@@ -6560,12 +6613,12 @@
       <c r="D247" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F247" s="7" t="s">
-        <v>56</v>
+      <c r="F247" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="7" t="s">
+      <c r="A248" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B248" s="1" t="n">
@@ -6577,12 +6630,12 @@
       <c r="D248" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F248" s="7" t="s">
-        <v>56</v>
+      <c r="F248" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="7" t="s">
+      <c r="A249" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B249" s="1" t="n">
@@ -6594,12 +6647,12 @@
       <c r="D249" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F249" s="7" t="s">
-        <v>56</v>
+      <c r="F249" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="7" t="s">
+      <c r="A250" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B250" s="1" t="n">
@@ -6611,12 +6664,12 @@
       <c r="D250" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F250" s="7" t="s">
-        <v>56</v>
+      <c r="F250" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="7" t="s">
+      <c r="A251" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B251" s="1" t="n">
@@ -6628,12 +6681,12 @@
       <c r="D251" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F251" s="7" t="s">
-        <v>56</v>
+      <c r="F251" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="7" t="s">
+      <c r="A252" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B252" s="1" t="n">
@@ -6645,12 +6698,12 @@
       <c r="D252" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F252" s="7" t="s">
-        <v>56</v>
+      <c r="F252" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="7" t="s">
+      <c r="A253" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B253" s="1" t="n">
@@ -6662,12 +6715,12 @@
       <c r="D253" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F253" s="7" t="s">
-        <v>56</v>
+      <c r="F253" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="7" t="s">
+      <c r="A254" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B254" s="1" t="n">
@@ -6679,12 +6732,12 @@
       <c r="D254" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F254" s="7" t="s">
-        <v>56</v>
+      <c r="F254" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="7" t="s">
+      <c r="A255" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B255" s="1" t="n">
@@ -6696,12 +6749,12 @@
       <c r="D255" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F255" s="7" t="s">
-        <v>56</v>
+      <c r="F255" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="7" t="s">
+      <c r="A256" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B256" s="1" t="n">
@@ -6713,12 +6766,12 @@
       <c r="D256" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F256" s="7" t="s">
-        <v>56</v>
+      <c r="F256" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="7" t="s">
+      <c r="A257" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B257" s="1" t="n">
@@ -6730,12 +6783,12 @@
       <c r="D257" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F257" s="7" t="s">
-        <v>56</v>
+      <c r="F257" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="7" t="s">
+      <c r="A258" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B258" s="1" t="n">
@@ -6747,12 +6800,12 @@
       <c r="D258" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F258" s="7" t="s">
-        <v>56</v>
+      <c r="F258" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="7" t="s">
+      <c r="A259" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B259" s="1" t="n">
@@ -6764,12 +6817,12 @@
       <c r="D259" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F259" s="7" t="s">
-        <v>56</v>
+      <c r="F259" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="7" t="s">
+      <c r="A260" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B260" s="1" t="n">
@@ -6781,12 +6834,12 @@
       <c r="D260" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F260" s="7" t="s">
-        <v>56</v>
+      <c r="F260" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="7" t="s">
+      <c r="A261" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B261" s="1" t="n">
@@ -6798,12 +6851,12 @@
       <c r="D261" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="F261" s="7" t="s">
-        <v>56</v>
+      <c r="F261" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="7" t="s">
+      <c r="A262" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B262" s="1" t="n">
@@ -6818,12 +6871,12 @@
       <c r="E262" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F262" s="7" t="s">
-        <v>55</v>
+      <c r="F262" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="7" t="s">
+      <c r="A263" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B263" s="1" t="n">
@@ -6838,12 +6891,12 @@
       <c r="E263" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F263" s="7" t="s">
-        <v>55</v>
+      <c r="F263" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="7" t="s">
+      <c r="A264" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B264" s="1" t="n">
@@ -6858,12 +6911,12 @@
       <c r="E264" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F264" s="7" t="s">
-        <v>55</v>
+      <c r="F264" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="7" t="s">
+      <c r="A265" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B265" s="1" t="n">
@@ -6878,12 +6931,12 @@
       <c r="E265" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F265" s="7" t="s">
-        <v>55</v>
+      <c r="F265" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="7" t="s">
+      <c r="A266" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B266" s="1" t="n">
@@ -6898,12 +6951,12 @@
       <c r="E266" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F266" s="7" t="s">
-        <v>55</v>
+      <c r="F266" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="7" t="s">
+      <c r="A267" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B267" s="1" t="n">
@@ -6918,12 +6971,12 @@
       <c r="E267" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F267" s="7" t="s">
-        <v>55</v>
+      <c r="F267" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="7" t="s">
+      <c r="A268" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B268" s="1" t="n">
@@ -6938,12 +6991,12 @@
       <c r="E268" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F268" s="7" t="s">
-        <v>55</v>
+      <c r="F268" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="7" t="s">
+      <c r="A269" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B269" s="1" t="n">
@@ -6958,12 +7011,12 @@
       <c r="E269" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F269" s="7" t="s">
-        <v>55</v>
+      <c r="F269" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="7" t="s">
+      <c r="A270" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B270" s="1" t="n">
@@ -6978,12 +7031,12 @@
       <c r="E270" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F270" s="7" t="s">
-        <v>55</v>
+      <c r="F270" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="7" t="s">
+      <c r="A271" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B271" s="1" t="n">
@@ -6998,12 +7051,12 @@
       <c r="E271" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F271" s="7" t="s">
-        <v>55</v>
+      <c r="F271" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="7" t="s">
+      <c r="A272" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B272" s="1" t="n">
@@ -7018,12 +7071,12 @@
       <c r="E272" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F272" s="7" t="s">
-        <v>55</v>
+      <c r="F272" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="7" t="s">
+      <c r="A273" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B273" s="1" t="n">
@@ -7038,12 +7091,12 @@
       <c r="E273" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F273" s="7" t="s">
-        <v>55</v>
+      <c r="F273" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="7" t="s">
+      <c r="A274" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B274" s="1" t="n">
@@ -7055,12 +7108,12 @@
       <c r="D274" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F274" s="7" t="s">
-        <v>55</v>
+      <c r="F274" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="7" t="s">
+      <c r="A275" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B275" s="1" t="n">
@@ -7072,12 +7125,12 @@
       <c r="D275" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F275" s="7" t="s">
-        <v>55</v>
+      <c r="F275" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="7" t="s">
+      <c r="A276" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B276" s="1" t="n">
@@ -7089,12 +7142,12 @@
       <c r="D276" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F276" s="7" t="s">
-        <v>55</v>
+      <c r="F276" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="7" t="s">
+      <c r="A277" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B277" s="1" t="n">
@@ -7106,12 +7159,12 @@
       <c r="D277" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F277" s="7" t="s">
-        <v>55</v>
+      <c r="F277" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="7" t="s">
+      <c r="A278" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B278" s="1" t="n">
@@ -7123,12 +7176,12 @@
       <c r="D278" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F278" s="7" t="s">
-        <v>55</v>
+      <c r="F278" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="7" t="s">
+      <c r="A279" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B279" s="1" t="n">
@@ -7140,12 +7193,12 @@
       <c r="D279" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F279" s="7" t="s">
-        <v>55</v>
+      <c r="F279" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="7" t="s">
+      <c r="A280" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B280" s="1" t="n">
@@ -7157,12 +7210,12 @@
       <c r="D280" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F280" s="7" t="s">
-        <v>55</v>
+      <c r="F280" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="7" t="s">
+      <c r="A281" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B281" s="1" t="n">
@@ -7174,12 +7227,12 @@
       <c r="D281" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F281" s="7" t="s">
-        <v>55</v>
+      <c r="F281" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="7" t="s">
+      <c r="A282" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B282" s="1" t="n">
@@ -7191,12 +7244,12 @@
       <c r="D282" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F282" s="7" t="s">
-        <v>55</v>
+      <c r="F282" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="7" t="s">
+      <c r="A283" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B283" s="1" t="n">
@@ -7208,12 +7261,12 @@
       <c r="D283" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F283" s="7" t="s">
-        <v>55</v>
+      <c r="F283" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="7" t="s">
+      <c r="A284" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B284" s="1" t="n">
@@ -7225,12 +7278,12 @@
       <c r="D284" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F284" s="7" t="s">
-        <v>55</v>
+      <c r="F284" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="7" t="s">
+      <c r="A285" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B285" s="1" t="n">
@@ -7242,12 +7295,12 @@
       <c r="D285" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F285" s="7" t="s">
-        <v>55</v>
+      <c r="F285" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="7" t="s">
+      <c r="A286" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B286" s="1" t="n">
@@ -7259,12 +7312,12 @@
       <c r="D286" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F286" s="7" t="s">
-        <v>55</v>
+      <c r="F286" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="7" t="s">
+      <c r="A287" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B287" s="1" t="n">
@@ -7276,12 +7329,12 @@
       <c r="D287" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F287" s="7" t="s">
-        <v>55</v>
+      <c r="F287" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="7" t="s">
+      <c r="A288" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B288" s="1" t="n">
@@ -7293,12 +7346,12 @@
       <c r="D288" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F288" s="7" t="s">
-        <v>55</v>
+      <c r="F288" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="7" t="s">
+      <c r="A289" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B289" s="1" t="n">
@@ -7310,12 +7363,12 @@
       <c r="D289" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F289" s="7" t="s">
-        <v>57</v>
+      <c r="F289" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="7" t="s">
+      <c r="A290" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B290" s="1" t="n">
@@ -7327,12 +7380,12 @@
       <c r="D290" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F290" s="7" t="s">
-        <v>57</v>
+      <c r="F290" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="7" t="s">
+      <c r="A291" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B291" s="1" t="n">
@@ -7344,12 +7397,12 @@
       <c r="D291" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F291" s="7" t="s">
-        <v>57</v>
+      <c r="F291" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="7" t="s">
+      <c r="A292" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B292" s="1" t="n">
@@ -7361,12 +7414,12 @@
       <c r="D292" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F292" s="7" t="s">
-        <v>57</v>
+      <c r="F292" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="7" t="s">
+      <c r="A293" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B293" s="1" t="n">
@@ -7378,12 +7431,12 @@
       <c r="D293" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F293" s="7" t="s">
-        <v>57</v>
+      <c r="F293" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="7" t="s">
+      <c r="A294" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B294" s="1" t="n">
@@ -7395,12 +7448,12 @@
       <c r="D294" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F294" s="7" t="s">
-        <v>57</v>
+      <c r="F294" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="7" t="s">
+      <c r="A295" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B295" s="1" t="n">
@@ -7412,12 +7465,12 @@
       <c r="D295" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F295" s="7" t="s">
-        <v>57</v>
+      <c r="F295" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="7" t="s">
+      <c r="A296" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B296" s="1" t="n">
@@ -7429,12 +7482,12 @@
       <c r="D296" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F296" s="7" t="s">
-        <v>57</v>
+      <c r="F296" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="7" t="s">
+      <c r="A297" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B297" s="1" t="n">
@@ -7446,12 +7499,12 @@
       <c r="D297" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F297" s="7" t="s">
-        <v>57</v>
+      <c r="F297" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="7" t="s">
+      <c r="A298" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B298" s="1" t="n">
@@ -7463,12 +7516,12 @@
       <c r="D298" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F298" s="7" t="s">
-        <v>57</v>
+      <c r="F298" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="7" t="s">
+      <c r="A299" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B299" s="1" t="n">
@@ -7480,12 +7533,12 @@
       <c r="D299" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F299" s="7" t="s">
-        <v>57</v>
+      <c r="F299" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="7" t="s">
+      <c r="A300" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B300" s="1" t="n">
@@ -7497,12 +7550,12 @@
       <c r="D300" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F300" s="7" t="s">
-        <v>57</v>
+      <c r="F300" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="7" t="s">
+      <c r="A301" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B301" s="1" t="n">
@@ -7514,12 +7567,12 @@
       <c r="D301" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F301" s="7" t="s">
-        <v>57</v>
+      <c r="F301" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="7" t="s">
+      <c r="A302" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B302" s="1" t="n">
@@ -7531,12 +7584,12 @@
       <c r="D302" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F302" s="7" t="s">
-        <v>57</v>
+      <c r="F302" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="7" t="s">
+      <c r="A303" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B303" s="1" t="n">
@@ -7548,12 +7601,12 @@
       <c r="D303" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F303" s="7" t="s">
-        <v>57</v>
+      <c r="F303" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="7" t="s">
+      <c r="A304" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B304" s="1" t="n">
@@ -7565,12 +7618,12 @@
       <c r="D304" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F304" s="7" t="s">
-        <v>56</v>
+      <c r="F304" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="7" t="s">
+      <c r="A305" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B305" s="1" t="n">
@@ -7582,12 +7635,12 @@
       <c r="D305" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F305" s="7" t="s">
-        <v>56</v>
+      <c r="F305" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="7" t="s">
+      <c r="A306" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B306" s="1" t="n">
@@ -7599,12 +7652,12 @@
       <c r="D306" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F306" s="7" t="s">
-        <v>56</v>
+      <c r="F306" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="7" t="s">
+      <c r="A307" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B307" s="1" t="n">
@@ -7616,12 +7669,12 @@
       <c r="D307" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F307" s="7" t="s">
-        <v>56</v>
+      <c r="F307" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="7" t="s">
+      <c r="A308" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B308" s="1" t="n">
@@ -7633,12 +7686,12 @@
       <c r="D308" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F308" s="7" t="s">
-        <v>56</v>
+      <c r="F308" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="7" t="s">
+      <c r="A309" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B309" s="1" t="n">
@@ -7650,12 +7703,12 @@
       <c r="D309" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F309" s="7" t="s">
-        <v>56</v>
+      <c r="F309" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="7" t="s">
+      <c r="A310" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B310" s="1" t="n">
@@ -7667,12 +7720,12 @@
       <c r="D310" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F310" s="7" t="s">
-        <v>56</v>
+      <c r="F310" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="7" t="s">
+      <c r="A311" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B311" s="1" t="n">
@@ -7684,12 +7737,12 @@
       <c r="D311" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F311" s="7" t="s">
-        <v>56</v>
+      <c r="F311" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="7" t="s">
+      <c r="A312" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B312" s="1" t="n">
@@ -7701,12 +7754,12 @@
       <c r="D312" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F312" s="7" t="s">
-        <v>56</v>
+      <c r="F312" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="7" t="s">
+      <c r="A313" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B313" s="1" t="n">
@@ -7718,12 +7771,12 @@
       <c r="D313" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F313" s="7" t="s">
-        <v>56</v>
+      <c r="F313" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="7" t="s">
+      <c r="A314" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B314" s="1" t="n">
@@ -7735,12 +7788,12 @@
       <c r="D314" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F314" s="7" t="s">
-        <v>56</v>
+      <c r="F314" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="7" t="s">
+      <c r="A315" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B315" s="1" t="n">
@@ -7752,12 +7805,12 @@
       <c r="D315" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F315" s="7" t="s">
-        <v>56</v>
+      <c r="F315" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="7" t="s">
+      <c r="A316" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B316" s="1" t="n">
@@ -7769,12 +7822,12 @@
       <c r="D316" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F316" s="7" t="s">
-        <v>56</v>
+      <c r="F316" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="7" t="s">
+      <c r="A317" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B317" s="1" t="n">
@@ -7786,12 +7839,12 @@
       <c r="D317" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F317" s="7" t="s">
-        <v>56</v>
+      <c r="F317" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="7" t="s">
+      <c r="A318" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B318" s="1" t="n">
@@ -7803,12 +7856,12 @@
       <c r="D318" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="F318" s="7" t="s">
-        <v>56</v>
+      <c r="F318" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="7" t="s">
+      <c r="A319" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B319" s="1" t="n">
@@ -7822,7 +7875,7 @@
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="7" t="s">
+      <c r="A320" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B320" s="1" t="n">
@@ -7836,7 +7889,7 @@
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="7" t="s">
+      <c r="A321" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B321" s="1" t="n">
@@ -7850,7 +7903,7 @@
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="7" t="s">
+      <c r="A322" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B322" s="1" t="n">
@@ -7864,7 +7917,7 @@
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="7" t="s">
+      <c r="A323" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B323" s="1" t="n">
@@ -7878,7 +7931,7 @@
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="7" t="s">
+      <c r="A324" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B324" s="1" t="n">
@@ -7892,7 +7945,7 @@
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="7" t="s">
+      <c r="A325" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B325" s="1" t="n">
@@ -7906,7 +7959,7 @@
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="7" t="s">
+      <c r="A326" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B326" s="1" t="n">
@@ -7920,7 +7973,7 @@
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="7" t="s">
+      <c r="A327" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B327" s="1" t="n">
@@ -7934,7 +7987,7 @@
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="7" t="s">
+      <c r="A328" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B328" s="1" t="n">
@@ -7948,7 +8001,7 @@
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="7" t="s">
+      <c r="A329" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B329" s="1" t="n">
@@ -7962,7 +8015,7 @@
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="7" t="s">
+      <c r="A330" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B330" s="1" t="n">
@@ -7976,7 +8029,7 @@
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="7" t="s">
+      <c r="A331" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B331" s="1" t="n">
@@ -7990,7 +8043,7 @@
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="7" t="s">
+      <c r="A332" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B332" s="1" t="n">
@@ -8004,7 +8057,7 @@
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="7" t="s">
+      <c r="A333" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B333" s="1" t="n">
@@ -8018,7 +8071,7 @@
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="7" t="s">
+      <c r="A334" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B334" s="1" t="n">
@@ -8032,7 +8085,7 @@
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="7" t="s">
+      <c r="A335" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B335" s="1" t="n">
@@ -8046,7 +8099,7 @@
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="7" t="s">
+      <c r="A336" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B336" s="1" t="n">
@@ -8060,7 +8113,7 @@
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="7" t="s">
+      <c r="A337" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B337" s="1" t="n">
@@ -8074,7 +8127,7 @@
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="7" t="s">
+      <c r="A338" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B338" s="1" t="n">
@@ -8088,7 +8141,7 @@
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="7" t="s">
+      <c r="A339" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B339" s="1" t="n">
@@ -8102,7 +8155,7 @@
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="7" t="s">
+      <c r="A340" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B340" s="1" t="n">
@@ -8116,7 +8169,7 @@
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="7" t="s">
+      <c r="A341" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B341" s="1" t="n">
@@ -8130,7 +8183,7 @@
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="7" t="s">
+      <c r="A342" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B342" s="1" t="n">
@@ -8144,7 +8197,7 @@
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="7" t="s">
+      <c r="A343" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B343" s="1" t="n">
@@ -8158,7 +8211,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="7" t="s">
+      <c r="A344" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B344" s="1" t="n">
@@ -8172,7 +8225,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="7" t="s">
+      <c r="A345" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B345" s="1" t="n">
@@ -8186,8 +8239,8 @@
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="7" t="s">
-        <v>58</v>
+      <c r="A346" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B346" s="1" t="n">
         <v>1</v>
@@ -8200,8 +8253,8 @@
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="7" t="s">
-        <v>58</v>
+      <c r="A347" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B347" s="1" t="n">
         <v>2</v>
@@ -8214,8 +8267,8 @@
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="7" t="s">
-        <v>58</v>
+      <c r="A348" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B348" s="1" t="n">
         <v>3</v>
@@ -8228,8 +8281,8 @@
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="7" t="s">
-        <v>58</v>
+      <c r="A349" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B349" s="1" t="n">
         <v>4</v>
@@ -8242,8 +8295,8 @@
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="7" t="s">
-        <v>58</v>
+      <c r="A350" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B350" s="1" t="n">
         <v>5</v>
@@ -8256,8 +8309,8 @@
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="7" t="s">
-        <v>58</v>
+      <c r="A351" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B351" s="1" t="n">
         <v>6</v>
@@ -8270,8 +8323,8 @@
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="7" t="s">
-        <v>58</v>
+      <c r="A352" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B352" s="1" t="n">
         <v>7</v>
@@ -8284,8 +8337,8 @@
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="7" t="s">
-        <v>58</v>
+      <c r="A353" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B353" s="1" t="n">
         <v>8</v>
@@ -8298,7 +8351,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="7" t="s">
+      <c r="A354" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B354" s="1" t="n">
@@ -8312,7 +8365,7 @@
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="7" t="s">
+      <c r="A355" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B355" s="1" t="n">
@@ -8326,7 +8379,7 @@
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="7" t="s">
+      <c r="A356" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B356" s="1" t="n">
@@ -8340,7 +8393,7 @@
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="7" t="s">
+      <c r="A357" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B357" s="1" t="n">
@@ -8354,7 +8407,7 @@
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="7" t="s">
+      <c r="A358" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B358" s="1" t="n">
@@ -8368,7 +8421,7 @@
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="7" t="s">
+      <c r="A359" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B359" s="1" t="n">
@@ -8382,7 +8435,7 @@
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="7" t="s">
+      <c r="A360" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B360" s="1" t="n">
@@ -8396,7 +8449,7 @@
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="7" t="s">
+      <c r="A361" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B361" s="1" t="n">
@@ -8410,7 +8463,7 @@
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="7" t="s">
+      <c r="A362" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B362" s="1" t="n">
@@ -8424,7 +8477,7 @@
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="7" t="s">
+      <c r="A363" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B363" s="1" t="n">
@@ -8438,7 +8491,7 @@
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="7" t="s">
+      <c r="A364" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B364" s="1" t="n">
@@ -8452,7 +8505,7 @@
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="7" t="s">
+      <c r="A365" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B365" s="1" t="n">
@@ -8466,7 +8519,7 @@
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="7" t="s">
+      <c r="A366" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B366" s="1" t="n">
@@ -8480,7 +8533,7 @@
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="7" t="s">
+      <c r="A367" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B367" s="1" t="n">
@@ -8494,7 +8547,7 @@
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="7" t="s">
+      <c r="A368" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B368" s="1" t="n">
@@ -8508,7 +8561,7 @@
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="7" t="s">
+      <c r="A369" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B369" s="1" t="n">
@@ -8522,7 +8575,7 @@
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="7" t="s">
+      <c r="A370" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B370" s="1" t="n">
@@ -8536,7 +8589,7 @@
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="7" t="s">
+      <c r="A371" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B371" s="1" t="n">
@@ -8550,7 +8603,7 @@
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="7" t="s">
+      <c r="A372" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B372" s="1" t="n">
@@ -8564,7 +8617,7 @@
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="7" t="s">
+      <c r="A373" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B373" s="1" t="n">
@@ -8578,7 +8631,7 @@
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="7" t="s">
+      <c r="A374" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B374" s="1" t="n">
@@ -8592,7 +8645,7 @@
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="7" t="s">
+      <c r="A375" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B375" s="1" t="n">
@@ -8606,7 +8659,7 @@
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="7" t="s">
+      <c r="A376" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B376" s="1" t="n">
@@ -8620,7 +8673,7 @@
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="7" t="s">
+      <c r="A377" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B377" s="1" t="n">
@@ -8634,7 +8687,7 @@
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="7" t="s">
+      <c r="A378" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B378" s="1" t="n">
@@ -8648,7 +8701,7 @@
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="7" t="s">
+      <c r="A379" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B379" s="1" t="n">
@@ -8662,7 +8715,7 @@
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="7" t="s">
+      <c r="A380" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B380" s="1" t="n">
@@ -8676,7 +8729,7 @@
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="7" t="s">
+      <c r="A381" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B381" s="1" t="n">
@@ -8690,7 +8743,7 @@
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="7" t="s">
+      <c r="A382" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B382" s="1" t="n">
@@ -8704,7 +8757,7 @@
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="7" t="s">
+      <c r="A383" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B383" s="1" t="n">
@@ -8718,7 +8771,7 @@
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="7" t="s">
+      <c r="A384" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B384" s="1" t="n">
@@ -8732,7 +8785,7 @@
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="7" t="s">
+      <c r="A385" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B385" s="1" t="n">
@@ -8746,7 +8799,7 @@
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="7" t="s">
+      <c r="A386" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B386" s="1" t="n">
@@ -8760,7 +8813,7 @@
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="7" t="s">
+      <c r="A387" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B387" s="1" t="n">
@@ -8774,7 +8827,7 @@
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="7" t="s">
+      <c r="A388" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B388" s="1" t="n">
@@ -8788,7 +8841,7 @@
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="7" t="s">
+      <c r="A389" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B389" s="1" t="n">
@@ -8802,7 +8855,7 @@
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="7" t="s">
+      <c r="A390" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B390" s="1" t="n">
@@ -8816,7 +8869,7 @@
       </c>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="7" t="s">
+      <c r="A391" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B391" s="1" t="n">
@@ -8830,7 +8883,7 @@
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="7" t="s">
+      <c r="A392" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B392" s="1" t="n">
@@ -8844,7 +8897,7 @@
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="7" t="s">
+      <c r="A393" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B393" s="1" t="n">
@@ -8858,7 +8911,7 @@
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="7" t="s">
+      <c r="A394" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B394" s="1" t="n">
@@ -8872,7 +8925,7 @@
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="7" t="s">
+      <c r="A395" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B395" s="1" t="n">
@@ -8886,7 +8939,7 @@
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="7" t="s">
+      <c r="A396" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B396" s="1" t="n">
@@ -8900,7 +8953,7 @@
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="7" t="s">
+      <c r="A397" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B397" s="1" t="n">
@@ -8914,7 +8967,7 @@
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="7" t="s">
+      <c r="A398" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B398" s="1" t="n">
@@ -8928,7 +8981,7 @@
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="7" t="s">
+      <c r="A399" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B399" s="1" t="n">
@@ -8942,7 +8995,7 @@
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="7" t="s">
+      <c r="A400" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B400" s="1" t="n">
@@ -8956,7 +9009,7 @@
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="7" t="s">
+      <c r="A401" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B401" s="1" t="n">
@@ -8970,7 +9023,7 @@
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="7" t="s">
+      <c r="A402" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B402" s="1" t="n">
@@ -8984,7 +9037,7 @@
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="7" t="s">
+      <c r="A403" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B403" s="1" t="n">
@@ -8998,7 +9051,7 @@
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="7" t="s">
+      <c r="A404" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B404" s="1" t="n">
@@ -9012,7 +9065,7 @@
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A405" s="7" t="s">
+      <c r="A405" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B405" s="1" t="n">
@@ -9026,7 +9079,7 @@
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A406" s="7" t="s">
+      <c r="A406" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B406" s="1" t="n">
@@ -9040,7 +9093,7 @@
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A407" s="7" t="s">
+      <c r="A407" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B407" s="1" t="n">
@@ -9054,7 +9107,7 @@
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A408" s="7" t="s">
+      <c r="A408" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B408" s="1" t="n">
@@ -9068,7 +9121,7 @@
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A409" s="7" t="s">
+      <c r="A409" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B409" s="1" t="n">
@@ -9082,7 +9135,7 @@
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A410" s="7" t="s">
+      <c r="A410" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B410" s="1" t="n">
@@ -9096,7 +9149,7 @@
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A411" s="7" t="s">
+      <c r="A411" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B411" s="1" t="n">
@@ -9110,7 +9163,7 @@
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A412" s="7" t="s">
+      <c r="A412" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B412" s="1" t="n">
@@ -9124,7 +9177,7 @@
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A413" s="7" t="s">
+      <c r="A413" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B413" s="1" t="n">
@@ -9138,7 +9191,7 @@
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A414" s="7" t="s">
+      <c r="A414" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B414" s="1" t="n">
@@ -9152,7 +9205,7 @@
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A415" s="7" t="s">
+      <c r="A415" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B415" s="1" t="n">
@@ -9161,13 +9214,13 @@
       <c r="C415" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F415" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M415" s="12"/>
+      <c r="F415" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M415" s="11"/>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A416" s="7" t="s">
+      <c r="A416" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B416" s="1" t="n">
@@ -9176,12 +9229,12 @@
       <c r="C416" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F416" s="7" t="s">
-        <v>55</v>
+      <c r="F416" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="7" t="s">
+      <c r="A417" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B417" s="1" t="n">
@@ -9190,12 +9243,12 @@
       <c r="C417" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F417" s="7" t="s">
-        <v>55</v>
+      <c r="F417" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="7" t="s">
+      <c r="A418" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B418" s="1" t="n">
@@ -9204,12 +9257,12 @@
       <c r="C418" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="F418" s="7" t="s">
-        <v>55</v>
+      <c r="F418" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="7" t="s">
+      <c r="A419" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B419" s="1" t="n">
@@ -9218,12 +9271,12 @@
       <c r="C419" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F419" s="7" t="s">
-        <v>55</v>
+      <c r="F419" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="7" t="s">
+      <c r="A420" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B420" s="1" t="n">
@@ -9232,12 +9285,12 @@
       <c r="C420" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F420" s="7" t="s">
-        <v>55</v>
+      <c r="F420" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A421" s="7" t="s">
+      <c r="A421" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B421" s="1" t="n">
@@ -9246,12 +9299,12 @@
       <c r="C421" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F421" s="7" t="s">
-        <v>55</v>
+      <c r="F421" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A422" s="7" t="s">
+      <c r="A422" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B422" s="1" t="n">
@@ -9260,12 +9313,12 @@
       <c r="C422" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F422" s="7" t="s">
-        <v>55</v>
+      <c r="F422" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A423" s="7" t="s">
+      <c r="A423" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B423" s="1" t="n">
@@ -9274,12 +9327,12 @@
       <c r="C423" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F423" s="7" t="s">
-        <v>55</v>
+      <c r="F423" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="7" t="s">
+      <c r="A424" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B424" s="1" t="n">
@@ -9288,12 +9341,12 @@
       <c r="C424" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F424" s="7" t="s">
-        <v>55</v>
+      <c r="F424" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A425" s="7" t="s">
+      <c r="A425" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B425" s="1" t="n">
@@ -9302,12 +9355,12 @@
       <c r="C425" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F425" s="7" t="s">
-        <v>55</v>
+      <c r="F425" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A426" s="7" t="s">
+      <c r="A426" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B426" s="1" t="n">
@@ -9316,12 +9369,12 @@
       <c r="C426" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F426" s="7" t="s">
-        <v>55</v>
+      <c r="F426" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A427" s="7" t="s">
+      <c r="A427" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B427" s="1" t="n">
@@ -9330,12 +9383,12 @@
       <c r="C427" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F427" s="7" t="s">
-        <v>55</v>
+      <c r="F427" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A428" s="7" t="s">
+      <c r="A428" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B428" s="1" t="n">
@@ -9344,12 +9397,12 @@
       <c r="C428" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F428" s="7" t="s">
-        <v>55</v>
+      <c r="F428" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A429" s="7" t="s">
+      <c r="A429" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B429" s="1" t="n">
@@ -9358,12 +9411,12 @@
       <c r="C429" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="F429" s="7" t="s">
-        <v>55</v>
+      <c r="F429" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A430" s="7" t="s">
+      <c r="A430" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B430" s="1" t="n">
@@ -9372,12 +9425,12 @@
       <c r="C430" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="F430" s="7" t="s">
-        <v>57</v>
+      <c r="F430" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A431" s="7" t="s">
+      <c r="A431" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B431" s="1" t="n">
@@ -9386,12 +9439,12 @@
       <c r="C431" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="F431" s="7" t="s">
-        <v>57</v>
+      <c r="F431" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A432" s="7" t="s">
+      <c r="A432" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B432" s="1" t="n">
@@ -9400,12 +9453,12 @@
       <c r="C432" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="F432" s="7" t="s">
-        <v>57</v>
+      <c r="F432" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A433" s="7" t="s">
+      <c r="A433" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B433" s="1" t="n">
@@ -9414,12 +9467,12 @@
       <c r="C433" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="F433" s="7" t="s">
-        <v>57</v>
+      <c r="F433" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A434" s="7" t="s">
+      <c r="A434" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B434" s="1" t="n">
@@ -9428,12 +9481,12 @@
       <c r="C434" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F434" s="7" t="s">
-        <v>57</v>
+      <c r="F434" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A435" s="7" t="s">
+      <c r="A435" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B435" s="1" t="n">
@@ -9442,12 +9495,12 @@
       <c r="C435" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F435" s="7" t="s">
-        <v>57</v>
+      <c r="F435" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A436" s="7" t="s">
+      <c r="A436" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B436" s="1" t="n">
@@ -9456,12 +9509,12 @@
       <c r="C436" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F436" s="7" t="s">
-        <v>57</v>
+      <c r="F436" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A437" s="7" t="s">
+      <c r="A437" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B437" s="1" t="n">
@@ -9470,12 +9523,12 @@
       <c r="C437" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F437" s="7" t="s">
-        <v>57</v>
+      <c r="F437" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A438" s="7" t="s">
+      <c r="A438" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B438" s="1" t="n">
@@ -9484,12 +9537,12 @@
       <c r="C438" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="F438" s="7" t="s">
-        <v>57</v>
+      <c r="F438" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A439" s="7" t="s">
+      <c r="A439" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B439" s="1" t="n">
@@ -9498,12 +9551,12 @@
       <c r="C439" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F439" s="7" t="s">
-        <v>57</v>
+      <c r="F439" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A440" s="7" t="s">
+      <c r="A440" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B440" s="1" t="n">
@@ -9512,12 +9565,12 @@
       <c r="C440" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F440" s="7" t="s">
-        <v>57</v>
+      <c r="F440" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A441" s="7" t="s">
+      <c r="A441" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B441" s="1" t="n">
@@ -9526,12 +9579,12 @@
       <c r="C441" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F441" s="7" t="s">
-        <v>57</v>
+      <c r="F441" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A442" s="7" t="s">
+      <c r="A442" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B442" s="1" t="n">
@@ -9540,12 +9593,12 @@
       <c r="C442" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F442" s="7" t="s">
-        <v>57</v>
+      <c r="F442" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="7" t="s">
+      <c r="A443" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B443" s="1" t="n">
@@ -9554,12 +9607,12 @@
       <c r="C443" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F443" s="7" t="s">
-        <v>57</v>
+      <c r="F443" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="7" t="s">
+      <c r="A444" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B444" s="1" t="n">
@@ -9568,12 +9621,12 @@
       <c r="C444" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="F444" s="7" t="s">
-        <v>57</v>
+      <c r="F444" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="7" t="s">
+      <c r="A445" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B445" s="1" t="n">
@@ -9582,12 +9635,12 @@
       <c r="C445" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F445" s="7" t="s">
-        <v>56</v>
+      <c r="F445" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="7" t="s">
+      <c r="A446" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B446" s="1" t="n">
@@ -9596,12 +9649,12 @@
       <c r="C446" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F446" s="7" t="s">
-        <v>56</v>
+      <c r="F446" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="7" t="s">
+      <c r="A447" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B447" s="1" t="n">
@@ -9610,12 +9663,12 @@
       <c r="C447" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F447" s="7" t="s">
-        <v>56</v>
+      <c r="F447" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A448" s="7" t="s">
+      <c r="A448" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B448" s="1" t="n">
@@ -9624,12 +9677,12 @@
       <c r="C448" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F448" s="7" t="s">
-        <v>56</v>
+      <c r="F448" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A449" s="7" t="s">
+      <c r="A449" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B449" s="1" t="n">
@@ -9638,12 +9691,12 @@
       <c r="C449" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F449" s="7" t="s">
-        <v>56</v>
+      <c r="F449" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A450" s="7" t="s">
+      <c r="A450" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B450" s="1" t="n">
@@ -9652,12 +9705,12 @@
       <c r="C450" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F450" s="7" t="s">
-        <v>56</v>
+      <c r="F450" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A451" s="7" t="s">
+      <c r="A451" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B451" s="1" t="n">
@@ -9666,12 +9719,12 @@
       <c r="C451" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="F451" s="7" t="s">
-        <v>56</v>
+      <c r="F451" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A452" s="7" t="s">
+      <c r="A452" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B452" s="1" t="n">
@@ -9680,12 +9733,12 @@
       <c r="C452" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F452" s="7" t="s">
-        <v>56</v>
+      <c r="F452" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A453" s="7" t="s">
+      <c r="A453" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B453" s="1" t="n">
@@ -9694,12 +9747,12 @@
       <c r="C453" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F453" s="7" t="s">
-        <v>56</v>
+      <c r="F453" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A454" s="7" t="s">
+      <c r="A454" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B454" s="1" t="n">
@@ -9708,12 +9761,12 @@
       <c r="C454" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F454" s="7" t="s">
-        <v>56</v>
+      <c r="F454" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A455" s="7" t="s">
+      <c r="A455" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B455" s="1" t="n">
@@ -9722,12 +9775,12 @@
       <c r="C455" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F455" s="7" t="s">
-        <v>56</v>
+      <c r="F455" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A456" s="7" t="s">
+      <c r="A456" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B456" s="1" t="n">
@@ -9736,12 +9789,12 @@
       <c r="C456" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F456" s="7" t="s">
-        <v>56</v>
+      <c r="F456" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A457" s="7" t="s">
+      <c r="A457" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B457" s="1" t="n">
@@ -9750,12 +9803,12 @@
       <c r="C457" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F457" s="7" t="s">
-        <v>56</v>
+      <c r="F457" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A458" s="7" t="s">
+      <c r="A458" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B458" s="1" t="n">
@@ -9764,12 +9817,12 @@
       <c r="C458" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F458" s="7" t="s">
-        <v>56</v>
+      <c r="F458" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A459" s="7" t="s">
+      <c r="A459" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B459" s="1" t="n">
@@ -9778,638 +9831,8 @@
       <c r="C459" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="F459" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B460" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C460" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F460" s="7" t="s">
+      <c r="F459" s="6" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B461" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C461" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F461" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A462" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B462" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C462" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F462" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A463" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B463" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C463" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F463" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A464" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B464" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C464" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F464" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A465" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B465" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C465" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F465" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A466" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B466" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C466" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F466" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A467" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B467" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C467" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F467" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B468" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C468" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F468" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A469" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B469" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C469" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F469" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B470" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C470" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F470" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B471" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C471" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F471" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A472" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B472" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C472" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F472" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B473" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C473" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F473" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B474" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C474" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F474" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B475" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C475" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="F475" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B476" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C476" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="F476" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A477" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B477" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C477" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="F477" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A478" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B478" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C478" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="F478" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A479" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B479" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C479" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F479" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A480" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B480" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C480" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F480" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B481" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C481" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F481" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A482" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B482" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C482" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F482" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A483" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B483" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C483" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="F483" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A484" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B484" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C484" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F484" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A485" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B485" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C485" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F485" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A486" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B486" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C486" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F486" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A487" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B487" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C487" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F487" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B488" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C488" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F488" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B489" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C489" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="F489" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B490" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C490" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F490" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A491" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B491" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C491" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F491" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A492" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B492" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C492" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F492" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A493" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B493" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C493" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F493" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A494" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B494" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C494" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F494" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A495" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B495" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C495" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F495" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A496" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B496" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="C496" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="F496" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A497" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B497" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="C497" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F497" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A498" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B498" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="C498" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F498" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B499" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C499" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F499" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A500" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B500" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="C500" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F500" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A501" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B501" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C501" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F501" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A502" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B502" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C502" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F502" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A503" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B503" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="C503" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F503" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A504" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B504" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="C504" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="F504" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -10421,4 +9844,282 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="28.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="19.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="13.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="12" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="n">
+        <v>129</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="n">
+        <v>367</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -355,7 +355,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -401,10 +401,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9854,262 +9850,262 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="18.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="28.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="19.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="13.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="12" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="1" t="n">
         <v>367</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="1" t="s">
         <v>75</v>
       </c>
     </row>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="81">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">unvan_sira_no</t>
   </si>
   <si>
-    <t xml:space="preserve">kadro_unvan</t>
+    <t xml:space="preserve">unvan_adi</t>
   </si>
   <si>
     <t xml:space="preserve">unvan_sinifi</t>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t xml:space="preserve">4B Sözleşmeli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/B İ.H.</t>
   </si>
   <si>
     <t xml:space="preserve">4/B K.K.Ö.</t>
@@ -9847,7 +9850,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
@@ -10055,7 +10058,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>76</v>
@@ -10069,7 +10072,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>77</v>
@@ -10083,29 +10086,43 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>367</v>
+        <v>155</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>367</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>75</v>
       </c>
     </row>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="87">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -212,6 +212,9 @@
     <t xml:space="preserve">personel_tipi</t>
   </si>
   <si>
+    <t xml:space="preserve">İl Müftü Yardımcısı</t>
+  </si>
+  <si>
     <t xml:space="preserve">İlçe Müftüsü</t>
   </si>
   <si>
@@ -227,7 +230,19 @@
     <t xml:space="preserve">Din Hizmetleri</t>
   </si>
   <si>
+    <t xml:space="preserve">Uzman Vaiz - Alo Fetva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cezaevi Vaizi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuran Kursu Uzm. Öğrt.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kuran Kursu Öğreticisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baş İmam Hatip</t>
   </si>
   <si>
     <t xml:space="preserve">Uzman İmam Hatip</t>
@@ -243,6 +258,9 @@
   </si>
   <si>
     <t xml:space="preserve">Yardımcı Hizmetler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaloriferci</t>
   </si>
   <si>
     <t xml:space="preserve">4/B M.K.</t>
@@ -358,7 +376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -407,6 +425,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,6 +438,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -9850,7 +9881,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
@@ -9876,13 +9907,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -9890,13 +9918,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>32</v>
@@ -9904,13 +9929,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>32</v>
@@ -9918,13 +9943,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
@@ -9932,13 +9957,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>32</v>
@@ -9946,41 +9971,37 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C7" s="12"/>
       <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>66</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C8" s="12"/>
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
@@ -9988,13 +10009,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>32</v>
@@ -10002,13 +10023,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>32</v>
@@ -10016,13 +10037,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>32</v>
@@ -10030,13 +10051,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>32</v>
@@ -10044,69 +10065,69 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>32</v>
@@ -10114,17 +10135,261 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
         <v>367</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="D35" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0"/>
+      <c r="C36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0"/>
+      <c r="C37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0"/>
+      <c r="C38" s="12"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0"/>
+      <c r="C39" s="12"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0"/>
+      <c r="C40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0"/>
+      <c r="C41" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,6 +13,7 @@
     <sheet name="yan_odeme_puanlari" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="ozel_hizmet_tazminati" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="kadro_unvan_sira_no" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sayfa6" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="119">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -212,25 +213,28 @@
     <t xml:space="preserve">personel_tipi</t>
   </si>
   <si>
+    <t xml:space="preserve">GİH</t>
+  </si>
+  <si>
     <t xml:space="preserve">İl Müftü Yardımcısı</t>
   </si>
   <si>
     <t xml:space="preserve">İlçe Müftüsü</t>
   </si>
   <si>
-    <t xml:space="preserve">Genel İdare Hizmetleri</t>
-  </si>
-  <si>
     <t xml:space="preserve">Şube Müdürü</t>
   </si>
   <si>
     <t xml:space="preserve">Din Hizmetleri Uzmanı</t>
   </si>
   <si>
-    <t xml:space="preserve">Din Hizmetleri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uzman Vaiz - Alo Fetva</t>
+    <t xml:space="preserve">EÖH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DH</t>
   </si>
   <si>
     <t xml:space="preserve">Cezaevi Vaizi</t>
@@ -257,7 +261,7 @@
     <t xml:space="preserve">Veri Haz.ve Kont.İşl.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yardımcı Hizmetler</t>
+    <t xml:space="preserve">YH</t>
   </si>
   <si>
     <t xml:space="preserve">Kaloriferci</t>
@@ -285,6 +289,99 @@
   </si>
   <si>
     <t xml:space="preserve">4/B Koruma ve Güvenlik Görevlisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırmacı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırmacı (6191 BKK) (01-12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırmacı (Ö.) (01-12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayniyat Saymanı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baş Müezzin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cami Rehberi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daire Tabibi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dini İhtisas Merkezi Müdürü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dini Yüksek İhtisas Merkezi Müdürü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eğitim Görevlisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eğitim Merkezi Müdürü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eğitim Uzmanı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kameraman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuran Eğitim Merkezi Müdürü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuran Kursu Baş Öğrt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kütüphaneci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhabir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhasebeci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müdür Yardımcısı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mühendis(Ö.) (01-08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psikolog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spiker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teberrukat Saymanı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekniker (Ö.) (01-09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekniker (Ş) (1-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknisyen (Ö.) (03-12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknisyen (Ş) (5-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veri Haz. ve Kont. İşl. (Ö.)(03-12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yapım ve Yayın Elemanı (Ş)(5-15)</t>
   </si>
 </sst>
 </file>
@@ -376,7 +473,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -423,6 +520,10 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -9881,27 +9982,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.8"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9912,6 +10013,9 @@
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
@@ -9921,6 +10025,9 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -9932,10 +10039,10 @@
         <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>32</v>
@@ -9949,7 +10056,7 @@
         <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
@@ -9963,7 +10070,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>32</v>
@@ -9976,7 +10083,9 @@
       <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
@@ -9988,7 +10097,9 @@
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
@@ -10001,7 +10112,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
@@ -10009,13 +10120,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>32</v>
@@ -10023,13 +10134,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>32</v>
@@ -10037,13 +10148,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>32</v>
@@ -10051,13 +10162,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>32</v>
@@ -10065,13 +10176,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>32</v>
@@ -10079,13 +10190,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>32</v>
@@ -10093,13 +10204,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>32</v>
@@ -10107,13 +10218,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>32</v>
@@ -10121,13 +10232,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>32</v>
@@ -10135,13 +10246,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>20</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>32</v>
@@ -10149,13 +10260,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>32</v>
@@ -10163,37 +10274,41 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="12"/>
+        <v>24</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="D21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="D22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>32</v>
@@ -10201,13 +10316,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>32</v>
@@ -10215,13 +10330,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -10229,13 +10344,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>32</v>
@@ -10243,13 +10358,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -10257,13 +10372,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>32</v>
@@ -10271,125 +10386,597 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>155</v>
+        <v>367</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="13"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="13"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="13"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="13"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="13"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D54" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D56" s="13"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="13"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D58" s="13"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="13"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D61" s="13"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D63" s="13"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D64" s="13"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D65" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>367</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0"/>
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0"/>
-      <c r="C37" s="12"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0"/>
-      <c r="C38" s="12"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0"/>
-      <c r="C39" s="12"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0"/>
-      <c r="C40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0"/>
-      <c r="C41" s="12"/>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="119">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -526,7 +526,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -539,15 +539,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2676,7 +2667,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M459"/>
+  <dimension ref="A1:M465"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.74"/>
@@ -3303,7 +3294,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>50</v>
@@ -3312,18 +3303,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
-        <v>31</v>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C45" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <v>100</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>115</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3331,10 +3322,10 @@
         <v>31</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>115</v>
@@ -3345,13 +3336,13 @@
         <v>31</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="1" t="n">
         <v>80</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,10 +3350,10 @@
         <v>31</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>110</v>
@@ -3373,41 +3364,41 @@
         <v>31</v>
       </c>
       <c r="B49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C50" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D50" s="1" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>20</v>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3415,13 +3406,13 @@
         <v>20</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" s="1" t="n">
         <v>82</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3429,13 +3420,13 @@
         <v>20</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="n">
         <v>82</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3443,13 +3434,13 @@
         <v>20</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3457,55 +3448,55 @@
         <v>20</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>120.56</v>
+        <v>72</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>120.56</v>
+        <v>72</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>115.56</v>
+        <v>72</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3513,10 +3504,10 @@
         <v>21</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>115.56</v>
+        <v>120.56</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>65</v>
@@ -3527,10 +3518,10 @@
         <v>21</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>105.56</v>
+        <v>120.56</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>65</v>
@@ -3541,10 +3532,10 @@
         <v>21</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>105.56</v>
+        <v>115.56</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>65</v>
@@ -3555,10 +3546,10 @@
         <v>21</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>105.56</v>
+        <v>115.56</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>65</v>
@@ -3569,7 +3560,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C63" s="1" t="n">
         <v>105.56</v>
@@ -3583,7 +3574,7 @@
         <v>21</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>105.56</v>
@@ -3594,44 +3585,44 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,13 +3630,13 @@
         <v>22</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>55</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3653,13 +3644,13 @@
         <v>22</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3667,13 +3658,13 @@
         <v>22</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3681,13 +3672,13 @@
         <v>22</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3695,13 +3686,13 @@
         <v>22</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,73 +3700,55 @@
         <v>22</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E74" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3783,16 +3756,16 @@
         <v>28</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D77" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>54</v>
@@ -3803,16 +3776,16 @@
         <v>28</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D78" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>54</v>
@@ -3820,19 +3793,19 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>54</v>
@@ -3840,19 +3813,19 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>54</v>
@@ -3860,19 +3833,19 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>54</v>
@@ -3883,16 +3856,16 @@
         <v>27</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>54</v>
@@ -3903,16 +3876,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>54</v>
@@ -3920,50 +3893,59 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F84" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E85" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F85" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>66</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>54</v>
@@ -3974,10 +3956,10 @@
         <v>29</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D87" s="1" t="n">
         <v>66</v>
@@ -3991,10 +3973,10 @@
         <v>29</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>66</v>
@@ -4005,13 +3987,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>66</v>
@@ -4022,13 +4004,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>66</v>
@@ -4039,13 +4021,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>66</v>
@@ -4059,10 +4041,10 @@
         <v>26</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>66</v>
@@ -4076,10 +4058,10 @@
         <v>26</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>66</v>
@@ -4093,10 +4075,10 @@
         <v>26</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D94" s="1" t="n">
         <v>66</v>
@@ -4110,10 +4092,10 @@
         <v>26</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>66</v>
@@ -4127,7 +4109,7 @@
         <v>26</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C96" s="1" t="n">
         <v>120</v>
@@ -4144,7 +4126,7 @@
         <v>26</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C97" s="1" t="n">
         <v>120</v>
@@ -4158,16 +4140,16 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>54</v>
@@ -4175,16 +4157,16 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>54</v>
@@ -4192,16 +4174,16 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>54</v>
@@ -4212,13 +4194,13 @@
         <v>23</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C101" s="1" t="n">
         <v>100</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>54</v>
@@ -4229,13 +4211,13 @@
         <v>23</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>54</v>
@@ -4246,13 +4228,13 @@
         <v>23</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>54</v>
@@ -4263,13 +4245,13 @@
         <v>23</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>54</v>
@@ -4280,13 +4262,13 @@
         <v>23</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C105" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>54</v>
@@ -4297,13 +4279,13 @@
         <v>23</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C106" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>54</v>
@@ -4314,13 +4296,13 @@
         <v>23</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C107" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>54</v>
@@ -4331,16 +4313,16 @@
         <v>23</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4348,16 +4330,16 @@
         <v>23</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,16 +4347,16 @@
         <v>23</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4382,13 +4364,13 @@
         <v>23</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C111" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>55</v>
@@ -4399,13 +4381,13 @@
         <v>23</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C112" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>55</v>
@@ -4416,13 +4398,13 @@
         <v>23</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>55</v>
@@ -4433,13 +4415,13 @@
         <v>23</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>55</v>
@@ -4450,13 +4432,13 @@
         <v>23</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>55</v>
@@ -4467,13 +4449,13 @@
         <v>23</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C116" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>55</v>
@@ -4484,13 +4466,13 @@
         <v>23</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C117" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>55</v>
@@ -4498,53 +4480,53 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4552,13 +4534,13 @@
         <v>24</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C121" s="1" t="n">
         <v>100</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>54</v>
@@ -4569,13 +4551,13 @@
         <v>24</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>54</v>
@@ -4586,13 +4568,13 @@
         <v>24</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>54</v>
@@ -4603,13 +4585,13 @@
         <v>24</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>54</v>
@@ -4620,13 +4602,13 @@
         <v>24</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C125" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>54</v>
@@ -4637,13 +4619,13 @@
         <v>24</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C126" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>54</v>
@@ -4654,13 +4636,13 @@
         <v>24</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C127" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>54</v>
@@ -4671,16 +4653,16 @@
         <v>24</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4688,16 +4670,16 @@
         <v>24</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4705,16 +4687,16 @@
         <v>24</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4722,13 +4704,13 @@
         <v>24</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C131" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>55</v>
@@ -4739,13 +4721,13 @@
         <v>24</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C132" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>55</v>
@@ -4756,13 +4738,13 @@
         <v>24</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>55</v>
@@ -4773,13 +4755,13 @@
         <v>24</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>55</v>
@@ -4790,13 +4772,13 @@
         <v>24</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>55</v>
@@ -4807,13 +4789,13 @@
         <v>24</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C136" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>55</v>
@@ -4824,13 +4806,13 @@
         <v>24</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>55</v>
@@ -4838,53 +4820,53 @@
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4892,7 +4874,7 @@
         <v>25</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C141" s="1" t="n">
         <v>140</v>
@@ -4909,10 +4891,10 @@
         <v>25</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>65</v>
@@ -4926,10 +4908,10 @@
         <v>25</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>65</v>
@@ -4943,10 +4925,10 @@
         <v>25</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>65</v>
@@ -4960,7 +4942,7 @@
         <v>25</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C145" s="1" t="n">
         <v>139</v>
@@ -4977,7 +4959,7 @@
         <v>25</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C146" s="1" t="n">
         <v>139</v>
@@ -4994,10 +4976,10 @@
         <v>25</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>65</v>
@@ -5011,16 +4993,16 @@
         <v>25</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5028,16 +5010,16 @@
         <v>25</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5045,16 +5027,16 @@
         <v>25</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5062,7 +5044,7 @@
         <v>25</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C151" s="1" t="n">
         <v>138</v>
@@ -5079,10 +5061,10 @@
         <v>25</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>65</v>
@@ -5096,10 +5078,10 @@
         <v>25</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>65</v>
@@ -5113,10 +5095,10 @@
         <v>25</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>65</v>
@@ -5130,7 +5112,7 @@
         <v>25</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C155" s="1" t="n">
         <v>137</v>
@@ -5147,7 +5129,7 @@
         <v>25</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>137</v>
@@ -5164,10 +5146,10 @@
         <v>25</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>65</v>
@@ -5177,63 +5159,54 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="9" t="s">
-        <v>35</v>
+      <c r="A158" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E158" s="1" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="9" t="s">
-        <v>35</v>
+      <c r="A159" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E159" s="1" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="9" t="s">
-        <v>35</v>
+      <c r="A160" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E160" s="1" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,7 +5214,7 @@
         <v>35</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C161" s="1" t="n">
         <v>95</v>
@@ -5250,18 +5223,18 @@
         <v>70</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="6" t="s">
-        <v>36</v>
+      <c r="A162" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" s="1" t="n">
         <v>95</v>
@@ -5270,18 +5243,18 @@
         <v>70</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="6" t="s">
-        <v>36</v>
+      <c r="A163" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163" s="1" t="n">
         <v>95</v>
@@ -5290,18 +5263,18 @@
         <v>70</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="6" t="s">
-        <v>36</v>
+      <c r="A164" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C164" s="1" t="n">
         <v>95</v>
@@ -5310,7 +5283,7 @@
         <v>70</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>54</v>
@@ -5321,7 +5294,7 @@
         <v>36</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C165" s="1" t="n">
         <v>95</v>
@@ -5330,7 +5303,7 @@
         <v>70</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>54</v>
@@ -5341,16 +5314,16 @@
         <v>36</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>70</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>54</v>
@@ -5361,10 +5334,10 @@
         <v>36</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>70</v>
@@ -5378,10 +5351,10 @@
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C168" s="1" t="n">
         <v>95</v>
@@ -5389,22 +5362,28 @@
       <c r="D168" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E168" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F168" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D169" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>54</v>
@@ -5412,16 +5391,19 @@
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E170" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>54</v>
@@ -5432,7 +5414,7 @@
         <v>37</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C171" s="1" t="n">
         <v>95</v>
@@ -5449,10 +5431,10 @@
         <v>37</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>70</v>
@@ -5466,10 +5448,10 @@
         <v>37</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D173" s="1" t="n">
         <v>70</v>
@@ -5483,10 +5465,10 @@
         <v>37</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D174" s="1" t="n">
         <v>70</v>
@@ -5500,7 +5482,7 @@
         <v>37</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C175" s="1" t="n">
         <v>94</v>
@@ -5517,7 +5499,7 @@
         <v>37</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C176" s="1" t="n">
         <v>94</v>
@@ -5534,7 +5516,7 @@
         <v>37</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C177" s="1" t="n">
         <v>94</v>
@@ -5551,7 +5533,7 @@
         <v>37</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C178" s="1" t="n">
         <v>94</v>
@@ -5568,7 +5550,7 @@
         <v>37</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C179" s="1" t="n">
         <v>94</v>
@@ -5585,7 +5567,7 @@
         <v>37</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C180" s="1" t="n">
         <v>94</v>
@@ -5602,7 +5584,7 @@
         <v>37</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C181" s="1" t="n">
         <v>94</v>
@@ -5619,7 +5601,7 @@
         <v>37</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C182" s="1" t="n">
         <v>94</v>
@@ -5636,16 +5618,16 @@
         <v>37</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D183" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5653,16 +5635,16 @@
         <v>37</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D184" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5670,16 +5652,16 @@
         <v>37</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D185" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,7 +5669,7 @@
         <v>37</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C186" s="1" t="n">
         <v>93</v>
@@ -5704,10 +5686,10 @@
         <v>37</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D187" s="1" t="n">
         <v>70</v>
@@ -5721,10 +5703,10 @@
         <v>37</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D188" s="1" t="n">
         <v>70</v>
@@ -5738,10 +5720,10 @@
         <v>37</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D189" s="1" t="n">
         <v>70</v>
@@ -5755,7 +5737,7 @@
         <v>37</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C190" s="1" t="n">
         <v>92</v>
@@ -5772,7 +5754,7 @@
         <v>37</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C191" s="1" t="n">
         <v>92</v>
@@ -5789,10 +5771,10 @@
         <v>37</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D192" s="1" t="n">
         <v>70</v>
@@ -5806,10 +5788,10 @@
         <v>37</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D193" s="1" t="n">
         <v>70</v>
@@ -5823,10 +5805,10 @@
         <v>37</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D194" s="1" t="n">
         <v>70</v>
@@ -5840,7 +5822,7 @@
         <v>37</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C195" s="1" t="n">
         <v>91</v>
@@ -5857,7 +5839,7 @@
         <v>37</v>
       </c>
       <c r="B196" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C196" s="1" t="n">
         <v>91</v>
@@ -5874,7 +5856,7 @@
         <v>37</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C197" s="1" t="n">
         <v>91</v>
@@ -5891,16 +5873,16 @@
         <v>37</v>
       </c>
       <c r="B198" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D198" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5908,16 +5890,16 @@
         <v>37</v>
       </c>
       <c r="B199" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D199" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5925,16 +5907,16 @@
         <v>37</v>
       </c>
       <c r="B200" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D200" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5942,7 +5924,7 @@
         <v>37</v>
       </c>
       <c r="B201" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C201" s="1" t="n">
         <v>89</v>
@@ -5959,7 +5941,7 @@
         <v>37</v>
       </c>
       <c r="B202" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C202" s="1" t="n">
         <v>89</v>
@@ -5976,7 +5958,7 @@
         <v>37</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C203" s="1" t="n">
         <v>89</v>
@@ -5993,7 +5975,7 @@
         <v>37</v>
       </c>
       <c r="B204" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C204" s="1" t="n">
         <v>89</v>
@@ -6010,10 +5992,10 @@
         <v>37</v>
       </c>
       <c r="B205" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D205" s="1" t="n">
         <v>70</v>
@@ -6027,10 +6009,10 @@
         <v>37</v>
       </c>
       <c r="B206" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D206" s="1" t="n">
         <v>70</v>
@@ -6044,10 +6026,10 @@
         <v>37</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D207" s="1" t="n">
         <v>70</v>
@@ -6061,7 +6043,7 @@
         <v>37</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C208" s="1" t="n">
         <v>88</v>
@@ -6078,7 +6060,7 @@
         <v>37</v>
       </c>
       <c r="B209" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C209" s="1" t="n">
         <v>88</v>
@@ -6095,7 +6077,7 @@
         <v>37</v>
       </c>
       <c r="B210" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C210" s="1" t="n">
         <v>88</v>
@@ -6112,7 +6094,7 @@
         <v>37</v>
       </c>
       <c r="B211" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C211" s="1" t="n">
         <v>88</v>
@@ -6129,7 +6111,7 @@
         <v>37</v>
       </c>
       <c r="B212" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C212" s="1" t="n">
         <v>88</v>
@@ -6143,62 +6125,53 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B213" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D213" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E213" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F213" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B214" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D214" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E214" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F214" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B215" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D215" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E215" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="F215" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6206,7 +6179,7 @@
         <v>42</v>
       </c>
       <c r="B216" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C216" s="1" t="n">
         <v>95</v>
@@ -6215,7 +6188,7 @@
         <v>70</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>54</v>
@@ -6223,10 +6196,10 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B217" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="1" t="n">
         <v>95</v>
@@ -6234,16 +6207,19 @@
       <c r="D217" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E217" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="F217" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B218" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C218" s="1" t="n">
         <v>95</v>
@@ -6251,22 +6227,28 @@
       <c r="D218" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E218" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F218" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B219" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C219" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D219" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E219" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F219" s="6" t="s">
         <v>54</v>
@@ -6277,7 +6259,7 @@
         <v>43</v>
       </c>
       <c r="B220" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C220" s="1" t="n">
         <v>95</v>
@@ -6294,10 +6276,10 @@
         <v>43</v>
       </c>
       <c r="B221" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D221" s="1" t="n">
         <v>70</v>
@@ -6311,10 +6293,10 @@
         <v>43</v>
       </c>
       <c r="B222" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D222" s="1" t="n">
         <v>70</v>
@@ -6328,10 +6310,10 @@
         <v>43</v>
       </c>
       <c r="B223" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D223" s="1" t="n">
         <v>70</v>
@@ -6345,7 +6327,7 @@
         <v>43</v>
       </c>
       <c r="B224" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C224" s="1" t="n">
         <v>94</v>
@@ -6362,7 +6344,7 @@
         <v>43</v>
       </c>
       <c r="B225" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C225" s="1" t="n">
         <v>94</v>
@@ -6379,7 +6361,7 @@
         <v>43</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C226" s="1" t="n">
         <v>94</v>
@@ -6396,7 +6378,7 @@
         <v>43</v>
       </c>
       <c r="B227" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C227" s="1" t="n">
         <v>94</v>
@@ -6413,7 +6395,7 @@
         <v>43</v>
       </c>
       <c r="B228" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C228" s="1" t="n">
         <v>94</v>
@@ -6430,7 +6412,7 @@
         <v>43</v>
       </c>
       <c r="B229" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C229" s="1" t="n">
         <v>94</v>
@@ -6447,7 +6429,7 @@
         <v>43</v>
       </c>
       <c r="B230" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C230" s="1" t="n">
         <v>94</v>
@@ -6464,7 +6446,7 @@
         <v>43</v>
       </c>
       <c r="B231" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C231" s="1" t="n">
         <v>94</v>
@@ -6481,16 +6463,16 @@
         <v>43</v>
       </c>
       <c r="B232" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D232" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6498,16 +6480,16 @@
         <v>43</v>
       </c>
       <c r="B233" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D233" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6515,16 +6497,16 @@
         <v>43</v>
       </c>
       <c r="B234" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D234" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6532,7 +6514,7 @@
         <v>43</v>
       </c>
       <c r="B235" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C235" s="1" t="n">
         <v>93</v>
@@ -6549,10 +6531,10 @@
         <v>43</v>
       </c>
       <c r="B236" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D236" s="1" t="n">
         <v>70</v>
@@ -6566,10 +6548,10 @@
         <v>43</v>
       </c>
       <c r="B237" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D237" s="1" t="n">
         <v>70</v>
@@ -6583,10 +6565,10 @@
         <v>43</v>
       </c>
       <c r="B238" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D238" s="1" t="n">
         <v>70</v>
@@ -6600,7 +6582,7 @@
         <v>43</v>
       </c>
       <c r="B239" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C239" s="1" t="n">
         <v>92</v>
@@ -6617,7 +6599,7 @@
         <v>43</v>
       </c>
       <c r="B240" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C240" s="1" t="n">
         <v>92</v>
@@ -6634,10 +6616,10 @@
         <v>43</v>
       </c>
       <c r="B241" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D241" s="1" t="n">
         <v>70</v>
@@ -6651,10 +6633,10 @@
         <v>43</v>
       </c>
       <c r="B242" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D242" s="1" t="n">
         <v>70</v>
@@ -6668,10 +6650,10 @@
         <v>43</v>
       </c>
       <c r="B243" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D243" s="1" t="n">
         <v>70</v>
@@ -6685,7 +6667,7 @@
         <v>43</v>
       </c>
       <c r="B244" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C244" s="1" t="n">
         <v>91</v>
@@ -6702,7 +6684,7 @@
         <v>43</v>
       </c>
       <c r="B245" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C245" s="1" t="n">
         <v>91</v>
@@ -6719,7 +6701,7 @@
         <v>43</v>
       </c>
       <c r="B246" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C246" s="1" t="n">
         <v>91</v>
@@ -6736,16 +6718,16 @@
         <v>43</v>
       </c>
       <c r="B247" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D247" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6753,16 +6735,16 @@
         <v>43</v>
       </c>
       <c r="B248" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D248" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6770,16 +6752,16 @@
         <v>43</v>
       </c>
       <c r="B249" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D249" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6787,7 +6769,7 @@
         <v>43</v>
       </c>
       <c r="B250" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C250" s="1" t="n">
         <v>89</v>
@@ -6804,7 +6786,7 @@
         <v>43</v>
       </c>
       <c r="B251" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C251" s="1" t="n">
         <v>89</v>
@@ -6821,7 +6803,7 @@
         <v>43</v>
       </c>
       <c r="B252" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C252" s="1" t="n">
         <v>89</v>
@@ -6838,7 +6820,7 @@
         <v>43</v>
       </c>
       <c r="B253" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C253" s="1" t="n">
         <v>89</v>
@@ -6855,10 +6837,10 @@
         <v>43</v>
       </c>
       <c r="B254" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D254" s="1" t="n">
         <v>70</v>
@@ -6872,10 +6854,10 @@
         <v>43</v>
       </c>
       <c r="B255" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D255" s="1" t="n">
         <v>70</v>
@@ -6889,10 +6871,10 @@
         <v>43</v>
       </c>
       <c r="B256" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D256" s="1" t="n">
         <v>70</v>
@@ -6906,7 +6888,7 @@
         <v>43</v>
       </c>
       <c r="B257" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C257" s="1" t="n">
         <v>88</v>
@@ -6923,7 +6905,7 @@
         <v>43</v>
       </c>
       <c r="B258" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C258" s="1" t="n">
         <v>88</v>
@@ -6940,7 +6922,7 @@
         <v>43</v>
       </c>
       <c r="B259" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C259" s="1" t="n">
         <v>88</v>
@@ -6957,7 +6939,7 @@
         <v>43</v>
       </c>
       <c r="B260" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C260" s="1" t="n">
         <v>88</v>
@@ -6974,7 +6956,7 @@
         <v>43</v>
       </c>
       <c r="B261" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C261" s="1" t="n">
         <v>88</v>
@@ -6988,62 +6970,53 @@
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B262" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D262" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E262" s="1" t="n">
-        <v>50</v>
-      </c>
       <c r="F262" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B263" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D263" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E263" s="1" t="n">
-        <v>50</v>
-      </c>
       <c r="F263" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B264" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D264" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E264" s="1" t="n">
-        <v>40</v>
-      </c>
       <c r="F264" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7051,7 +7024,7 @@
         <v>39</v>
       </c>
       <c r="B265" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C265" s="1" t="n">
         <v>95</v>
@@ -7060,7 +7033,7 @@
         <v>70</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>54</v>
@@ -7068,19 +7041,19 @@
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B266" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>54</v>
@@ -7088,19 +7061,19 @@
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B267" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C267" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D267" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F267" s="6" t="s">
         <v>54</v>
@@ -7108,19 +7081,19 @@
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B268" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C268" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D268" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>54</v>
@@ -7131,7 +7104,7 @@
         <v>40</v>
       </c>
       <c r="B269" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C269" s="1" t="n">
         <v>95</v>
@@ -7140,7 +7113,7 @@
         <v>65</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F269" s="6" t="s">
         <v>54</v>
@@ -7151,16 +7124,16 @@
         <v>40</v>
       </c>
       <c r="B270" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D270" s="1" t="n">
         <v>65</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>54</v>
@@ -7171,10 +7144,10 @@
         <v>40</v>
       </c>
       <c r="B271" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D271" s="1" t="n">
         <v>65</v>
@@ -7191,10 +7164,10 @@
         <v>40</v>
       </c>
       <c r="B272" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D272" s="1" t="n">
         <v>65</v>
@@ -7211,7 +7184,7 @@
         <v>40</v>
       </c>
       <c r="B273" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C273" s="1" t="n">
         <v>94</v>
@@ -7228,50 +7201,59 @@
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B274" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D274" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E274" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F274" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B275" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D275" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E275" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F275" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B276" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D276" s="1" t="n">
         <v>65</v>
+      </c>
+      <c r="E276" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>54</v>
@@ -7282,7 +7264,7 @@
         <v>41</v>
       </c>
       <c r="B277" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C277" s="1" t="n">
         <v>95</v>
@@ -7299,10 +7281,10 @@
         <v>41</v>
       </c>
       <c r="B278" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D278" s="1" t="n">
         <v>65</v>
@@ -7316,10 +7298,10 @@
         <v>41</v>
       </c>
       <c r="B279" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D279" s="1" t="n">
         <v>65</v>
@@ -7333,10 +7315,10 @@
         <v>41</v>
       </c>
       <c r="B280" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D280" s="1" t="n">
         <v>65</v>
@@ -7350,7 +7332,7 @@
         <v>41</v>
       </c>
       <c r="B281" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C281" s="1" t="n">
         <v>94</v>
@@ -7367,7 +7349,7 @@
         <v>41</v>
       </c>
       <c r="B282" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C282" s="1" t="n">
         <v>94</v>
@@ -7384,7 +7366,7 @@
         <v>41</v>
       </c>
       <c r="B283" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C283" s="1" t="n">
         <v>94</v>
@@ -7401,7 +7383,7 @@
         <v>41</v>
       </c>
       <c r="B284" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C284" s="1" t="n">
         <v>94</v>
@@ -7418,7 +7400,7 @@
         <v>41</v>
       </c>
       <c r="B285" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C285" s="1" t="n">
         <v>94</v>
@@ -7435,7 +7417,7 @@
         <v>41</v>
       </c>
       <c r="B286" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C286" s="1" t="n">
         <v>94</v>
@@ -7452,7 +7434,7 @@
         <v>41</v>
       </c>
       <c r="B287" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C287" s="1" t="n">
         <v>94</v>
@@ -7469,7 +7451,7 @@
         <v>41</v>
       </c>
       <c r="B288" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C288" s="1" t="n">
         <v>94</v>
@@ -7486,16 +7468,16 @@
         <v>41</v>
       </c>
       <c r="B289" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D289" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7503,16 +7485,16 @@
         <v>41</v>
       </c>
       <c r="B290" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D290" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F290" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7520,16 +7502,16 @@
         <v>41</v>
       </c>
       <c r="B291" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D291" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7537,7 +7519,7 @@
         <v>41</v>
       </c>
       <c r="B292" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C292" s="1" t="n">
         <v>93</v>
@@ -7554,10 +7536,10 @@
         <v>41</v>
       </c>
       <c r="B293" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D293" s="1" t="n">
         <v>65</v>
@@ -7571,10 +7553,10 @@
         <v>41</v>
       </c>
       <c r="B294" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D294" s="1" t="n">
         <v>65</v>
@@ -7588,10 +7570,10 @@
         <v>41</v>
       </c>
       <c r="B295" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D295" s="1" t="n">
         <v>65</v>
@@ -7605,7 +7587,7 @@
         <v>41</v>
       </c>
       <c r="B296" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C296" s="1" t="n">
         <v>92</v>
@@ -7622,7 +7604,7 @@
         <v>41</v>
       </c>
       <c r="B297" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C297" s="1" t="n">
         <v>92</v>
@@ -7639,10 +7621,10 @@
         <v>41</v>
       </c>
       <c r="B298" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D298" s="1" t="n">
         <v>65</v>
@@ -7656,10 +7638,10 @@
         <v>41</v>
       </c>
       <c r="B299" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D299" s="1" t="n">
         <v>65</v>
@@ -7673,10 +7655,10 @@
         <v>41</v>
       </c>
       <c r="B300" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D300" s="1" t="n">
         <v>65</v>
@@ -7690,7 +7672,7 @@
         <v>41</v>
       </c>
       <c r="B301" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C301" s="1" t="n">
         <v>91</v>
@@ -7707,7 +7689,7 @@
         <v>41</v>
       </c>
       <c r="B302" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C302" s="1" t="n">
         <v>91</v>
@@ -7724,7 +7706,7 @@
         <v>41</v>
       </c>
       <c r="B303" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C303" s="1" t="n">
         <v>91</v>
@@ -7741,16 +7723,16 @@
         <v>41</v>
       </c>
       <c r="B304" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D304" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F304" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7758,16 +7740,16 @@
         <v>41</v>
       </c>
       <c r="B305" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D305" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F305" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7775,16 +7757,16 @@
         <v>41</v>
       </c>
       <c r="B306" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D306" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F306" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7792,7 +7774,7 @@
         <v>41</v>
       </c>
       <c r="B307" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C307" s="1" t="n">
         <v>89</v>
@@ -7809,7 +7791,7 @@
         <v>41</v>
       </c>
       <c r="B308" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C308" s="1" t="n">
         <v>89</v>
@@ -7826,7 +7808,7 @@
         <v>41</v>
       </c>
       <c r="B309" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C309" s="1" t="n">
         <v>89</v>
@@ -7843,7 +7825,7 @@
         <v>41</v>
       </c>
       <c r="B310" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C310" s="1" t="n">
         <v>89</v>
@@ -7860,10 +7842,10 @@
         <v>41</v>
       </c>
       <c r="B311" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D311" s="1" t="n">
         <v>65</v>
@@ -7877,10 +7859,10 @@
         <v>41</v>
       </c>
       <c r="B312" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D312" s="1" t="n">
         <v>65</v>
@@ -7894,10 +7876,10 @@
         <v>41</v>
       </c>
       <c r="B313" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D313" s="1" t="n">
         <v>65</v>
@@ -7911,7 +7893,7 @@
         <v>41</v>
       </c>
       <c r="B314" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C314" s="1" t="n">
         <v>88</v>
@@ -7928,7 +7910,7 @@
         <v>41</v>
       </c>
       <c r="B315" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C315" s="1" t="n">
         <v>88</v>
@@ -7945,7 +7927,7 @@
         <v>41</v>
       </c>
       <c r="B316" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C316" s="1" t="n">
         <v>88</v>
@@ -7962,7 +7944,7 @@
         <v>41</v>
       </c>
       <c r="B317" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C317" s="1" t="n">
         <v>88</v>
@@ -7979,7 +7961,7 @@
         <v>41</v>
       </c>
       <c r="B318" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C318" s="1" t="n">
         <v>88</v>
@@ -7993,44 +7975,53 @@
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B319" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B320" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
+      </c>
+      <c r="F320" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B321" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="F321" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8038,13 +8029,13 @@
         <v>32</v>
       </c>
       <c r="B322" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C322" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8052,13 +8043,13 @@
         <v>32</v>
       </c>
       <c r="B323" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C323" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8066,13 +8057,13 @@
         <v>32</v>
       </c>
       <c r="B324" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C324" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8080,13 +8071,13 @@
         <v>32</v>
       </c>
       <c r="B325" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C325" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8094,13 +8085,13 @@
         <v>32</v>
       </c>
       <c r="B326" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8108,13 +8099,13 @@
         <v>32</v>
       </c>
       <c r="B327" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8122,13 +8113,13 @@
         <v>32</v>
       </c>
       <c r="B328" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8136,7 +8127,7 @@
         <v>32</v>
       </c>
       <c r="B329" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C329" s="1" t="n">
         <v>48</v>
@@ -8150,7 +8141,7 @@
         <v>32</v>
       </c>
       <c r="B330" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C330" s="1" t="n">
         <v>48</v>
@@ -8161,44 +8152,44 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B331" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B332" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B333" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8206,13 +8197,13 @@
         <v>33</v>
       </c>
       <c r="B334" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C334" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8220,13 +8211,13 @@
         <v>33</v>
       </c>
       <c r="B335" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C335" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8234,13 +8225,13 @@
         <v>33</v>
       </c>
       <c r="B336" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C336" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8248,13 +8239,13 @@
         <v>33</v>
       </c>
       <c r="B337" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C337" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8262,13 +8253,13 @@
         <v>33</v>
       </c>
       <c r="B338" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8276,13 +8267,13 @@
         <v>33</v>
       </c>
       <c r="B339" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8290,13 +8281,13 @@
         <v>33</v>
       </c>
       <c r="B340" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8304,7 +8295,7 @@
         <v>33</v>
       </c>
       <c r="B341" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C341" s="1" t="n">
         <v>48</v>
@@ -8318,7 +8309,7 @@
         <v>33</v>
       </c>
       <c r="B342" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C342" s="1" t="n">
         <v>48</v>
@@ -8332,7 +8323,7 @@
         <v>33</v>
       </c>
       <c r="B343" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C343" s="1" t="n">
         <v>48</v>
@@ -8346,7 +8337,7 @@
         <v>33</v>
       </c>
       <c r="B344" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C344" s="1" t="n">
         <v>48</v>
@@ -8360,7 +8351,7 @@
         <v>33</v>
       </c>
       <c r="B345" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C345" s="1" t="n">
         <v>48</v>
@@ -8371,44 +8362,44 @@
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="6" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B346" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D346" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B347" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D347" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="6" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B348" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,13 +8407,13 @@
         <v>57</v>
       </c>
       <c r="B349" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C349" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8430,13 +8421,13 @@
         <v>57</v>
       </c>
       <c r="B350" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C350" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8444,13 +8435,13 @@
         <v>57</v>
       </c>
       <c r="B351" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C351" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8458,13 +8449,13 @@
         <v>57</v>
       </c>
       <c r="B352" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C352" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8472,55 +8463,55 @@
         <v>57</v>
       </c>
       <c r="B353" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="6" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B354" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C354" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="6" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B355" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C355" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B356" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8528,13 +8519,13 @@
         <v>34</v>
       </c>
       <c r="B357" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C357" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8542,13 +8533,13 @@
         <v>34</v>
       </c>
       <c r="B358" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C358" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8556,13 +8547,13 @@
         <v>34</v>
       </c>
       <c r="B359" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C359" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8570,13 +8561,13 @@
         <v>34</v>
       </c>
       <c r="B360" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C360" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8584,24 +8575,24 @@
         <v>34</v>
       </c>
       <c r="B361" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B362" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D362" s="1" t="n">
         <v>90</v>
@@ -8609,13 +8600,13 @@
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B363" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D363" s="1" t="n">
         <v>90</v>
@@ -8623,16 +8614,16 @@
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B364" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8640,7 +8631,7 @@
         <v>45</v>
       </c>
       <c r="B365" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C365" s="1" t="n">
         <v>45</v>
@@ -8654,13 +8645,13 @@
         <v>45</v>
       </c>
       <c r="B366" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C366" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D366" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8668,13 +8659,13 @@
         <v>45</v>
       </c>
       <c r="B367" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C367" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8682,13 +8673,13 @@
         <v>45</v>
       </c>
       <c r="B368" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C368" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D368" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8696,13 +8687,13 @@
         <v>45</v>
       </c>
       <c r="B369" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8710,13 +8701,13 @@
         <v>45</v>
       </c>
       <c r="B370" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8724,13 +8715,13 @@
         <v>45</v>
       </c>
       <c r="B371" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8738,7 +8729,7 @@
         <v>45</v>
       </c>
       <c r="B372" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C372" s="1" t="n">
         <v>44</v>
@@ -8752,7 +8743,7 @@
         <v>45</v>
       </c>
       <c r="B373" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C373" s="1" t="n">
         <v>44</v>
@@ -8766,7 +8757,7 @@
         <v>45</v>
       </c>
       <c r="B374" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C374" s="1" t="n">
         <v>44</v>
@@ -8780,7 +8771,7 @@
         <v>45</v>
       </c>
       <c r="B375" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C375" s="1" t="n">
         <v>44</v>
@@ -8791,44 +8782,44 @@
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B376" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D376" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B377" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D377" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B378" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8836,7 +8827,7 @@
         <v>46</v>
       </c>
       <c r="B379" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C379" s="1" t="n">
         <v>45</v>
@@ -8850,13 +8841,13 @@
         <v>46</v>
       </c>
       <c r="B380" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C380" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8864,13 +8855,13 @@
         <v>46</v>
       </c>
       <c r="B381" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C381" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8878,13 +8869,13 @@
         <v>46</v>
       </c>
       <c r="B382" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C382" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8892,13 +8883,13 @@
         <v>46</v>
       </c>
       <c r="B383" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8906,13 +8897,13 @@
         <v>46</v>
       </c>
       <c r="B384" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8920,13 +8911,13 @@
         <v>46</v>
       </c>
       <c r="B385" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8934,7 +8925,7 @@
         <v>46</v>
       </c>
       <c r="B386" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C386" s="1" t="n">
         <v>44</v>
@@ -8948,7 +8939,7 @@
         <v>46</v>
       </c>
       <c r="B387" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C387" s="1" t="n">
         <v>44</v>
@@ -8962,7 +8953,7 @@
         <v>46</v>
       </c>
       <c r="B388" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C388" s="1" t="n">
         <v>44</v>
@@ -8976,7 +8967,7 @@
         <v>46</v>
       </c>
       <c r="B389" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C389" s="1" t="n">
         <v>44</v>
@@ -8990,7 +8981,7 @@
         <v>46</v>
       </c>
       <c r="B390" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C390" s="1" t="n">
         <v>44</v>
@@ -9001,44 +8992,44 @@
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B391" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D391" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B392" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D392" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B393" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D393" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9046,7 +9037,7 @@
         <v>47</v>
       </c>
       <c r="B394" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C394" s="1" t="n">
         <v>45</v>
@@ -9060,13 +9051,13 @@
         <v>47</v>
       </c>
       <c r="B395" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C395" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D395" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9074,13 +9065,13 @@
         <v>47</v>
       </c>
       <c r="B396" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C396" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D396" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9088,13 +9079,13 @@
         <v>47</v>
       </c>
       <c r="B397" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C397" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D397" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9102,69 +9093,69 @@
         <v>47</v>
       </c>
       <c r="B398" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B399" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C399" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B400" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C400" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B401" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C401" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B401" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C401" s="1" t="n">
-        <v>45</v>
-      </c>
       <c r="D401" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B402" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C402" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B402" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C402" s="1" t="n">
-        <v>45</v>
-      </c>
       <c r="D402" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9172,13 +9163,13 @@
         <v>44</v>
       </c>
       <c r="B403" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C403" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9186,13 +9177,13 @@
         <v>44</v>
       </c>
       <c r="B404" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C404" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9200,13 +9191,13 @@
         <v>44</v>
       </c>
       <c r="B405" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C405" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D405" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9214,83 +9205,83 @@
         <v>44</v>
       </c>
       <c r="B406" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D406" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B407" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C407" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B408" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C408" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B409" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C409" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B410" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B411" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9298,13 +9289,13 @@
         <v>48</v>
       </c>
       <c r="B412" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C412" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9312,13 +9303,13 @@
         <v>48</v>
       </c>
       <c r="B413" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C413" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9326,98 +9317,97 @@
         <v>48</v>
       </c>
       <c r="B414" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B415" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F415" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M415" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="D415" s="1" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B416" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F416" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B417" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F417" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="D417" s="1" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B418" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F418" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="D418" s="1" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B419" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F419" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
+      </c>
+      <c r="D419" s="1" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B420" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="F420" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
+      </c>
+      <c r="D420" s="1" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,24 +9415,25 @@
         <v>49</v>
       </c>
       <c r="B421" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F421" s="6" t="s">
         <v>54</v>
       </c>
+      <c r="M421" s="11"/>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B422" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F422" s="6" t="s">
         <v>54</v>
@@ -9453,10 +9444,10 @@
         <v>49</v>
       </c>
       <c r="B423" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F423" s="6" t="s">
         <v>54</v>
@@ -9467,10 +9458,10 @@
         <v>49</v>
       </c>
       <c r="B424" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F424" s="6" t="s">
         <v>54</v>
@@ -9481,7 +9472,7 @@
         <v>49</v>
       </c>
       <c r="B425" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C425" s="1" t="n">
         <v>94</v>
@@ -9495,7 +9486,7 @@
         <v>49</v>
       </c>
       <c r="B426" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C426" s="1" t="n">
         <v>94</v>
@@ -9509,7 +9500,7 @@
         <v>49</v>
       </c>
       <c r="B427" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C427" s="1" t="n">
         <v>94</v>
@@ -9523,7 +9514,7 @@
         <v>49</v>
       </c>
       <c r="B428" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C428" s="1" t="n">
         <v>94</v>
@@ -9537,7 +9528,7 @@
         <v>49</v>
       </c>
       <c r="B429" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C429" s="1" t="n">
         <v>94</v>
@@ -9551,13 +9542,13 @@
         <v>49</v>
       </c>
       <c r="B430" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F430" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9565,13 +9556,13 @@
         <v>49</v>
       </c>
       <c r="B431" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F431" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,13 +9570,13 @@
         <v>49</v>
       </c>
       <c r="B432" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F432" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9593,13 +9584,13 @@
         <v>49</v>
       </c>
       <c r="B433" s="1" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F433" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9607,13 +9598,13 @@
         <v>49</v>
       </c>
       <c r="B434" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F434" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9621,13 +9612,13 @@
         <v>49</v>
       </c>
       <c r="B435" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F435" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9635,10 +9626,10 @@
         <v>49</v>
       </c>
       <c r="B436" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F436" s="6" t="s">
         <v>56</v>
@@ -9649,10 +9640,10 @@
         <v>49</v>
       </c>
       <c r="B437" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F437" s="6" t="s">
         <v>56</v>
@@ -9663,10 +9654,10 @@
         <v>49</v>
       </c>
       <c r="B438" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F438" s="6" t="s">
         <v>56</v>
@@ -9677,10 +9668,10 @@
         <v>49</v>
       </c>
       <c r="B439" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F439" s="6" t="s">
         <v>56</v>
@@ -9691,10 +9682,10 @@
         <v>49</v>
       </c>
       <c r="B440" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F440" s="6" t="s">
         <v>56</v>
@@ -9705,10 +9696,10 @@
         <v>49</v>
       </c>
       <c r="B441" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F441" s="6" t="s">
         <v>56</v>
@@ -9719,10 +9710,10 @@
         <v>49</v>
       </c>
       <c r="B442" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F442" s="6" t="s">
         <v>56</v>
@@ -9733,10 +9724,10 @@
         <v>49</v>
       </c>
       <c r="B443" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F443" s="6" t="s">
         <v>56</v>
@@ -9747,10 +9738,10 @@
         <v>49</v>
       </c>
       <c r="B444" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F444" s="6" t="s">
         <v>56</v>
@@ -9761,13 +9752,13 @@
         <v>49</v>
       </c>
       <c r="B445" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F445" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9775,13 +9766,13 @@
         <v>49</v>
       </c>
       <c r="B446" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F446" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9789,13 +9780,13 @@
         <v>49</v>
       </c>
       <c r="B447" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F447" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9803,13 +9794,13 @@
         <v>49</v>
       </c>
       <c r="B448" s="1" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F448" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9817,13 +9808,13 @@
         <v>49</v>
       </c>
       <c r="B449" s="1" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9831,13 +9822,13 @@
         <v>49</v>
       </c>
       <c r="B450" s="1" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F450" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9845,7 +9836,7 @@
         <v>49</v>
       </c>
       <c r="B451" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C451" s="1" t="n">
         <v>89</v>
@@ -9859,10 +9850,10 @@
         <v>49</v>
       </c>
       <c r="B452" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F452" s="6" t="s">
         <v>55</v>
@@ -9873,10 +9864,10 @@
         <v>49</v>
       </c>
       <c r="B453" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F453" s="6" t="s">
         <v>55</v>
@@ -9887,10 +9878,10 @@
         <v>49</v>
       </c>
       <c r="B454" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F454" s="6" t="s">
         <v>55</v>
@@ -9901,10 +9892,10 @@
         <v>49</v>
       </c>
       <c r="B455" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F455" s="6" t="s">
         <v>55</v>
@@ -9915,10 +9906,10 @@
         <v>49</v>
       </c>
       <c r="B456" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F456" s="6" t="s">
         <v>55</v>
@@ -9929,10 +9920,10 @@
         <v>49</v>
       </c>
       <c r="B457" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F457" s="6" t="s">
         <v>55</v>
@@ -9943,7 +9934,7 @@
         <v>49</v>
       </c>
       <c r="B458" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C458" s="1" t="n">
         <v>88</v>
@@ -9957,12 +9948,96 @@
         <v>49</v>
       </c>
       <c r="B459" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C459" s="1" t="n">
         <v>88</v>
       </c>
       <c r="F459" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B460" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F460" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B461" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C461" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F461" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B462" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C462" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F462" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B463" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C463" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F463" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A464" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B464" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C464" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F464" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A465" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B465" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C465" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F465" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10580,10 +10655,10 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="13.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="30.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="120">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -174,7 +174,10 @@
     <t xml:space="preserve">Kaloriferc</t>
   </si>
   <si>
-    <t xml:space="preserve">Vekil</t>
+    <t xml:space="preserve">Vekil İ-H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vekil M-K</t>
   </si>
   <si>
     <t xml:space="preserve">oht_orani</t>
@@ -2602,8 +2605,15 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="2"/>
@@ -2667,7 +2677,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M465"/>
+  <dimension ref="A1:M510"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.74"/>
@@ -2688,16 +2698,16 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3768,7 +3778,7 @@
         <v>50</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,7 +3798,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3808,7 +3818,7 @@
         <v>40</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3828,7 +3838,7 @@
         <v>40</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3848,7 +3858,7 @@
         <v>40</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3868,7 +3878,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3888,7 +3898,7 @@
         <v>25</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,7 +3918,7 @@
         <v>20</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3928,7 +3938,7 @@
         <v>20</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,7 +3958,7 @@
         <v>20</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3965,7 +3975,7 @@
         <v>66</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3982,7 +3992,7 @@
         <v>66</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3999,7 +4009,7 @@
         <v>66</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4016,7 +4026,7 @@
         <v>66</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4033,7 +4043,7 @@
         <v>66</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4050,7 +4060,7 @@
         <v>66</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4067,7 +4077,7 @@
         <v>66</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4084,7 +4094,7 @@
         <v>66</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4101,7 +4111,7 @@
         <v>66</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4118,7 +4128,7 @@
         <v>66</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4135,7 +4145,7 @@
         <v>66</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4152,7 +4162,7 @@
         <v>66</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,7 +4179,7 @@
         <v>66</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4186,7 +4196,7 @@
         <v>66</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4203,7 +4213,7 @@
         <v>115</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4220,7 +4230,7 @@
         <v>115</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,7 +4247,7 @@
         <v>105</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4254,7 +4264,7 @@
         <v>105</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4271,7 +4281,7 @@
         <v>95</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4288,7 +4298,7 @@
         <v>95</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4305,7 +4315,7 @@
         <v>95</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4322,7 +4332,7 @@
         <v>90</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4339,7 +4349,7 @@
         <v>90</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4356,7 +4366,7 @@
         <v>90</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4373,7 +4383,7 @@
         <v>115</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4390,7 +4400,7 @@
         <v>115</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4407,7 +4417,7 @@
         <v>105</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4424,7 +4434,7 @@
         <v>105</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4441,7 +4451,7 @@
         <v>95</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4458,7 +4468,7 @@
         <v>95</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4475,7 +4485,7 @@
         <v>95</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4492,7 +4502,7 @@
         <v>90</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4509,7 +4519,7 @@
         <v>90</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4526,7 +4536,7 @@
         <v>90</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4543,7 +4553,7 @@
         <v>115</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4560,7 +4570,7 @@
         <v>115</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4577,7 +4587,7 @@
         <v>105</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4594,7 +4604,7 @@
         <v>105</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4611,7 +4621,7 @@
         <v>95</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4628,7 +4638,7 @@
         <v>95</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4645,7 +4655,7 @@
         <v>95</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4662,7 +4672,7 @@
         <v>90</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4679,7 +4689,7 @@
         <v>90</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4696,7 +4706,7 @@
         <v>90</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4713,7 +4723,7 @@
         <v>115</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4730,7 +4740,7 @@
         <v>115</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4747,7 +4757,7 @@
         <v>105</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4764,7 +4774,7 @@
         <v>105</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4781,7 +4791,7 @@
         <v>95</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4798,7 +4808,7 @@
         <v>95</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4815,7 +4825,7 @@
         <v>95</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,7 +4842,7 @@
         <v>90</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4849,7 +4859,7 @@
         <v>90</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4866,7 +4876,7 @@
         <v>90</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4883,7 +4893,7 @@
         <v>65</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4900,7 +4910,7 @@
         <v>65</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4917,7 +4927,7 @@
         <v>65</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4934,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4951,7 +4961,7 @@
         <v>65</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4968,7 +4978,7 @@
         <v>65</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4985,7 +4995,7 @@
         <v>65</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5002,7 +5012,7 @@
         <v>65</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5019,7 +5029,7 @@
         <v>65</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5036,7 +5046,7 @@
         <v>65</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5053,7 +5063,7 @@
         <v>65</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5070,7 +5080,7 @@
         <v>65</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5087,7 +5097,7 @@
         <v>65</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5104,7 +5114,7 @@
         <v>65</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,7 +5131,7 @@
         <v>65</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5138,7 +5148,7 @@
         <v>65</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5155,7 +5165,7 @@
         <v>65</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5172,7 +5182,7 @@
         <v>65</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,7 +5199,7 @@
         <v>65</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5206,7 +5216,7 @@
         <v>65</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5226,7 +5236,7 @@
         <v>50</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5246,7 +5256,7 @@
         <v>50</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5266,7 +5276,7 @@
         <v>40</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5286,7 +5296,7 @@
         <v>40</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5306,7 +5316,7 @@
         <v>25</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5326,7 +5336,7 @@
         <v>25</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5346,7 +5356,7 @@
         <v>20</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5366,7 +5376,7 @@
         <v>20</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5386,7 +5396,7 @@
         <v>20</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5406,7 +5416,7 @@
         <v>20</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5423,7 +5433,7 @@
         <v>70</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5440,7 +5450,7 @@
         <v>70</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5457,7 +5467,7 @@
         <v>70</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5474,7 +5484,7 @@
         <v>70</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5491,7 +5501,7 @@
         <v>70</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5508,7 +5518,7 @@
         <v>70</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5525,7 +5535,7 @@
         <v>70</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5542,7 +5552,7 @@
         <v>70</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5559,7 +5569,7 @@
         <v>70</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5576,7 +5586,7 @@
         <v>70</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5593,7 +5603,7 @@
         <v>70</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5610,7 +5620,7 @@
         <v>70</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,7 +5637,7 @@
         <v>70</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5644,7 +5654,7 @@
         <v>70</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5661,7 +5671,7 @@
         <v>70</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5678,7 +5688,7 @@
         <v>70</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,7 +5705,7 @@
         <v>70</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5712,7 +5722,7 @@
         <v>70</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5729,7 +5739,7 @@
         <v>70</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5746,7 +5756,7 @@
         <v>70</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5763,7 +5773,7 @@
         <v>70</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5780,7 +5790,7 @@
         <v>70</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5797,7 +5807,7 @@
         <v>70</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5814,7 +5824,7 @@
         <v>70</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5831,7 +5841,7 @@
         <v>70</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5848,7 +5858,7 @@
         <v>70</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5865,7 +5875,7 @@
         <v>70</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5882,7 +5892,7 @@
         <v>70</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5899,7 +5909,7 @@
         <v>70</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5916,7 +5926,7 @@
         <v>70</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5933,7 +5943,7 @@
         <v>70</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5950,7 +5960,7 @@
         <v>70</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5967,7 +5977,7 @@
         <v>70</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5984,7 +5994,7 @@
         <v>70</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6001,7 +6011,7 @@
         <v>70</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6018,7 +6028,7 @@
         <v>70</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6035,7 +6045,7 @@
         <v>70</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6052,7 +6062,7 @@
         <v>70</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6069,7 +6079,7 @@
         <v>70</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6086,7 +6096,7 @@
         <v>70</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6103,7 +6113,7 @@
         <v>70</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6120,7 +6130,7 @@
         <v>70</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6137,7 +6147,7 @@
         <v>70</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6154,7 +6164,7 @@
         <v>70</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6171,7 +6181,7 @@
         <v>70</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6191,7 +6201,7 @@
         <v>25</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6211,7 +6221,7 @@
         <v>25</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6231,7 +6241,7 @@
         <v>20</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,7 +6261,7 @@
         <v>20</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6268,7 +6278,7 @@
         <v>70</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6285,7 +6295,7 @@
         <v>70</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6302,7 +6312,7 @@
         <v>70</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6319,7 +6329,7 @@
         <v>70</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6336,7 +6346,7 @@
         <v>70</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6353,7 +6363,7 @@
         <v>70</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6370,7 +6380,7 @@
         <v>70</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6387,7 +6397,7 @@
         <v>70</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6404,7 +6414,7 @@
         <v>70</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6421,7 +6431,7 @@
         <v>70</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6438,7 +6448,7 @@
         <v>70</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6455,7 +6465,7 @@
         <v>70</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6472,7 +6482,7 @@
         <v>70</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6489,7 +6499,7 @@
         <v>70</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6506,7 +6516,7 @@
         <v>70</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6523,7 +6533,7 @@
         <v>70</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6540,7 +6550,7 @@
         <v>70</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6557,7 +6567,7 @@
         <v>70</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6574,7 +6584,7 @@
         <v>70</v>
       </c>
       <c r="F238" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6591,7 +6601,7 @@
         <v>70</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6608,7 +6618,7 @@
         <v>70</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6625,7 +6635,7 @@
         <v>70</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6642,7 +6652,7 @@
         <v>70</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6659,7 +6669,7 @@
         <v>70</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6676,7 +6686,7 @@
         <v>70</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6693,7 +6703,7 @@
         <v>70</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6710,7 +6720,7 @@
         <v>70</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6727,7 +6737,7 @@
         <v>70</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6744,7 +6754,7 @@
         <v>70</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6761,7 +6771,7 @@
         <v>70</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6778,7 +6788,7 @@
         <v>70</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6795,7 +6805,7 @@
         <v>70</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6812,7 +6822,7 @@
         <v>70</v>
       </c>
       <c r="F252" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6829,7 +6839,7 @@
         <v>70</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6846,7 +6856,7 @@
         <v>70</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6863,7 +6873,7 @@
         <v>70</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6880,7 +6890,7 @@
         <v>70</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6897,7 +6907,7 @@
         <v>70</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6914,7 +6924,7 @@
         <v>70</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6931,7 +6941,7 @@
         <v>70</v>
       </c>
       <c r="F259" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6948,7 +6958,7 @@
         <v>70</v>
       </c>
       <c r="F260" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6965,7 +6975,7 @@
         <v>70</v>
       </c>
       <c r="F261" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6982,7 +6992,7 @@
         <v>70</v>
       </c>
       <c r="F262" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6999,7 +7009,7 @@
         <v>70</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7016,7 +7026,7 @@
         <v>70</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7036,7 +7046,7 @@
         <v>50</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7056,7 +7066,7 @@
         <v>50</v>
       </c>
       <c r="F266" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7076,7 +7086,7 @@
         <v>40</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7096,7 +7106,7 @@
         <v>40</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7116,7 +7126,7 @@
         <v>25</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7136,7 +7146,7 @@
         <v>25</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7156,7 +7166,7 @@
         <v>20</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7176,7 +7186,7 @@
         <v>20</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7196,7 +7206,7 @@
         <v>20</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7216,7 +7226,7 @@
         <v>20</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7236,7 +7246,7 @@
         <v>20</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7256,7 +7266,7 @@
         <v>20</v>
       </c>
       <c r="F276" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7273,7 +7283,7 @@
         <v>65</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7290,7 +7300,7 @@
         <v>65</v>
       </c>
       <c r="F278" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7307,7 +7317,7 @@
         <v>65</v>
       </c>
       <c r="F279" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7324,7 +7334,7 @@
         <v>65</v>
       </c>
       <c r="F280" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,7 +7351,7 @@
         <v>65</v>
       </c>
       <c r="F281" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7358,7 +7368,7 @@
         <v>65</v>
       </c>
       <c r="F282" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7375,7 +7385,7 @@
         <v>65</v>
       </c>
       <c r="F283" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7392,7 +7402,7 @@
         <v>65</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7409,7 +7419,7 @@
         <v>65</v>
       </c>
       <c r="F285" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7426,7 +7436,7 @@
         <v>65</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7443,7 +7453,7 @@
         <v>65</v>
       </c>
       <c r="F287" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7460,7 +7470,7 @@
         <v>65</v>
       </c>
       <c r="F288" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7477,7 +7487,7 @@
         <v>65</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7494,7 +7504,7 @@
         <v>65</v>
       </c>
       <c r="F290" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,7 +7521,7 @@
         <v>65</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7528,7 +7538,7 @@
         <v>65</v>
       </c>
       <c r="F292" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7545,7 +7555,7 @@
         <v>65</v>
       </c>
       <c r="F293" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7562,7 +7572,7 @@
         <v>65</v>
       </c>
       <c r="F294" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7579,7 +7589,7 @@
         <v>65</v>
       </c>
       <c r="F295" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7596,7 +7606,7 @@
         <v>65</v>
       </c>
       <c r="F296" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7613,7 +7623,7 @@
         <v>65</v>
       </c>
       <c r="F297" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7630,7 +7640,7 @@
         <v>65</v>
       </c>
       <c r="F298" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,7 +7657,7 @@
         <v>65</v>
       </c>
       <c r="F299" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7664,7 +7674,7 @@
         <v>65</v>
       </c>
       <c r="F300" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,7 +7691,7 @@
         <v>65</v>
       </c>
       <c r="F301" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7698,7 +7708,7 @@
         <v>65</v>
       </c>
       <c r="F302" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7715,7 +7725,7 @@
         <v>65</v>
       </c>
       <c r="F303" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7732,7 +7742,7 @@
         <v>65</v>
       </c>
       <c r="F304" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7749,7 +7759,7 @@
         <v>65</v>
       </c>
       <c r="F305" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7766,7 +7776,7 @@
         <v>65</v>
       </c>
       <c r="F306" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7783,7 +7793,7 @@
         <v>65</v>
       </c>
       <c r="F307" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7800,7 +7810,7 @@
         <v>65</v>
       </c>
       <c r="F308" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7817,7 +7827,7 @@
         <v>65</v>
       </c>
       <c r="F309" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7834,7 +7844,7 @@
         <v>65</v>
       </c>
       <c r="F310" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7851,7 +7861,7 @@
         <v>65</v>
       </c>
       <c r="F311" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7868,7 +7878,7 @@
         <v>65</v>
       </c>
       <c r="F312" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7885,7 +7895,7 @@
         <v>65</v>
       </c>
       <c r="F313" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7902,7 +7912,7 @@
         <v>65</v>
       </c>
       <c r="F314" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7919,7 +7929,7 @@
         <v>65</v>
       </c>
       <c r="F315" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7936,7 +7946,7 @@
         <v>65</v>
       </c>
       <c r="F316" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,7 +7963,7 @@
         <v>65</v>
       </c>
       <c r="F317" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7970,7 +7980,7 @@
         <v>65</v>
       </c>
       <c r="F318" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7987,7 +7997,7 @@
         <v>65</v>
       </c>
       <c r="F319" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8004,7 +8014,7 @@
         <v>65</v>
       </c>
       <c r="F320" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8021,7 +8031,7 @@
         <v>65</v>
       </c>
       <c r="F321" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8404,7 +8414,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B349" s="1" t="n">
         <v>1</v>
@@ -8418,7 +8428,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B350" s="1" t="n">
         <v>2</v>
@@ -8432,7 +8442,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B351" s="1" t="n">
         <v>3</v>
@@ -8446,7 +8456,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B352" s="1" t="n">
         <v>4</v>
@@ -8460,7 +8470,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B353" s="1" t="n">
         <v>5</v>
@@ -8474,7 +8484,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B354" s="1" t="n">
         <v>6</v>
@@ -8488,7 +8498,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B355" s="1" t="n">
         <v>7</v>
@@ -8502,7 +8512,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B356" s="1" t="n">
         <v>8</v>
@@ -9421,7 +9431,7 @@
         <v>95</v>
       </c>
       <c r="F421" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M421" s="11"/>
     </row>
@@ -9436,7 +9446,7 @@
         <v>95</v>
       </c>
       <c r="F422" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,7 +9460,7 @@
         <v>95</v>
       </c>
       <c r="F423" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9464,7 +9474,7 @@
         <v>95</v>
       </c>
       <c r="F424" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9478,7 +9488,7 @@
         <v>94</v>
       </c>
       <c r="F425" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9492,7 +9502,7 @@
         <v>94</v>
       </c>
       <c r="F426" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9506,7 +9516,7 @@
         <v>94</v>
       </c>
       <c r="F427" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9520,7 +9530,7 @@
         <v>94</v>
       </c>
       <c r="F428" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9534,7 +9544,7 @@
         <v>94</v>
       </c>
       <c r="F429" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9548,7 +9558,7 @@
         <v>94</v>
       </c>
       <c r="F430" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9562,7 +9572,7 @@
         <v>94</v>
       </c>
       <c r="F431" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9576,7 +9586,7 @@
         <v>94</v>
       </c>
       <c r="F432" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9590,7 +9600,7 @@
         <v>94</v>
       </c>
       <c r="F433" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9604,7 +9614,7 @@
         <v>94</v>
       </c>
       <c r="F434" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9618,7 +9628,7 @@
         <v>94</v>
       </c>
       <c r="F435" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9632,7 +9642,7 @@
         <v>93</v>
       </c>
       <c r="F436" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9646,7 +9656,7 @@
         <v>93</v>
       </c>
       <c r="F437" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9660,7 +9670,7 @@
         <v>93</v>
       </c>
       <c r="F438" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9674,7 +9684,7 @@
         <v>93</v>
       </c>
       <c r="F439" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,7 +9698,7 @@
         <v>92</v>
       </c>
       <c r="F440" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9702,7 +9712,7 @@
         <v>92</v>
       </c>
       <c r="F441" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9716,7 +9726,7 @@
         <v>92</v>
       </c>
       <c r="F442" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9730,7 +9740,7 @@
         <v>92</v>
       </c>
       <c r="F443" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9744,7 +9754,7 @@
         <v>92</v>
       </c>
       <c r="F444" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9758,7 +9768,7 @@
         <v>91</v>
       </c>
       <c r="F445" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9772,7 +9782,7 @@
         <v>91</v>
       </c>
       <c r="F446" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9786,7 +9796,7 @@
         <v>91</v>
       </c>
       <c r="F447" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9800,7 +9810,7 @@
         <v>91</v>
       </c>
       <c r="F448" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9814,7 +9824,7 @@
         <v>91</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9828,7 +9838,7 @@
         <v>91</v>
       </c>
       <c r="F450" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9842,7 +9852,7 @@
         <v>89</v>
       </c>
       <c r="F451" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9856,7 +9866,7 @@
         <v>89</v>
       </c>
       <c r="F452" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9870,7 +9880,7 @@
         <v>89</v>
       </c>
       <c r="F453" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9884,7 +9894,7 @@
         <v>89</v>
       </c>
       <c r="F454" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9898,7 +9908,7 @@
         <v>89</v>
       </c>
       <c r="F455" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9912,7 +9922,7 @@
         <v>89</v>
       </c>
       <c r="F456" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9926,7 +9936,7 @@
         <v>89</v>
       </c>
       <c r="F457" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9940,7 +9950,7 @@
         <v>88</v>
       </c>
       <c r="F458" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9954,7 +9964,7 @@
         <v>88</v>
       </c>
       <c r="F459" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9968,7 +9978,7 @@
         <v>88</v>
       </c>
       <c r="F460" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9982,7 +9992,7 @@
         <v>88</v>
       </c>
       <c r="F461" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9996,7 +10006,7 @@
         <v>88</v>
       </c>
       <c r="F462" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10010,7 +10020,7 @@
         <v>88</v>
       </c>
       <c r="F463" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10024,7 +10034,7 @@
         <v>88</v>
       </c>
       <c r="F464" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10038,7 +10048,637 @@
         <v>88</v>
       </c>
       <c r="F465" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A466" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B466" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C466" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F466" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A467" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B467" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C467" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F467" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B468" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C468" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F468" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A469" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B469" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C469" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F469" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B470" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C470" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F470" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B471" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C471" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F471" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B472" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F472" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B473" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C473" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F473" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B474" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F474" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B475" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F475" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B476" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C476" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F476" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A477" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B477" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F477" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A478" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B478" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C478" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F478" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A479" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B479" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C479" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F479" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A480" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B480" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C480" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="F480" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A481" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B481" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C481" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F481" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A482" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B482" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C482" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F482" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A483" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B483" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C483" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F483" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A484" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B484" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C484" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="F484" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A485" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B485" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F485" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A486" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B486" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C486" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F486" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A487" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B487" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C487" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F487" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A488" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B488" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F488" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A489" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B489" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C489" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="F489" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A490" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B490" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C490" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F490" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A491" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B491" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C491" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F491" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A492" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B492" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C492" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F492" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A493" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B493" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C493" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F493" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A494" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B494" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C494" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F494" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A495" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B495" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C495" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="F495" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A496" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B496" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C496" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F496" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A497" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B497" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C497" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F497" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A498" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B498" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C498" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F498" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B499" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C499" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F499" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B500" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C500" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F500" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B501" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C501" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F501" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B502" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C502" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="F502" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B503" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C503" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F503" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B504" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C504" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F504" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A505" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B505" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C505" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F505" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A506" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B506" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C506" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F506" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A507" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B507" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C507" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F507" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A508" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B508" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C508" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F508" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A509" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B509" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C509" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F509" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A510" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B510" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C510" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F510" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -10069,16 +10709,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10089,7 +10729,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>32</v>
@@ -10100,10 +10740,10 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>32</v>
@@ -10114,10 +10754,10 @@
         <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>32</v>
@@ -10128,10 +10768,10 @@
         <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
@@ -10142,10 +10782,10 @@
         <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>32</v>
@@ -10159,7 +10799,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>32</v>
@@ -10173,7 +10813,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>32</v>
@@ -10187,7 +10827,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
@@ -10201,7 +10841,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>32</v>
@@ -10212,10 +10852,10 @@
         <v>63</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>32</v>
@@ -10229,7 +10869,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>32</v>
@@ -10240,10 +10880,10 @@
         <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>32</v>
@@ -10254,10 +10894,10 @@
         <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>32</v>
@@ -10268,10 +10908,10 @@
         <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>32</v>
@@ -10282,10 +10922,10 @@
         <v>70</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>32</v>
@@ -10296,10 +10936,10 @@
         <v>71</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>32</v>
@@ -10310,10 +10950,10 @@
         <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>32</v>
@@ -10327,7 +10967,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>32</v>
@@ -10341,7 +10981,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>32</v>
@@ -10355,7 +10995,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>32</v>
@@ -10369,7 +11009,7 @@
         <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>32</v>
@@ -10380,10 +11020,10 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>32</v>
@@ -10397,7 +11037,7 @@
         <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>32</v>
@@ -10411,7 +11051,7 @@
         <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -10425,7 +11065,7 @@
         <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>32</v>
@@ -10436,10 +11076,10 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -10453,7 +11093,7 @@
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>32</v>
@@ -10464,13 +11104,13 @@
         <v>127</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10478,13 +11118,13 @@
         <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10492,13 +11132,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10506,13 +11146,13 @@
         <v>137</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10520,10 +11160,10 @@
         <v>155</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>32</v>
@@ -10534,13 +11174,13 @@
         <v>367</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10663,25 +11303,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>32</v>
@@ -10690,10 +11330,10 @@
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>32</v>
@@ -10702,10 +11342,10 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>32</v>
@@ -10717,7 +11357,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>32</v>
@@ -10726,10 +11366,10 @@
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>32</v>
@@ -10738,10 +11378,10 @@
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>32</v>
@@ -10753,7 +11393,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>32</v>
@@ -10762,10 +11402,10 @@
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>32</v>
@@ -10774,10 +11414,10 @@
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>32</v>
@@ -10786,10 +11426,10 @@
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>32</v>
@@ -10798,10 +11438,10 @@
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>32</v>
@@ -10810,10 +11450,10 @@
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>32</v>
@@ -10822,10 +11462,10 @@
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>32</v>
@@ -10834,10 +11474,10 @@
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>32</v>
@@ -10846,10 +11486,10 @@
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>32</v>
@@ -10858,10 +11498,10 @@
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>32</v>
@@ -10870,10 +11510,10 @@
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>32</v>
@@ -10882,10 +11522,10 @@
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>32</v>
@@ -10894,10 +11534,10 @@
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>32</v>
@@ -10906,10 +11546,10 @@
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>32</v>
@@ -10918,10 +11558,10 @@
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>32</v>
@@ -10930,10 +11570,10 @@
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>32</v>
@@ -10942,10 +11582,10 @@
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>32</v>
@@ -10954,10 +11594,10 @@
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>32</v>
@@ -10966,10 +11606,10 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>32</v>
@@ -10978,10 +11618,10 @@
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>32</v>
@@ -10990,10 +11630,10 @@
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>32</v>
@@ -11002,10 +11642,10 @@
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>32</v>
@@ -11014,10 +11654,10 @@
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>32</v>
@@ -11026,10 +11666,10 @@
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>32</v>
@@ -11038,10 +11678,10 @@
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>32</v>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -657,7 +657,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="1" width="7.22"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="11" style="1" width="11.52"/>
@@ -1116,8 +1116,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="10.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.14"/>
@@ -1711,6 +1711,20 @@
       </c>
       <c r="D42" s="2" t="n">
         <v>15.848415</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1.170211</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0.371113</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>18.316014</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1744,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G83"/>
-  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.82421875" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="35.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.98"/>
@@ -2678,7 +2692,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M510"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.85"/>
@@ -10698,7 +10712,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.39"/>
@@ -11293,7 +11307,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="13.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="30.78"/>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="120">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -2691,7 +2691,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M510"/>
+  <dimension ref="A1:M514"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="14.74"/>
@@ -3318,7 +3318,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="1" t="n">
         <v>50</v>
@@ -3332,7 +3332,7 @@
         <v>30</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>50</v>
@@ -3341,18 +3341,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="s">
-        <v>31</v>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C46" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="D46" s="1" t="n">
         <v>100</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>115</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3360,10 +3360,10 @@
         <v>31</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>115</v>
@@ -3374,13 +3374,13 @@
         <v>31</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="1" t="n">
         <v>80</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3388,10 +3388,10 @@
         <v>31</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>110</v>
@@ -3402,13 +3402,13 @@
         <v>31</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3416,7 +3416,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1" t="n">
         <v>50</v>
@@ -3425,46 +3425,46 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>20</v>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3472,13 +3472,13 @@
         <v>20</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55" s="1" t="n">
         <v>82</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3486,13 +3486,13 @@
         <v>20</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3500,13 +3500,13 @@
         <v>20</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3514,55 +3514,55 @@
         <v>20</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>120.56</v>
+        <v>72</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>120.56</v>
+        <v>72</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>115.56</v>
+        <v>72</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3570,10 +3570,10 @@
         <v>21</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>115.56</v>
+        <v>120.56</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>65</v>
@@ -3584,10 +3584,10 @@
         <v>21</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>105.56</v>
+        <v>120.56</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>65</v>
@@ -3598,10 +3598,10 @@
         <v>21</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>105.56</v>
+        <v>115.56</v>
       </c>
       <c r="D64" s="1" t="n">
         <v>65</v>
@@ -3612,10 +3612,10 @@
         <v>21</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>105.56</v>
+        <v>115.56</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>65</v>
@@ -3626,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>105.56</v>
@@ -3640,7 +3640,7 @@
         <v>21</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>105.56</v>
@@ -3651,44 +3651,44 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>55</v>
+        <v>105.56</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,13 +3696,13 @@
         <v>22</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71" s="1" t="n">
         <v>55</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3710,13 +3710,13 @@
         <v>22</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3724,13 +3724,13 @@
         <v>22</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3738,13 +3738,13 @@
         <v>22</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3752,13 +3752,13 @@
         <v>22</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,73 +3766,55 @@
         <v>22</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3840,16 +3822,16 @@
         <v>28</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>55</v>
@@ -3860,16 +3842,16 @@
         <v>28</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>55</v>
@@ -3877,19 +3859,19 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>55</v>
@@ -3897,19 +3879,19 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>55</v>
@@ -3917,19 +3899,19 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>55</v>
@@ -3940,16 +3922,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>55</v>
@@ -3960,16 +3942,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>66</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>55</v>
@@ -3977,50 +3959,59 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D87" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E87" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F87" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>66</v>
       </c>
+      <c r="E88" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F88" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>66</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>55</v>
@@ -4031,10 +4022,10 @@
         <v>29</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D90" s="1" t="n">
         <v>66</v>
@@ -4048,10 +4039,10 @@
         <v>29</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>66</v>
@@ -4062,13 +4053,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>66</v>
@@ -4079,13 +4070,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D93" s="1" t="n">
         <v>66</v>
@@ -4096,13 +4087,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D94" s="1" t="n">
         <v>66</v>
@@ -4116,10 +4107,10 @@
         <v>26</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>66</v>
@@ -4133,10 +4124,10 @@
         <v>26</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>66</v>
@@ -4150,10 +4141,10 @@
         <v>26</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D97" s="1" t="n">
         <v>66</v>
@@ -4167,10 +4158,10 @@
         <v>26</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>66</v>
@@ -4184,7 +4175,7 @@
         <v>26</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C99" s="1" t="n">
         <v>120</v>
@@ -4201,7 +4192,7 @@
         <v>26</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C100" s="1" t="n">
         <v>120</v>
@@ -4215,16 +4206,16 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>55</v>
@@ -4232,16 +4223,16 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>55</v>
@@ -4249,16 +4240,16 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>55</v>
@@ -4269,13 +4260,13 @@
         <v>23</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C104" s="1" t="n">
         <v>100</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>55</v>
@@ -4286,13 +4277,13 @@
         <v>23</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>55</v>
@@ -4303,13 +4294,13 @@
         <v>23</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>55</v>
@@ -4320,13 +4311,13 @@
         <v>23</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>55</v>
@@ -4337,13 +4328,13 @@
         <v>23</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C108" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>55</v>
@@ -4354,13 +4345,13 @@
         <v>23</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C109" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>55</v>
@@ -4371,13 +4362,13 @@
         <v>23</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C110" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>55</v>
@@ -4388,16 +4379,16 @@
         <v>23</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4405,16 +4396,16 @@
         <v>23</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4422,16 +4413,16 @@
         <v>23</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4439,13 +4430,13 @@
         <v>23</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C114" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>56</v>
@@ -4456,13 +4447,13 @@
         <v>23</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C115" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>56</v>
@@ -4473,13 +4464,13 @@
         <v>23</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>56</v>
@@ -4490,13 +4481,13 @@
         <v>23</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>56</v>
@@ -4507,13 +4498,13 @@
         <v>23</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>56</v>
@@ -4524,13 +4515,13 @@
         <v>23</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C119" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>56</v>
@@ -4541,13 +4532,13 @@
         <v>23</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C120" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>56</v>
@@ -4555,53 +4546,53 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4609,13 +4600,13 @@
         <v>24</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C124" s="1" t="n">
         <v>100</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>55</v>
@@ -4626,13 +4617,13 @@
         <v>24</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>55</v>
@@ -4643,13 +4634,13 @@
         <v>24</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>55</v>
@@ -4660,13 +4651,13 @@
         <v>24</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>55</v>
@@ -4677,13 +4668,13 @@
         <v>24</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C128" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D128" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>55</v>
@@ -4694,13 +4685,13 @@
         <v>24</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C129" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>55</v>
@@ -4711,13 +4702,13 @@
         <v>24</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C130" s="1" t="n">
         <v>93</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>55</v>
@@ -4728,16 +4719,16 @@
         <v>24</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4745,16 +4736,16 @@
         <v>24</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4762,16 +4753,16 @@
         <v>24</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4779,13 +4770,13 @@
         <v>24</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C134" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>56</v>
@@ -4796,13 +4787,13 @@
         <v>24</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C135" s="1" t="n">
         <v>64</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>56</v>
@@ -4813,13 +4804,13 @@
         <v>24</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>56</v>
@@ -4830,13 +4821,13 @@
         <v>24</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>56</v>
@@ -4847,13 +4838,13 @@
         <v>24</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D138" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>56</v>
@@ -4864,13 +4855,13 @@
         <v>24</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C139" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>56</v>
@@ -4881,13 +4872,13 @@
         <v>24</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1" t="n">
         <v>61</v>
       </c>
       <c r="D140" s="1" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>56</v>
@@ -4895,53 +4886,53 @@
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4949,7 +4940,7 @@
         <v>25</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C144" s="1" t="n">
         <v>140</v>
@@ -4966,10 +4957,10 @@
         <v>25</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>65</v>
@@ -4983,10 +4974,10 @@
         <v>25</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>65</v>
@@ -5000,10 +4991,10 @@
         <v>25</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>65</v>
@@ -5017,7 +5008,7 @@
         <v>25</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C148" s="1" t="n">
         <v>139</v>
@@ -5034,7 +5025,7 @@
         <v>25</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C149" s="1" t="n">
         <v>139</v>
@@ -5051,10 +5042,10 @@
         <v>25</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>65</v>
@@ -5068,16 +5059,16 @@
         <v>25</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5085,16 +5076,16 @@
         <v>25</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5102,16 +5093,16 @@
         <v>25</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5119,7 +5110,7 @@
         <v>25</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C154" s="1" t="n">
         <v>138</v>
@@ -5136,10 +5127,10 @@
         <v>25</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>65</v>
@@ -5153,10 +5144,10 @@
         <v>25</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>65</v>
@@ -5170,10 +5161,10 @@
         <v>25</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>65</v>
@@ -5187,7 +5178,7 @@
         <v>25</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>137</v>
@@ -5204,7 +5195,7 @@
         <v>25</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>137</v>
@@ -5221,10 +5212,10 @@
         <v>25</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>65</v>
@@ -5234,63 +5225,54 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="9" t="s">
-        <v>35</v>
+      <c r="A161" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D161" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E161" s="1" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="9" t="s">
-        <v>35</v>
+      <c r="A162" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E162" s="1" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="9" t="s">
-        <v>35</v>
+      <c r="A163" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="D163" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="E163" s="1" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,7 +5280,7 @@
         <v>35</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C164" s="1" t="n">
         <v>95</v>
@@ -5307,18 +5289,18 @@
         <v>70</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="6" t="s">
-        <v>36</v>
+      <c r="A165" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" s="1" t="n">
         <v>95</v>
@@ -5327,18 +5309,18 @@
         <v>70</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="6" t="s">
-        <v>36</v>
+      <c r="A166" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C166" s="1" t="n">
         <v>95</v>
@@ -5347,18 +5329,18 @@
         <v>70</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="6" t="s">
-        <v>36</v>
+      <c r="A167" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C167" s="1" t="n">
         <v>95</v>
@@ -5367,7 +5349,7 @@
         <v>70</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>55</v>
@@ -5378,7 +5360,7 @@
         <v>36</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C168" s="1" t="n">
         <v>95</v>
@@ -5387,7 +5369,7 @@
         <v>70</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>55</v>
@@ -5398,16 +5380,16 @@
         <v>36</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D169" s="1" t="n">
         <v>70</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>55</v>
@@ -5418,10 +5400,10 @@
         <v>36</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>70</v>
@@ -5435,10 +5417,10 @@
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C171" s="1" t="n">
         <v>95</v>
@@ -5446,22 +5428,28 @@
       <c r="D171" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E171" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F171" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>55</v>
@@ -5469,16 +5457,19 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D173" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E173" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>55</v>
@@ -5489,7 +5480,7 @@
         <v>37</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C174" s="1" t="n">
         <v>95</v>
@@ -5506,10 +5497,10 @@
         <v>37</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D175" s="1" t="n">
         <v>70</v>
@@ -5523,10 +5514,10 @@
         <v>37</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D176" s="1" t="n">
         <v>70</v>
@@ -5540,10 +5531,10 @@
         <v>37</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D177" s="1" t="n">
         <v>70</v>
@@ -5557,7 +5548,7 @@
         <v>37</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C178" s="1" t="n">
         <v>94</v>
@@ -5574,7 +5565,7 @@
         <v>37</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C179" s="1" t="n">
         <v>94</v>
@@ -5591,7 +5582,7 @@
         <v>37</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C180" s="1" t="n">
         <v>94</v>
@@ -5608,7 +5599,7 @@
         <v>37</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C181" s="1" t="n">
         <v>94</v>
@@ -5625,7 +5616,7 @@
         <v>37</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C182" s="1" t="n">
         <v>94</v>
@@ -5642,7 +5633,7 @@
         <v>37</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C183" s="1" t="n">
         <v>94</v>
@@ -5659,7 +5650,7 @@
         <v>37</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C184" s="1" t="n">
         <v>94</v>
@@ -5676,7 +5667,7 @@
         <v>37</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C185" s="1" t="n">
         <v>94</v>
@@ -5693,16 +5684,16 @@
         <v>37</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D186" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5710,16 +5701,16 @@
         <v>37</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D187" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5727,16 +5718,16 @@
         <v>37</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D188" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,7 +5735,7 @@
         <v>37</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C189" s="1" t="n">
         <v>93</v>
@@ -5761,10 +5752,10 @@
         <v>37</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D190" s="1" t="n">
         <v>70</v>
@@ -5778,10 +5769,10 @@
         <v>37</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D191" s="1" t="n">
         <v>70</v>
@@ -5795,10 +5786,10 @@
         <v>37</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D192" s="1" t="n">
         <v>70</v>
@@ -5812,7 +5803,7 @@
         <v>37</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C193" s="1" t="n">
         <v>92</v>
@@ -5829,7 +5820,7 @@
         <v>37</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C194" s="1" t="n">
         <v>92</v>
@@ -5846,10 +5837,10 @@
         <v>37</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D195" s="1" t="n">
         <v>70</v>
@@ -5863,10 +5854,10 @@
         <v>37</v>
       </c>
       <c r="B196" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D196" s="1" t="n">
         <v>70</v>
@@ -5880,10 +5871,10 @@
         <v>37</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D197" s="1" t="n">
         <v>70</v>
@@ -5897,7 +5888,7 @@
         <v>37</v>
       </c>
       <c r="B198" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C198" s="1" t="n">
         <v>91</v>
@@ -5914,7 +5905,7 @@
         <v>37</v>
       </c>
       <c r="B199" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C199" s="1" t="n">
         <v>91</v>
@@ -5931,7 +5922,7 @@
         <v>37</v>
       </c>
       <c r="B200" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C200" s="1" t="n">
         <v>91</v>
@@ -5948,16 +5939,16 @@
         <v>37</v>
       </c>
       <c r="B201" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D201" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5965,16 +5956,16 @@
         <v>37</v>
       </c>
       <c r="B202" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D202" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5982,16 +5973,16 @@
         <v>37</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D203" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5999,7 +5990,7 @@
         <v>37</v>
       </c>
       <c r="B204" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C204" s="1" t="n">
         <v>89</v>
@@ -6016,7 +6007,7 @@
         <v>37</v>
       </c>
       <c r="B205" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C205" s="1" t="n">
         <v>89</v>
@@ -6033,7 +6024,7 @@
         <v>37</v>
       </c>
       <c r="B206" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C206" s="1" t="n">
         <v>89</v>
@@ -6050,7 +6041,7 @@
         <v>37</v>
       </c>
       <c r="B207" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C207" s="1" t="n">
         <v>89</v>
@@ -6067,10 +6058,10 @@
         <v>37</v>
       </c>
       <c r="B208" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D208" s="1" t="n">
         <v>70</v>
@@ -6084,10 +6075,10 @@
         <v>37</v>
       </c>
       <c r="B209" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D209" s="1" t="n">
         <v>70</v>
@@ -6101,10 +6092,10 @@
         <v>37</v>
       </c>
       <c r="B210" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D210" s="1" t="n">
         <v>70</v>
@@ -6118,7 +6109,7 @@
         <v>37</v>
       </c>
       <c r="B211" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C211" s="1" t="n">
         <v>88</v>
@@ -6135,7 +6126,7 @@
         <v>37</v>
       </c>
       <c r="B212" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C212" s="1" t="n">
         <v>88</v>
@@ -6152,7 +6143,7 @@
         <v>37</v>
       </c>
       <c r="B213" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C213" s="1" t="n">
         <v>88</v>
@@ -6169,7 +6160,7 @@
         <v>37</v>
       </c>
       <c r="B214" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C214" s="1" t="n">
         <v>88</v>
@@ -6186,7 +6177,7 @@
         <v>37</v>
       </c>
       <c r="B215" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C215" s="1" t="n">
         <v>88</v>
@@ -6200,62 +6191,53 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B216" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D216" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E216" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F216" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B217" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D217" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E217" s="1" t="n">
-        <v>25</v>
-      </c>
       <c r="F217" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B218" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D218" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E218" s="1" t="n">
-        <v>20</v>
-      </c>
       <c r="F218" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6263,7 +6245,7 @@
         <v>42</v>
       </c>
       <c r="B219" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C219" s="1" t="n">
         <v>95</v>
@@ -6272,7 +6254,7 @@
         <v>70</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F219" s="6" t="s">
         <v>55</v>
@@ -6280,10 +6262,10 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B220" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220" s="1" t="n">
         <v>95</v>
@@ -6291,16 +6273,19 @@
       <c r="D220" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E220" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="F220" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B221" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C221" s="1" t="n">
         <v>95</v>
@@ -6308,22 +6293,28 @@
       <c r="D221" s="1" t="n">
         <v>70</v>
       </c>
+      <c r="E221" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F221" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B222" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C222" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D222" s="1" t="n">
         <v>70</v>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>55</v>
@@ -6334,7 +6325,7 @@
         <v>43</v>
       </c>
       <c r="B223" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C223" s="1" t="n">
         <v>95</v>
@@ -6351,10 +6342,10 @@
         <v>43</v>
       </c>
       <c r="B224" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D224" s="1" t="n">
         <v>70</v>
@@ -6368,10 +6359,10 @@
         <v>43</v>
       </c>
       <c r="B225" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D225" s="1" t="n">
         <v>70</v>
@@ -6385,10 +6376,10 @@
         <v>43</v>
       </c>
       <c r="B226" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D226" s="1" t="n">
         <v>70</v>
@@ -6402,7 +6393,7 @@
         <v>43</v>
       </c>
       <c r="B227" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C227" s="1" t="n">
         <v>94</v>
@@ -6419,7 +6410,7 @@
         <v>43</v>
       </c>
       <c r="B228" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C228" s="1" t="n">
         <v>94</v>
@@ -6436,7 +6427,7 @@
         <v>43</v>
       </c>
       <c r="B229" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C229" s="1" t="n">
         <v>94</v>
@@ -6453,7 +6444,7 @@
         <v>43</v>
       </c>
       <c r="B230" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C230" s="1" t="n">
         <v>94</v>
@@ -6470,7 +6461,7 @@
         <v>43</v>
       </c>
       <c r="B231" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C231" s="1" t="n">
         <v>94</v>
@@ -6487,7 +6478,7 @@
         <v>43</v>
       </c>
       <c r="B232" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C232" s="1" t="n">
         <v>94</v>
@@ -6504,7 +6495,7 @@
         <v>43</v>
       </c>
       <c r="B233" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C233" s="1" t="n">
         <v>94</v>
@@ -6521,7 +6512,7 @@
         <v>43</v>
       </c>
       <c r="B234" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C234" s="1" t="n">
         <v>94</v>
@@ -6538,16 +6529,16 @@
         <v>43</v>
       </c>
       <c r="B235" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D235" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6555,16 +6546,16 @@
         <v>43</v>
       </c>
       <c r="B236" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D236" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6572,16 +6563,16 @@
         <v>43</v>
       </c>
       <c r="B237" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D237" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6589,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="B238" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C238" s="1" t="n">
         <v>93</v>
@@ -6606,10 +6597,10 @@
         <v>43</v>
       </c>
       <c r="B239" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D239" s="1" t="n">
         <v>70</v>
@@ -6623,10 +6614,10 @@
         <v>43</v>
       </c>
       <c r="B240" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D240" s="1" t="n">
         <v>70</v>
@@ -6640,10 +6631,10 @@
         <v>43</v>
       </c>
       <c r="B241" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D241" s="1" t="n">
         <v>70</v>
@@ -6657,7 +6648,7 @@
         <v>43</v>
       </c>
       <c r="B242" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C242" s="1" t="n">
         <v>92</v>
@@ -6674,7 +6665,7 @@
         <v>43</v>
       </c>
       <c r="B243" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C243" s="1" t="n">
         <v>92</v>
@@ -6691,10 +6682,10 @@
         <v>43</v>
       </c>
       <c r="B244" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D244" s="1" t="n">
         <v>70</v>
@@ -6708,10 +6699,10 @@
         <v>43</v>
       </c>
       <c r="B245" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D245" s="1" t="n">
         <v>70</v>
@@ -6725,10 +6716,10 @@
         <v>43</v>
       </c>
       <c r="B246" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D246" s="1" t="n">
         <v>70</v>
@@ -6742,7 +6733,7 @@
         <v>43</v>
       </c>
       <c r="B247" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C247" s="1" t="n">
         <v>91</v>
@@ -6759,7 +6750,7 @@
         <v>43</v>
       </c>
       <c r="B248" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C248" s="1" t="n">
         <v>91</v>
@@ -6776,7 +6767,7 @@
         <v>43</v>
       </c>
       <c r="B249" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C249" s="1" t="n">
         <v>91</v>
@@ -6793,16 +6784,16 @@
         <v>43</v>
       </c>
       <c r="B250" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D250" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6810,16 +6801,16 @@
         <v>43</v>
       </c>
       <c r="B251" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D251" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6827,16 +6818,16 @@
         <v>43</v>
       </c>
       <c r="B252" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D252" s="1" t="n">
         <v>70</v>
       </c>
       <c r="F252" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6844,7 +6835,7 @@
         <v>43</v>
       </c>
       <c r="B253" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C253" s="1" t="n">
         <v>89</v>
@@ -6861,7 +6852,7 @@
         <v>43</v>
       </c>
       <c r="B254" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C254" s="1" t="n">
         <v>89</v>
@@ -6878,7 +6869,7 @@
         <v>43</v>
       </c>
       <c r="B255" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C255" s="1" t="n">
         <v>89</v>
@@ -6895,7 +6886,7 @@
         <v>43</v>
       </c>
       <c r="B256" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C256" s="1" t="n">
         <v>89</v>
@@ -6912,10 +6903,10 @@
         <v>43</v>
       </c>
       <c r="B257" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D257" s="1" t="n">
         <v>70</v>
@@ -6929,10 +6920,10 @@
         <v>43</v>
       </c>
       <c r="B258" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D258" s="1" t="n">
         <v>70</v>
@@ -6946,10 +6937,10 @@
         <v>43</v>
       </c>
       <c r="B259" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D259" s="1" t="n">
         <v>70</v>
@@ -6963,7 +6954,7 @@
         <v>43</v>
       </c>
       <c r="B260" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C260" s="1" t="n">
         <v>88</v>
@@ -6980,7 +6971,7 @@
         <v>43</v>
       </c>
       <c r="B261" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C261" s="1" t="n">
         <v>88</v>
@@ -6997,7 +6988,7 @@
         <v>43</v>
       </c>
       <c r="B262" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C262" s="1" t="n">
         <v>88</v>
@@ -7014,7 +7005,7 @@
         <v>43</v>
       </c>
       <c r="B263" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C263" s="1" t="n">
         <v>88</v>
@@ -7031,7 +7022,7 @@
         <v>43</v>
       </c>
       <c r="B264" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C264" s="1" t="n">
         <v>88</v>
@@ -7045,62 +7036,53 @@
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B265" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D265" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E265" s="1" t="n">
-        <v>50</v>
-      </c>
       <c r="F265" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B266" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D266" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E266" s="1" t="n">
-        <v>50</v>
-      </c>
       <c r="F266" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B267" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D267" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="E267" s="1" t="n">
-        <v>40</v>
-      </c>
       <c r="F267" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7108,7 +7090,7 @@
         <v>39</v>
       </c>
       <c r="B268" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C268" s="1" t="n">
         <v>95</v>
@@ -7117,7 +7099,7 @@
         <v>70</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>55</v>
@@ -7125,19 +7107,19 @@
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B269" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D269" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F269" s="6" t="s">
         <v>55</v>
@@ -7145,19 +7127,19 @@
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B270" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C270" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D270" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>55</v>
@@ -7165,19 +7147,19 @@
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B271" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C271" s="1" t="n">
         <v>95</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>55</v>
@@ -7188,7 +7170,7 @@
         <v>40</v>
       </c>
       <c r="B272" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C272" s="1" t="n">
         <v>95</v>
@@ -7197,7 +7179,7 @@
         <v>65</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>55</v>
@@ -7208,16 +7190,16 @@
         <v>40</v>
       </c>
       <c r="B273" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D273" s="1" t="n">
         <v>65</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F273" s="6" t="s">
         <v>55</v>
@@ -7228,10 +7210,10 @@
         <v>40</v>
       </c>
       <c r="B274" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D274" s="1" t="n">
         <v>65</v>
@@ -7248,10 +7230,10 @@
         <v>40</v>
       </c>
       <c r="B275" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D275" s="1" t="n">
         <v>65</v>
@@ -7268,7 +7250,7 @@
         <v>40</v>
       </c>
       <c r="B276" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C276" s="1" t="n">
         <v>94</v>
@@ -7285,50 +7267,59 @@
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B277" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D277" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E277" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F277" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B278" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D278" s="1" t="n">
         <v>65</v>
       </c>
+      <c r="E278" s="1" t="n">
+        <v>20</v>
+      </c>
       <c r="F278" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B279" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D279" s="1" t="n">
         <v>65</v>
+      </c>
+      <c r="E279" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="F279" s="6" t="s">
         <v>55</v>
@@ -7339,7 +7330,7 @@
         <v>41</v>
       </c>
       <c r="B280" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C280" s="1" t="n">
         <v>95</v>
@@ -7356,10 +7347,10 @@
         <v>41</v>
       </c>
       <c r="B281" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D281" s="1" t="n">
         <v>65</v>
@@ -7373,10 +7364,10 @@
         <v>41</v>
       </c>
       <c r="B282" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D282" s="1" t="n">
         <v>65</v>
@@ -7390,10 +7381,10 @@
         <v>41</v>
       </c>
       <c r="B283" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D283" s="1" t="n">
         <v>65</v>
@@ -7407,7 +7398,7 @@
         <v>41</v>
       </c>
       <c r="B284" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C284" s="1" t="n">
         <v>94</v>
@@ -7424,7 +7415,7 @@
         <v>41</v>
       </c>
       <c r="B285" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C285" s="1" t="n">
         <v>94</v>
@@ -7441,7 +7432,7 @@
         <v>41</v>
       </c>
       <c r="B286" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C286" s="1" t="n">
         <v>94</v>
@@ -7458,7 +7449,7 @@
         <v>41</v>
       </c>
       <c r="B287" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C287" s="1" t="n">
         <v>94</v>
@@ -7475,7 +7466,7 @@
         <v>41</v>
       </c>
       <c r="B288" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C288" s="1" t="n">
         <v>94</v>
@@ -7492,7 +7483,7 @@
         <v>41</v>
       </c>
       <c r="B289" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C289" s="1" t="n">
         <v>94</v>
@@ -7509,7 +7500,7 @@
         <v>41</v>
       </c>
       <c r="B290" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C290" s="1" t="n">
         <v>94</v>
@@ -7526,7 +7517,7 @@
         <v>41</v>
       </c>
       <c r="B291" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C291" s="1" t="n">
         <v>94</v>
@@ -7543,16 +7534,16 @@
         <v>41</v>
       </c>
       <c r="B292" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D292" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F292" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7560,16 +7551,16 @@
         <v>41</v>
       </c>
       <c r="B293" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D293" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F293" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7577,16 +7568,16 @@
         <v>41</v>
       </c>
       <c r="B294" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D294" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F294" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7594,7 +7585,7 @@
         <v>41</v>
       </c>
       <c r="B295" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C295" s="1" t="n">
         <v>93</v>
@@ -7611,10 +7602,10 @@
         <v>41</v>
       </c>
       <c r="B296" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D296" s="1" t="n">
         <v>65</v>
@@ -7628,10 +7619,10 @@
         <v>41</v>
       </c>
       <c r="B297" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D297" s="1" t="n">
         <v>65</v>
@@ -7645,10 +7636,10 @@
         <v>41</v>
       </c>
       <c r="B298" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D298" s="1" t="n">
         <v>65</v>
@@ -7662,7 +7653,7 @@
         <v>41</v>
       </c>
       <c r="B299" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C299" s="1" t="n">
         <v>92</v>
@@ -7679,7 +7670,7 @@
         <v>41</v>
       </c>
       <c r="B300" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C300" s="1" t="n">
         <v>92</v>
@@ -7696,10 +7687,10 @@
         <v>41</v>
       </c>
       <c r="B301" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D301" s="1" t="n">
         <v>65</v>
@@ -7713,10 +7704,10 @@
         <v>41</v>
       </c>
       <c r="B302" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D302" s="1" t="n">
         <v>65</v>
@@ -7730,10 +7721,10 @@
         <v>41</v>
       </c>
       <c r="B303" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D303" s="1" t="n">
         <v>65</v>
@@ -7747,7 +7738,7 @@
         <v>41</v>
       </c>
       <c r="B304" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C304" s="1" t="n">
         <v>91</v>
@@ -7764,7 +7755,7 @@
         <v>41</v>
       </c>
       <c r="B305" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C305" s="1" t="n">
         <v>91</v>
@@ -7781,7 +7772,7 @@
         <v>41</v>
       </c>
       <c r="B306" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C306" s="1" t="n">
         <v>91</v>
@@ -7798,16 +7789,16 @@
         <v>41</v>
       </c>
       <c r="B307" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D307" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F307" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7815,16 +7806,16 @@
         <v>41</v>
       </c>
       <c r="B308" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D308" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F308" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7832,16 +7823,16 @@
         <v>41</v>
       </c>
       <c r="B309" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D309" s="1" t="n">
         <v>65</v>
       </c>
       <c r="F309" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,7 +7840,7 @@
         <v>41</v>
       </c>
       <c r="B310" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C310" s="1" t="n">
         <v>89</v>
@@ -7866,7 +7857,7 @@
         <v>41</v>
       </c>
       <c r="B311" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C311" s="1" t="n">
         <v>89</v>
@@ -7883,7 +7874,7 @@
         <v>41</v>
       </c>
       <c r="B312" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C312" s="1" t="n">
         <v>89</v>
@@ -7900,7 +7891,7 @@
         <v>41</v>
       </c>
       <c r="B313" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C313" s="1" t="n">
         <v>89</v>
@@ -7917,10 +7908,10 @@
         <v>41</v>
       </c>
       <c r="B314" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D314" s="1" t="n">
         <v>65</v>
@@ -7934,10 +7925,10 @@
         <v>41</v>
       </c>
       <c r="B315" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D315" s="1" t="n">
         <v>65</v>
@@ -7951,10 +7942,10 @@
         <v>41</v>
       </c>
       <c r="B316" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D316" s="1" t="n">
         <v>65</v>
@@ -7968,7 +7959,7 @@
         <v>41</v>
       </c>
       <c r="B317" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C317" s="1" t="n">
         <v>88</v>
@@ -7985,7 +7976,7 @@
         <v>41</v>
       </c>
       <c r="B318" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C318" s="1" t="n">
         <v>88</v>
@@ -8002,7 +7993,7 @@
         <v>41</v>
       </c>
       <c r="B319" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C319" s="1" t="n">
         <v>88</v>
@@ -8019,7 +8010,7 @@
         <v>41</v>
       </c>
       <c r="B320" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C320" s="1" t="n">
         <v>88</v>
@@ -8036,7 +8027,7 @@
         <v>41</v>
       </c>
       <c r="B321" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C321" s="1" t="n">
         <v>88</v>
@@ -8050,44 +8041,53 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B322" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
+      </c>
+      <c r="F322" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B323" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>110</v>
+        <v>65</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B324" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="F324" s="6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8095,13 +8095,13 @@
         <v>32</v>
       </c>
       <c r="B325" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C325" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,13 +8109,13 @@
         <v>32</v>
       </c>
       <c r="B326" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C326" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,13 +8123,13 @@
         <v>32</v>
       </c>
       <c r="B327" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C327" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8137,13 +8137,13 @@
         <v>32</v>
       </c>
       <c r="B328" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C328" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8151,13 +8151,13 @@
         <v>32</v>
       </c>
       <c r="B329" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8165,13 +8165,13 @@
         <v>32</v>
       </c>
       <c r="B330" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8179,13 +8179,13 @@
         <v>32</v>
       </c>
       <c r="B331" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8193,7 +8193,7 @@
         <v>32</v>
       </c>
       <c r="B332" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C332" s="1" t="n">
         <v>48</v>
@@ -8207,7 +8207,7 @@
         <v>32</v>
       </c>
       <c r="B333" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C333" s="1" t="n">
         <v>48</v>
@@ -8218,44 +8218,44 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B334" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B335" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B336" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8263,13 +8263,13 @@
         <v>33</v>
       </c>
       <c r="B337" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C337" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8277,13 +8277,13 @@
         <v>33</v>
       </c>
       <c r="B338" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C338" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8291,13 +8291,13 @@
         <v>33</v>
       </c>
       <c r="B339" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C339" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8305,13 +8305,13 @@
         <v>33</v>
       </c>
       <c r="B340" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C340" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8319,13 +8319,13 @@
         <v>33</v>
       </c>
       <c r="B341" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8333,13 +8333,13 @@
         <v>33</v>
       </c>
       <c r="B342" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8347,13 +8347,13 @@
         <v>33</v>
       </c>
       <c r="B343" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D343" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8361,7 +8361,7 @@
         <v>33</v>
       </c>
       <c r="B344" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C344" s="1" t="n">
         <v>48</v>
@@ -8375,7 +8375,7 @@
         <v>33</v>
       </c>
       <c r="B345" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C345" s="1" t="n">
         <v>48</v>
@@ -8389,7 +8389,7 @@
         <v>33</v>
       </c>
       <c r="B346" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C346" s="1" t="n">
         <v>48</v>
@@ -8403,7 +8403,7 @@
         <v>33</v>
       </c>
       <c r="B347" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C347" s="1" t="n">
         <v>48</v>
@@ -8417,7 +8417,7 @@
         <v>33</v>
       </c>
       <c r="B348" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C348" s="1" t="n">
         <v>48</v>
@@ -8428,44 +8428,44 @@
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="6" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B349" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D349" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="6" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B350" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D350" s="1" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="6" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B351" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D351" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8473,13 +8473,13 @@
         <v>58</v>
       </c>
       <c r="B352" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C352" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D352" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8487,13 +8487,13 @@
         <v>58</v>
       </c>
       <c r="B353" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C353" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D353" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8501,13 +8501,13 @@
         <v>58</v>
       </c>
       <c r="B354" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C354" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8515,13 +8515,13 @@
         <v>58</v>
       </c>
       <c r="B355" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C355" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D355" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8529,55 +8529,55 @@
         <v>58</v>
       </c>
       <c r="B356" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D356" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="6" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B357" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C357" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D357" s="1" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="6" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B358" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C358" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D358" s="1" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="6" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B359" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D359" s="1" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8585,13 +8585,13 @@
         <v>34</v>
       </c>
       <c r="B360" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C360" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D360" s="1" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8599,13 +8599,13 @@
         <v>34</v>
       </c>
       <c r="B361" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C361" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D361" s="1" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8613,13 +8613,13 @@
         <v>34</v>
       </c>
       <c r="B362" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C362" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D362" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8627,13 +8627,13 @@
         <v>34</v>
       </c>
       <c r="B363" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C363" s="1" t="n">
         <v>49</v>
       </c>
       <c r="D363" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8641,24 +8641,24 @@
         <v>34</v>
       </c>
       <c r="B364" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D364" s="1" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B365" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D365" s="1" t="n">
         <v>90</v>
@@ -8666,13 +8666,13 @@
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B366" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D366" s="1" t="n">
         <v>90</v>
@@ -8680,16 +8680,16 @@
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B367" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D367" s="1" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8697,7 +8697,7 @@
         <v>45</v>
       </c>
       <c r="B368" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C368" s="1" t="n">
         <v>45</v>
@@ -8711,13 +8711,13 @@
         <v>45</v>
       </c>
       <c r="B369" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C369" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D369" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8725,13 +8725,13 @@
         <v>45</v>
       </c>
       <c r="B370" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C370" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D370" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8739,13 +8739,13 @@
         <v>45</v>
       </c>
       <c r="B371" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C371" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8753,13 +8753,13 @@
         <v>45</v>
       </c>
       <c r="B372" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D372" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8767,13 +8767,13 @@
         <v>45</v>
       </c>
       <c r="B373" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D373" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8781,13 +8781,13 @@
         <v>45</v>
       </c>
       <c r="B374" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D374" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8795,7 +8795,7 @@
         <v>45</v>
       </c>
       <c r="B375" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C375" s="1" t="n">
         <v>44</v>
@@ -8809,7 +8809,7 @@
         <v>45</v>
       </c>
       <c r="B376" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C376" s="1" t="n">
         <v>44</v>
@@ -8823,7 +8823,7 @@
         <v>45</v>
       </c>
       <c r="B377" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C377" s="1" t="n">
         <v>44</v>
@@ -8837,7 +8837,7 @@
         <v>45</v>
       </c>
       <c r="B378" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C378" s="1" t="n">
         <v>44</v>
@@ -8848,58 +8848,58 @@
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B379" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D379" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B380" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D380" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B381" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D381" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B382" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,13 +8907,13 @@
         <v>46</v>
       </c>
       <c r="B383" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C383" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8921,13 +8921,13 @@
         <v>46</v>
       </c>
       <c r="B384" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C384" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8935,13 +8935,13 @@
         <v>46</v>
       </c>
       <c r="B385" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C385" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D385" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8949,13 +8949,13 @@
         <v>46</v>
       </c>
       <c r="B386" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D386" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8963,13 +8963,13 @@
         <v>46</v>
       </c>
       <c r="B387" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D387" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8977,13 +8977,13 @@
         <v>46</v>
       </c>
       <c r="B388" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8991,13 +8991,13 @@
         <v>46</v>
       </c>
       <c r="B389" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D389" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9005,7 +9005,7 @@
         <v>46</v>
       </c>
       <c r="B390" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C390" s="1" t="n">
         <v>44</v>
@@ -9019,7 +9019,7 @@
         <v>46</v>
       </c>
       <c r="B391" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C391" s="1" t="n">
         <v>44</v>
@@ -9033,7 +9033,7 @@
         <v>46</v>
       </c>
       <c r="B392" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C392" s="1" t="n">
         <v>44</v>
@@ -9047,7 +9047,7 @@
         <v>46</v>
       </c>
       <c r="B393" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C393" s="1" t="n">
         <v>44</v>
@@ -9058,58 +9058,58 @@
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B394" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B395" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D395" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B396" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D396" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B397" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D397" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9117,13 +9117,13 @@
         <v>47</v>
       </c>
       <c r="B398" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C398" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D398" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9131,13 +9131,13 @@
         <v>47</v>
       </c>
       <c r="B399" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C399" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D399" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9145,13 +9145,13 @@
         <v>47</v>
       </c>
       <c r="B400" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C400" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D400" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9159,13 +9159,13 @@
         <v>47</v>
       </c>
       <c r="B401" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D401" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9173,69 +9173,69 @@
         <v>47</v>
       </c>
       <c r="B402" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B403" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C403" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D403" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B404" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C404" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D404" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B405" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C405" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B405" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C405" s="1" t="n">
-        <v>45</v>
-      </c>
       <c r="D405" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B406" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C406" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B406" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="C406" s="1" t="n">
-        <v>45</v>
-      </c>
       <c r="D406" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9243,13 +9243,13 @@
         <v>44</v>
       </c>
       <c r="B407" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C407" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D407" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9257,13 +9257,13 @@
         <v>44</v>
       </c>
       <c r="B408" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C408" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D408" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9271,13 +9271,13 @@
         <v>44</v>
       </c>
       <c r="B409" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C409" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D409" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9285,13 +9285,13 @@
         <v>44</v>
       </c>
       <c r="B410" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D410" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9299,69 +9299,69 @@
         <v>44</v>
       </c>
       <c r="B411" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D411" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B412" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C412" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D412" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B413" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C413" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D413" s="1" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B414" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D414" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B415" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9369,13 +9369,13 @@
         <v>48</v>
       </c>
       <c r="B416" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C416" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D416" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9383,13 +9383,13 @@
         <v>48</v>
       </c>
       <c r="B417" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C417" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D417" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9397,13 +9397,13 @@
         <v>48</v>
       </c>
       <c r="B418" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C418" s="1" t="n">
         <v>45</v>
       </c>
       <c r="D418" s="1" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9411,13 +9411,13 @@
         <v>48</v>
       </c>
       <c r="B419" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D419" s="1" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,70 +9425,69 @@
         <v>48</v>
       </c>
       <c r="B420" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D420" s="1" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B421" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F421" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M421" s="11"/>
+        <v>45</v>
+      </c>
+      <c r="D421" s="1" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B422" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F422" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
+      </c>
+      <c r="D422" s="1" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B423" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F423" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c r="D423" s="1" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B424" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="F424" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c r="D424" s="1" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,24 +9495,25 @@
         <v>49</v>
       </c>
       <c r="B425" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F425" s="6" t="s">
         <v>55</v>
       </c>
+      <c r="M425" s="11"/>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B426" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F426" s="6" t="s">
         <v>55</v>
@@ -9524,10 +9524,10 @@
         <v>49</v>
       </c>
       <c r="B427" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F427" s="6" t="s">
         <v>55</v>
@@ -9538,10 +9538,10 @@
         <v>49</v>
       </c>
       <c r="B428" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F428" s="6" t="s">
         <v>55</v>
@@ -9552,7 +9552,7 @@
         <v>49</v>
       </c>
       <c r="B429" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C429" s="1" t="n">
         <v>94</v>
@@ -9566,7 +9566,7 @@
         <v>49</v>
       </c>
       <c r="B430" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C430" s="1" t="n">
         <v>94</v>
@@ -9580,7 +9580,7 @@
         <v>49</v>
       </c>
       <c r="B431" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C431" s="1" t="n">
         <v>94</v>
@@ -9594,7 +9594,7 @@
         <v>49</v>
       </c>
       <c r="B432" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C432" s="1" t="n">
         <v>94</v>
@@ -9608,7 +9608,7 @@
         <v>49</v>
       </c>
       <c r="B433" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C433" s="1" t="n">
         <v>94</v>
@@ -9622,7 +9622,7 @@
         <v>49</v>
       </c>
       <c r="B434" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C434" s="1" t="n">
         <v>94</v>
@@ -9636,7 +9636,7 @@
         <v>49</v>
       </c>
       <c r="B435" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C435" s="1" t="n">
         <v>94</v>
@@ -9650,13 +9650,13 @@
         <v>49</v>
       </c>
       <c r="B436" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F436" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9664,13 +9664,13 @@
         <v>49</v>
       </c>
       <c r="B437" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F437" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9678,13 +9678,13 @@
         <v>49</v>
       </c>
       <c r="B438" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F438" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9692,13 +9692,13 @@
         <v>49</v>
       </c>
       <c r="B439" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F439" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9706,10 +9706,10 @@
         <v>49</v>
       </c>
       <c r="B440" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F440" s="6" t="s">
         <v>57</v>
@@ -9720,10 +9720,10 @@
         <v>49</v>
       </c>
       <c r="B441" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F441" s="6" t="s">
         <v>57</v>
@@ -9734,10 +9734,10 @@
         <v>49</v>
       </c>
       <c r="B442" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F442" s="6" t="s">
         <v>57</v>
@@ -9748,10 +9748,10 @@
         <v>49</v>
       </c>
       <c r="B443" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F443" s="6" t="s">
         <v>57</v>
@@ -9762,7 +9762,7 @@
         <v>49</v>
       </c>
       <c r="B444" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C444" s="1" t="n">
         <v>92</v>
@@ -9776,10 +9776,10 @@
         <v>49</v>
       </c>
       <c r="B445" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F445" s="6" t="s">
         <v>57</v>
@@ -9790,10 +9790,10 @@
         <v>49</v>
       </c>
       <c r="B446" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F446" s="6" t="s">
         <v>57</v>
@@ -9804,10 +9804,10 @@
         <v>49</v>
       </c>
       <c r="B447" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F447" s="6" t="s">
         <v>57</v>
@@ -9818,10 +9818,10 @@
         <v>49</v>
       </c>
       <c r="B448" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F448" s="6" t="s">
         <v>57</v>
@@ -9832,7 +9832,7 @@
         <v>49</v>
       </c>
       <c r="B449" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C449" s="1" t="n">
         <v>91</v>
@@ -9846,7 +9846,7 @@
         <v>49</v>
       </c>
       <c r="B450" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C450" s="1" t="n">
         <v>91</v>
@@ -9860,13 +9860,13 @@
         <v>49</v>
       </c>
       <c r="B451" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F451" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9874,13 +9874,13 @@
         <v>49</v>
       </c>
       <c r="B452" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F452" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9888,13 +9888,13 @@
         <v>49</v>
       </c>
       <c r="B453" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F453" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9902,13 +9902,13 @@
         <v>49</v>
       </c>
       <c r="B454" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F454" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9916,7 +9916,7 @@
         <v>49</v>
       </c>
       <c r="B455" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C455" s="1" t="n">
         <v>89</v>
@@ -9930,7 +9930,7 @@
         <v>49</v>
       </c>
       <c r="B456" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C456" s="1" t="n">
         <v>89</v>
@@ -9944,7 +9944,7 @@
         <v>49</v>
       </c>
       <c r="B457" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C457" s="1" t="n">
         <v>89</v>
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="B458" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F458" s="6" t="s">
         <v>56</v>
@@ -9972,10 +9972,10 @@
         <v>49</v>
       </c>
       <c r="B459" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F459" s="6" t="s">
         <v>56</v>
@@ -9986,10 +9986,10 @@
         <v>49</v>
       </c>
       <c r="B460" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F460" s="6" t="s">
         <v>56</v>
@@ -10000,10 +10000,10 @@
         <v>49</v>
       </c>
       <c r="B461" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F461" s="6" t="s">
         <v>56</v>
@@ -10014,7 +10014,7 @@
         <v>49</v>
       </c>
       <c r="B462" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C462" s="1" t="n">
         <v>88</v>
@@ -10028,7 +10028,7 @@
         <v>49</v>
       </c>
       <c r="B463" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C463" s="1" t="n">
         <v>88</v>
@@ -10042,7 +10042,7 @@
         <v>49</v>
       </c>
       <c r="B464" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C464" s="1" t="n">
         <v>88</v>
@@ -10056,7 +10056,7 @@
         <v>49</v>
       </c>
       <c r="B465" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C465" s="1" t="n">
         <v>88</v>
@@ -10067,58 +10067,58 @@
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B466" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F466" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B467" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F467" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B468" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F468" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B469" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F469" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10126,10 +10126,10 @@
         <v>50</v>
       </c>
       <c r="B470" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F470" s="6" t="s">
         <v>55</v>
@@ -10140,10 +10140,10 @@
         <v>50</v>
       </c>
       <c r="B471" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F471" s="6" t="s">
         <v>55</v>
@@ -10154,10 +10154,10 @@
         <v>50</v>
       </c>
       <c r="B472" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F472" s="6" t="s">
         <v>55</v>
@@ -10168,10 +10168,10 @@
         <v>50</v>
       </c>
       <c r="B473" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F473" s="6" t="s">
         <v>55</v>
@@ -10182,7 +10182,7 @@
         <v>50</v>
       </c>
       <c r="B474" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C474" s="1" t="n">
         <v>94</v>
@@ -10196,7 +10196,7 @@
         <v>50</v>
       </c>
       <c r="B475" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C475" s="1" t="n">
         <v>94</v>
@@ -10210,7 +10210,7 @@
         <v>50</v>
       </c>
       <c r="B476" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C476" s="1" t="n">
         <v>94</v>
@@ -10224,7 +10224,7 @@
         <v>50</v>
       </c>
       <c r="B477" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C477" s="1" t="n">
         <v>94</v>
@@ -10238,7 +10238,7 @@
         <v>50</v>
       </c>
       <c r="B478" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C478" s="1" t="n">
         <v>94</v>
@@ -10252,7 +10252,7 @@
         <v>50</v>
       </c>
       <c r="B479" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C479" s="1" t="n">
         <v>94</v>
@@ -10266,7 +10266,7 @@
         <v>50</v>
       </c>
       <c r="B480" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C480" s="1" t="n">
         <v>94</v>
@@ -10280,13 +10280,13 @@
         <v>50</v>
       </c>
       <c r="B481" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F481" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10294,13 +10294,13 @@
         <v>50</v>
       </c>
       <c r="B482" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F482" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10308,13 +10308,13 @@
         <v>50</v>
       </c>
       <c r="B483" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F483" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10322,13 +10322,13 @@
         <v>50</v>
       </c>
       <c r="B484" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F484" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10336,10 +10336,10 @@
         <v>50</v>
       </c>
       <c r="B485" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F485" s="6" t="s">
         <v>57</v>
@@ -10350,10 +10350,10 @@
         <v>50</v>
       </c>
       <c r="B486" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F486" s="6" t="s">
         <v>57</v>
@@ -10364,10 +10364,10 @@
         <v>50</v>
       </c>
       <c r="B487" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F487" s="6" t="s">
         <v>57</v>
@@ -10378,10 +10378,10 @@
         <v>50</v>
       </c>
       <c r="B488" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F488" s="6" t="s">
         <v>57</v>
@@ -10392,7 +10392,7 @@
         <v>50</v>
       </c>
       <c r="B489" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C489" s="1" t="n">
         <v>92</v>
@@ -10406,10 +10406,10 @@
         <v>50</v>
       </c>
       <c r="B490" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F490" s="6" t="s">
         <v>57</v>
@@ -10420,10 +10420,10 @@
         <v>50</v>
       </c>
       <c r="B491" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F491" s="6" t="s">
         <v>57</v>
@@ -10434,10 +10434,10 @@
         <v>50</v>
       </c>
       <c r="B492" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F492" s="6" t="s">
         <v>57</v>
@@ -10448,10 +10448,10 @@
         <v>50</v>
       </c>
       <c r="B493" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F493" s="6" t="s">
         <v>57</v>
@@ -10462,7 +10462,7 @@
         <v>50</v>
       </c>
       <c r="B494" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C494" s="1" t="n">
         <v>91</v>
@@ -10476,7 +10476,7 @@
         <v>50</v>
       </c>
       <c r="B495" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C495" s="1" t="n">
         <v>91</v>
@@ -10490,13 +10490,13 @@
         <v>50</v>
       </c>
       <c r="B496" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F496" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10504,13 +10504,13 @@
         <v>50</v>
       </c>
       <c r="B497" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F497" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10518,13 +10518,13 @@
         <v>50</v>
       </c>
       <c r="B498" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F498" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10532,13 +10532,13 @@
         <v>50</v>
       </c>
       <c r="B499" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F499" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10546,7 +10546,7 @@
         <v>50</v>
       </c>
       <c r="B500" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C500" s="1" t="n">
         <v>89</v>
@@ -10560,7 +10560,7 @@
         <v>50</v>
       </c>
       <c r="B501" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C501" s="1" t="n">
         <v>89</v>
@@ -10574,7 +10574,7 @@
         <v>50</v>
       </c>
       <c r="B502" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C502" s="1" t="n">
         <v>89</v>
@@ -10588,10 +10588,10 @@
         <v>50</v>
       </c>
       <c r="B503" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F503" s="6" t="s">
         <v>56</v>
@@ -10602,10 +10602,10 @@
         <v>50</v>
       </c>
       <c r="B504" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F504" s="6" t="s">
         <v>56</v>
@@ -10616,10 +10616,10 @@
         <v>50</v>
       </c>
       <c r="B505" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F505" s="6" t="s">
         <v>56</v>
@@ -10630,10 +10630,10 @@
         <v>50</v>
       </c>
       <c r="B506" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F506" s="6" t="s">
         <v>56</v>
@@ -10644,7 +10644,7 @@
         <v>50</v>
       </c>
       <c r="B507" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C507" s="1" t="n">
         <v>88</v>
@@ -10658,7 +10658,7 @@
         <v>50</v>
       </c>
       <c r="B508" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C508" s="1" t="n">
         <v>88</v>
@@ -10672,7 +10672,7 @@
         <v>50</v>
       </c>
       <c r="B509" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C509" s="1" t="n">
         <v>88</v>
@@ -10686,12 +10686,68 @@
         <v>50</v>
       </c>
       <c r="B510" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C510" s="1" t="n">
         <v>88</v>
       </c>
       <c r="F510" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A511" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B511" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C511" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F511" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A512" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B512" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C512" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F512" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A513" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B513" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="C513" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F513" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B514" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C514" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="F514" s="6" t="s">
         <v>56</v>
       </c>
     </row>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -7532,7 +7532,7 @@
         <v>95</v>
       </c>
       <c r="D268" s="7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E268" s="7" t="n">
         <v>50</v>
@@ -7552,7 +7552,7 @@
         <v>95</v>
       </c>
       <c r="D269" s="7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E269" s="7" t="n">
         <v>50</v>
@@ -7572,7 +7572,7 @@
         <v>95</v>
       </c>
       <c r="D270" s="7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E270" s="7" t="n">
         <v>40</v>
@@ -7592,7 +7592,7 @@
         <v>95</v>
       </c>
       <c r="D271" s="7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E271" s="7" t="n">
         <v>40</v>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -2022,15 +2022,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="D16" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>750</v>
-      </c>
-      <c r="F16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="n">
+        <v>375</v>
+      </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2458,7 +2456,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7" t="n">
@@ -2475,7 +2473,7 @@
         <v>6</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="n">
@@ -2492,7 +2490,7 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7" t="n">
@@ -2509,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="n">
@@ -2526,7 +2524,7 @@
         <v>9</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="n">

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="aylik_gosterge_puanlari" sheetId="1" state="visible" r:id="rId3"/>
@@ -177,7 +177,7 @@
     <t xml:space="preserve">Vekil İ-H</t>
   </si>
   <si>
-    <t xml:space="preserve">Vekil M-K</t>
+    <t xml:space="preserve">Vekil M.K</t>
   </si>
   <si>
     <t xml:space="preserve">oht_orani</t>
@@ -258,6 +258,9 @@
     <t xml:space="preserve">İmam-Hatip</t>
   </si>
   <si>
+    <t xml:space="preserve">Baş Müezzin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Müezzin-Kayyım</t>
   </si>
   <si>
@@ -307,9 +310,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ayniyat Saymanı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baş Müezzin</t>
   </si>
   <si>
     <t xml:space="preserve">Cami Rehberi</t>
@@ -11526,7 +11526,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.68"/>
@@ -11776,7 +11776,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>77</v>
@@ -11790,13 +11790,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>32</v>
@@ -11804,13 +11804,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>32</v>
@@ -11818,10 +11818,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>69</v>
@@ -11832,13 +11832,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>24</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>32</v>
@@ -11846,10 +11846,10 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>63</v>
@@ -11860,10 +11860,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>63</v>
@@ -11874,13 +11874,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>32</v>
@@ -11888,13 +11888,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>32</v>
@@ -11902,13 +11902,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>32</v>
@@ -11916,13 +11916,13 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>32</v>
@@ -11930,90 +11930,101 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>367</v>
+        <v>155</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>367</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="14"/>
+      <c r="D35" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="14"/>
@@ -12104,6 +12115,9 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D65" s="14"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D66" s="14"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12121,7 +12135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="13.26"/>
@@ -12147,7 +12161,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>63</v>
@@ -12159,7 +12173,7 @@
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>63</v>
@@ -12171,7 +12185,7 @@
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>63</v>
@@ -12186,7 +12200,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>32</v>
@@ -12195,7 +12209,7 @@
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>63</v>
@@ -12207,7 +12221,7 @@
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>70</v>
@@ -12219,7 +12233,7 @@
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>70</v>
@@ -12231,10 +12245,10 @@
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>32</v>
@@ -12243,10 +12257,10 @@
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>32</v>
@@ -12255,7 +12269,7 @@
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>63</v>
@@ -12267,10 +12281,10 @@
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>32</v>
@@ -12279,10 +12293,10 @@
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>32</v>
@@ -12291,7 +12305,7 @@
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>63</v>
@@ -12303,7 +12317,7 @@
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>63</v>
@@ -12315,7 +12329,7 @@
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>63</v>
@@ -12327,10 +12341,10 @@
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>32</v>
@@ -12339,10 +12353,10 @@
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>32</v>
@@ -12351,10 +12365,10 @@
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>32</v>
@@ -12363,7 +12377,7 @@
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>63</v>
@@ -12375,7 +12389,7 @@
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>63</v>
@@ -12387,10 +12401,10 @@
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>32</v>
@@ -12399,10 +12413,10 @@
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>32</v>
@@ -12411,10 +12425,10 @@
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>32</v>
@@ -12423,7 +12437,7 @@
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>63</v>
@@ -12435,10 +12449,10 @@
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>32</v>
@@ -12447,7 +12461,7 @@
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>69</v>
@@ -12459,7 +12473,7 @@
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>69</v>
@@ -12471,7 +12485,7 @@
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>69</v>
@@ -12483,10 +12497,10 @@
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>32</v>
@@ -12495,7 +12509,7 @@
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>63</v>
@@ -12506,21 +12520,9 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
-      <c r="B32" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/maas_verileri.xlsx
+++ b/maas_verileri.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="128">
   <si>
     <t xml:space="preserve">yil</t>
   </si>
@@ -500,7 +500,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -562,10 +562,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2965,7 +2961,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M528"/>
+  <dimension ref="A1:M552"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="24.41"/>
@@ -6060,19 +6056,19 @@
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B182" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C182" s="7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D182" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E182" s="7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F182" s="11" t="s">
         <v>60</v>
@@ -6080,19 +6076,19 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B183" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C183" s="7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D183" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E183" s="7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F183" s="11" t="s">
         <v>60</v>
@@ -6100,19 +6096,19 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B184" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C184" s="7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D184" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E184" s="7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F184" s="11" t="s">
         <v>60</v>
@@ -6120,19 +6116,19 @@
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B185" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C185" s="7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D185" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E185" s="7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F185" s="11" t="s">
         <v>60</v>
@@ -6140,10 +6136,10 @@
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B186" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C186" s="7" t="n">
         <v>94</v>
@@ -6152,7 +6148,7 @@
         <v>70</v>
       </c>
       <c r="E186" s="7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F186" s="11" t="s">
         <v>60</v>
@@ -6160,10 +6156,10 @@
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B187" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C187" s="7" t="n">
         <v>94</v>
@@ -6172,7 +6168,7 @@
         <v>70</v>
       </c>
       <c r="E187" s="7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F187" s="11" t="s">
         <v>60</v>
@@ -6180,7 +6176,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B188" s="7" t="n">
         <v>1</v>
@@ -6191,14 +6187,16 @@
       <c r="D188" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E188" s="7"/>
+      <c r="E188" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F188" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B189" s="7" t="n">
         <v>2</v>
@@ -6209,14 +6207,16 @@
       <c r="D189" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E189" s="7"/>
+      <c r="E189" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F189" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B190" s="7" t="n">
         <v>3</v>
@@ -6227,14 +6227,16 @@
       <c r="D190" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E190" s="7"/>
+      <c r="E190" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F190" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B191" s="7" t="n">
         <v>4</v>
@@ -6245,14 +6247,16 @@
       <c r="D191" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E191" s="7"/>
+      <c r="E191" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F191" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B192" s="7" t="n">
         <v>5</v>
@@ -6263,14 +6267,16 @@
       <c r="D192" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E192" s="7"/>
+      <c r="E192" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F192" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B193" s="7" t="n">
         <v>6</v>
@@ -6281,14 +6287,16 @@
       <c r="D193" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E193" s="7"/>
+      <c r="E193" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F193" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B194" s="7" t="n">
         <v>7</v>
@@ -6299,14 +6307,16 @@
       <c r="D194" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E194" s="7"/>
+      <c r="E194" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F194" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B195" s="7" t="n">
         <v>8</v>
@@ -6317,14 +6327,16 @@
       <c r="D195" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E195" s="7"/>
+      <c r="E195" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F195" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B196" s="7" t="n">
         <v>9</v>
@@ -6335,14 +6347,16 @@
       <c r="D196" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E196" s="7"/>
+      <c r="E196" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F196" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B197" s="7" t="n">
         <v>10</v>
@@ -6353,7 +6367,9 @@
       <c r="D197" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E197" s="7"/>
+      <c r="E197" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F197" s="11" t="s">
         <v>60</v>
       </c>
@@ -6363,10 +6379,10 @@
         <v>40</v>
       </c>
       <c r="B198" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C198" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D198" s="7" t="n">
         <v>70</v>
@@ -6381,10 +6397,10 @@
         <v>40</v>
       </c>
       <c r="B199" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C199" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D199" s="7" t="n">
         <v>70</v>
@@ -6399,10 +6415,10 @@
         <v>40</v>
       </c>
       <c r="B200" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C200" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D200" s="7" t="n">
         <v>70</v>
@@ -6417,10 +6433,10 @@
         <v>40</v>
       </c>
       <c r="B201" s="7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C201" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D201" s="7" t="n">
         <v>70</v>
@@ -6435,7 +6451,7 @@
         <v>40</v>
       </c>
       <c r="B202" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C202" s="7" t="n">
         <v>94</v>
@@ -6453,17 +6469,17 @@
         <v>40</v>
       </c>
       <c r="B203" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C203" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D203" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6471,17 +6487,17 @@
         <v>40</v>
       </c>
       <c r="B204" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C204" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D204" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E204" s="7"/>
       <c r="F204" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6489,17 +6505,17 @@
         <v>40</v>
       </c>
       <c r="B205" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C205" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D205" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6507,17 +6523,17 @@
         <v>40</v>
       </c>
       <c r="B206" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C206" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D206" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E206" s="7"/>
       <c r="F206" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6525,17 +6541,17 @@
         <v>40</v>
       </c>
       <c r="B207" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C207" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D207" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,17 +6559,17 @@
         <v>40</v>
       </c>
       <c r="B208" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C208" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D208" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6561,17 +6577,17 @@
         <v>40</v>
       </c>
       <c r="B209" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C209" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D209" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6579,17 +6595,17 @@
         <v>40</v>
       </c>
       <c r="B210" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C210" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D210" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6597,17 +6613,17 @@
         <v>40</v>
       </c>
       <c r="B211" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C211" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D211" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,17 +6631,17 @@
         <v>40</v>
       </c>
       <c r="B212" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D212" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E212" s="7"/>
       <c r="F212" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6633,10 +6649,10 @@
         <v>40</v>
       </c>
       <c r="B213" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C213" s="7" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D213" s="7" t="n">
         <v>70</v>
@@ -6651,10 +6667,10 @@
         <v>40</v>
       </c>
       <c r="B214" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C214" s="7" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D214" s="7" t="n">
         <v>70</v>
@@ -6669,10 +6685,10 @@
         <v>40</v>
       </c>
       <c r="B215" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C215" s="7" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D215" s="7" t="n">
         <v>70</v>
@@ -6687,10 +6703,10 @@
         <v>40</v>
       </c>
       <c r="B216" s="7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C216" s="7" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D216" s="7" t="n">
         <v>70</v>
@@ -6705,10 +6721,10 @@
         <v>40</v>
       </c>
       <c r="B217" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C217" s="7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D217" s="7" t="n">
         <v>70</v>
@@ -6723,17 +6739,17 @@
         <v>40</v>
       </c>
       <c r="B218" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C218" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D218" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6741,17 +6757,17 @@
         <v>40</v>
       </c>
       <c r="B219" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C219" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D219" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6759,17 +6775,17 @@
         <v>40</v>
       </c>
       <c r="B220" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C220" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D220" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6777,17 +6793,17 @@
         <v>40</v>
       </c>
       <c r="B221" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C221" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D221" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6795,17 +6811,17 @@
         <v>40</v>
       </c>
       <c r="B222" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C222" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D222" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6813,17 +6829,17 @@
         <v>40</v>
       </c>
       <c r="B223" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C223" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D223" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6831,17 +6847,17 @@
         <v>40</v>
       </c>
       <c r="B224" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C224" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D224" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6849,17 +6865,17 @@
         <v>40</v>
       </c>
       <c r="B225" s="7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C225" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D225" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6867,17 +6883,17 @@
         <v>40</v>
       </c>
       <c r="B226" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C226" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D226" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6885,17 +6901,17 @@
         <v>40</v>
       </c>
       <c r="B227" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C227" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D227" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6903,10 +6919,10 @@
         <v>40</v>
       </c>
       <c r="B228" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C228" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D228" s="7" t="n">
         <v>70</v>
@@ -6921,10 +6937,10 @@
         <v>40</v>
       </c>
       <c r="B229" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C229" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D229" s="7" t="n">
         <v>70</v>
@@ -6939,10 +6955,10 @@
         <v>40</v>
       </c>
       <c r="B230" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C230" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D230" s="7" t="n">
         <v>70</v>
@@ -6957,10 +6973,10 @@
         <v>40</v>
       </c>
       <c r="B231" s="7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C231" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D231" s="7" t="n">
         <v>70</v>
@@ -6975,10 +6991,10 @@
         <v>40</v>
       </c>
       <c r="B232" s="7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C232" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D232" s="7" t="n">
         <v>70</v>
@@ -6990,270 +7006,270 @@
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B233" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C233" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D233" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E233" s="7" t="n">
-        <v>25</v>
-      </c>
+      <c r="E233" s="7"/>
       <c r="F233" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B234" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C234" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D234" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E234" s="7" t="n">
-        <v>25</v>
-      </c>
+      <c r="E234" s="7"/>
       <c r="F234" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B235" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C235" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D235" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E235" s="7" t="n">
-        <v>20</v>
-      </c>
+      <c r="E235" s="7"/>
       <c r="F235" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B236" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C236" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D236" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E236" s="7" t="n">
-        <v>20</v>
-      </c>
+      <c r="E236" s="7"/>
       <c r="F236" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B237" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C237" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D237" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B238" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C238" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D238" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B239" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C239" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D239" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B240" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C240" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B241" s="7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C241" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B242" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C242" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B243" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C243" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D243" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E243" s="7"/>
+      <c r="E243" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F243" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B244" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C244" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D244" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E244" s="7"/>
+      <c r="E244" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F244" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B245" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C245" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D245" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E245" s="7"/>
+      <c r="E245" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F245" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B246" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C246" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D246" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E246" s="7"/>
+      <c r="E246" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F246" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B247" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C247" s="7" t="n">
         <v>94</v>
@@ -7261,17 +7277,19 @@
       <c r="D247" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E247" s="7"/>
+      <c r="E247" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F247" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B248" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C248" s="7" t="n">
         <v>94</v>
@@ -7279,17 +7297,19 @@
       <c r="D248" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E248" s="7"/>
+      <c r="E248" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F248" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B249" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C249" s="7" t="n">
         <v>94</v>
@@ -7297,17 +7317,19 @@
       <c r="D249" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E249" s="7"/>
+      <c r="E249" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F249" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B250" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C250" s="7" t="n">
         <v>94</v>
@@ -7315,17 +7337,19 @@
       <c r="D250" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E250" s="7"/>
+      <c r="E250" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F250" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B251" s="7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C251" s="7" t="n">
         <v>94</v>
@@ -7333,27 +7357,31 @@
       <c r="D251" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E251" s="7"/>
+      <c r="E251" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F251" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B252" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C252" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D252" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="E252" s="7"/>
+      <c r="E252" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F252" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7361,17 +7389,17 @@
         <v>46</v>
       </c>
       <c r="B253" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C253" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D253" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E253" s="7"/>
       <c r="F253" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7379,17 +7407,17 @@
         <v>46</v>
       </c>
       <c r="B254" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C254" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D254" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7397,17 +7425,17 @@
         <v>46</v>
       </c>
       <c r="B255" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C255" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D255" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7415,17 +7443,17 @@
         <v>46</v>
       </c>
       <c r="B256" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C256" s="7" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D256" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7433,17 +7461,17 @@
         <v>46</v>
       </c>
       <c r="B257" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C257" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D257" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7451,17 +7479,17 @@
         <v>46</v>
       </c>
       <c r="B258" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C258" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D258" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7469,17 +7497,17 @@
         <v>46</v>
       </c>
       <c r="B259" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C259" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D259" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7487,17 +7515,17 @@
         <v>46</v>
       </c>
       <c r="B260" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D260" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7505,17 +7533,17 @@
         <v>46</v>
       </c>
       <c r="B261" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C261" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D261" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7523,17 +7551,17 @@
         <v>46</v>
       </c>
       <c r="B262" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C262" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D262" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7541,17 +7569,17 @@
         <v>46</v>
       </c>
       <c r="B263" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C263" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D263" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7559,17 +7587,17 @@
         <v>46</v>
       </c>
       <c r="B264" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C264" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D264" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7577,17 +7605,17 @@
         <v>46</v>
       </c>
       <c r="B265" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C265" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D265" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7595,17 +7623,17 @@
         <v>46</v>
       </c>
       <c r="B266" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C266" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D266" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7613,17 +7641,17 @@
         <v>46</v>
       </c>
       <c r="B267" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C267" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D267" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7631,17 +7659,17 @@
         <v>46</v>
       </c>
       <c r="B268" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268" s="7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D268" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7649,17 +7677,17 @@
         <v>46</v>
       </c>
       <c r="B269" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C269" s="7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D269" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7667,17 +7695,17 @@
         <v>46</v>
       </c>
       <c r="B270" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C270" s="7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D270" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7685,17 +7713,17 @@
         <v>46</v>
       </c>
       <c r="B271" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271" s="7" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D271" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7703,17 +7731,17 @@
         <v>46</v>
       </c>
       <c r="B272" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C272" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D272" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7721,17 +7749,17 @@
         <v>46</v>
       </c>
       <c r="B273" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C273" s="7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D273" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7739,17 +7767,17 @@
         <v>46</v>
       </c>
       <c r="B274" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C274" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D274" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7757,17 +7785,17 @@
         <v>46</v>
       </c>
       <c r="B275" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C275" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D275" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7775,17 +7803,17 @@
         <v>46</v>
       </c>
       <c r="B276" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C276" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D276" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,17 +7821,17 @@
         <v>46</v>
       </c>
       <c r="B277" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C277" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D277" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7811,17 +7839,17 @@
         <v>46</v>
       </c>
       <c r="B278" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C278" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D278" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,17 +7857,17 @@
         <v>46</v>
       </c>
       <c r="B279" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C279" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D279" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7847,17 +7875,17 @@
         <v>46</v>
       </c>
       <c r="B280" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C280" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D280" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7865,409 +7893,393 @@
         <v>46</v>
       </c>
       <c r="B281" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C281" s="7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D281" s="7" t="n">
         <v>70</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B282" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C282" s="7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D282" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E282" s="7" t="n">
-        <v>50</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E282" s="7"/>
       <c r="F282" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B283" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C283" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D283" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E283" s="7" t="n">
-        <v>50</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E283" s="7"/>
       <c r="F283" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B284" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C284" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D284" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E284" s="7" t="n">
-        <v>40</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E284" s="7"/>
       <c r="F284" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B285" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C285" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D285" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E285" s="7" t="n">
-        <v>40</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E285" s="7"/>
       <c r="F285" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B286" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C286" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D286" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E286" s="7" t="n">
-        <v>25</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E286" s="7"/>
       <c r="F286" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B287" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C287" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D287" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E287" s="7" t="n">
-        <v>25</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E287" s="7"/>
       <c r="F287" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B288" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C288" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D288" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E288" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E288" s="7"/>
       <c r="F288" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B289" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C289" s="7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D289" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E289" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E289" s="7"/>
       <c r="F289" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B290" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C290" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D290" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E290" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E290" s="7"/>
       <c r="F290" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B291" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C291" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D291" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E291" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E291" s="7"/>
       <c r="F291" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B292" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C292" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D292" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E292" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E292" s="7"/>
       <c r="F292" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B293" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C293" s="7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D293" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="E293" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E293" s="7"/>
       <c r="F293" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B294" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C294" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D294" s="7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B295" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C295" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D295" s="7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B296" s="7" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C296" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D296" s="7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B297" s="7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C297" s="7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D297" s="7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B298" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C298" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D298" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E298" s="7"/>
+      <c r="E298" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F298" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B299" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C299" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D299" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E299" s="7"/>
+      <c r="E299" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F299" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B300" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C300" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D300" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E300" s="7"/>
+      <c r="E300" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F300" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B301" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C301" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D301" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E301" s="7"/>
+      <c r="E301" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F301" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B302" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C302" s="7" t="n">
         <v>94</v>
@@ -8275,17 +8287,19 @@
       <c r="D302" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E302" s="7"/>
+      <c r="E302" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F302" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B303" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C303" s="7" t="n">
         <v>94</v>
@@ -8293,17 +8307,19 @@
       <c r="D303" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E303" s="7"/>
+      <c r="E303" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F303" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B304" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C304" s="7" t="n">
         <v>94</v>
@@ -8311,17 +8327,19 @@
       <c r="D304" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E304" s="7"/>
+      <c r="E304" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F304" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B305" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C305" s="7" t="n">
         <v>94</v>
@@ -8329,17 +8347,19 @@
       <c r="D305" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E305" s="7"/>
+      <c r="E305" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F305" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B306" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C306" s="7" t="n">
         <v>94</v>
@@ -8347,17 +8367,19 @@
       <c r="D306" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E306" s="7"/>
+      <c r="E306" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F306" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B307" s="7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C307" s="7" t="n">
         <v>94</v>
@@ -8365,189 +8387,211 @@
       <c r="D307" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E307" s="7"/>
+      <c r="E307" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F307" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B308" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C308" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D308" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E308" s="7"/>
+      <c r="E308" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F308" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B309" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C309" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D309" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E309" s="7"/>
+      <c r="E309" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F309" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B310" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C310" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D310" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E310" s="7"/>
+      <c r="E310" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F310" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B311" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C311" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D311" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E311" s="7"/>
+      <c r="E311" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F311" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B312" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C312" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D312" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E312" s="7"/>
+      <c r="E312" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F312" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B313" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C313" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D313" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E313" s="7"/>
+      <c r="E313" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F313" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B314" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C314" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D314" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E314" s="7"/>
+      <c r="E314" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F314" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B315" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C315" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D315" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E315" s="7"/>
+      <c r="E315" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F315" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B316" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C316" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D316" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E316" s="7"/>
+      <c r="E316" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F316" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B317" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C317" s="7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D317" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="E317" s="7"/>
+      <c r="E317" s="7" t="n">
+        <v>20</v>
+      </c>
       <c r="F317" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8555,17 +8599,17 @@
         <v>44</v>
       </c>
       <c r="B318" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C318" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D318" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8573,17 +8617,17 @@
         <v>44</v>
       </c>
       <c r="B319" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C319" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D319" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8591,17 +8635,17 @@
         <v>44</v>
       </c>
       <c r="B320" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C320" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D320" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8609,17 +8653,17 @@
         <v>44</v>
       </c>
       <c r="B321" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C321" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D321" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8627,17 +8671,17 @@
         <v>44</v>
       </c>
       <c r="B322" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C322" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D322" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8645,17 +8689,17 @@
         <v>44</v>
       </c>
       <c r="B323" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C323" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D323" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8663,17 +8707,17 @@
         <v>44</v>
       </c>
       <c r="B324" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C324" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D324" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8681,17 +8725,17 @@
         <v>44</v>
       </c>
       <c r="B325" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C325" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D325" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8699,17 +8743,17 @@
         <v>44</v>
       </c>
       <c r="B326" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C326" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D326" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8717,17 +8761,17 @@
         <v>44</v>
       </c>
       <c r="B327" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C327" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D327" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8735,17 +8779,17 @@
         <v>44</v>
       </c>
       <c r="B328" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C328" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D328" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8753,17 +8797,17 @@
         <v>44</v>
       </c>
       <c r="B329" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C329" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D329" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E329" s="7"/>
       <c r="F329" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8771,17 +8815,17 @@
         <v>44</v>
       </c>
       <c r="B330" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C330" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D330" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8789,17 +8833,17 @@
         <v>44</v>
       </c>
       <c r="B331" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C331" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D331" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8807,17 +8851,17 @@
         <v>44</v>
       </c>
       <c r="B332" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C332" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D332" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8825,17 +8869,17 @@
         <v>44</v>
       </c>
       <c r="B333" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C333" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D333" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E333" s="7"/>
       <c r="F333" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8843,17 +8887,17 @@
         <v>44</v>
       </c>
       <c r="B334" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C334" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D334" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8861,17 +8905,17 @@
         <v>44</v>
       </c>
       <c r="B335" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C335" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D335" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8879,17 +8923,17 @@
         <v>44</v>
       </c>
       <c r="B336" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C336" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D336" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8897,17 +8941,17 @@
         <v>44</v>
       </c>
       <c r="B337" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C337" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D337" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8915,535 +8959,607 @@
         <v>44</v>
       </c>
       <c r="B338" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C338" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D338" s="7" t="n">
         <v>65</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B339" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C339" s="7" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D339" s="7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E339" s="7"/>
+      <c r="F339" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B340" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C340" s="7" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D340" s="7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E340" s="7"/>
+      <c r="F340" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B341" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C341" s="7" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D341" s="7" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E341" s="7"/>
+      <c r="F341" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B342" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C342" s="7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D342" s="7" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E342" s="7"/>
+      <c r="F342" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B343" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C343" s="7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D343" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E343" s="7"/>
+      <c r="F343" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B344" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C344" s="7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D344" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E344" s="7"/>
+      <c r="F344" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B345" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C345" s="7" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D345" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E345" s="7"/>
+      <c r="F345" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B346" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C346" s="7" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D346" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E346" s="7"/>
+      <c r="F346" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B347" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C347" s="7" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D347" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E347" s="7"/>
+      <c r="F347" s="11" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B348" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C348" s="7" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D348" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E348" s="7"/>
+      <c r="F348" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B349" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C349" s="7" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D349" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E349" s="7"/>
+      <c r="F349" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B350" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C350" s="7" t="n">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D350" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E350" s="7"/>
+      <c r="F350" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B351" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C351" s="7" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D351" s="7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E351" s="7"/>
+      <c r="F351" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B352" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C352" s="7" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D352" s="7" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E352" s="7"/>
+      <c r="F352" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B353" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C353" s="7" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D353" s="7" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E353" s="7"/>
+      <c r="F353" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B354" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C354" s="7" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D354" s="7" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E354" s="7"/>
+      <c r="F354" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B355" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C355" s="7" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D355" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E355" s="7"/>
+      <c r="F355" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B356" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C356" s="7" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D356" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E356" s="7"/>
+      <c r="F356" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B357" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C357" s="7" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="D357" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E357" s="7"/>
+      <c r="F357" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B358" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C358" s="7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D358" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E358" s="7"/>
+      <c r="F358" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B359" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C359" s="7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D359" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E359" s="7"/>
+      <c r="F359" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B360" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C360" s="7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D360" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E360" s="7"/>
+      <c r="F360" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B361" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C361" s="7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D361" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E361" s="7"/>
+      <c r="F361" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B362" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C362" s="7" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D362" s="7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E362" s="7"/>
+      <c r="F362" s="11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B363" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C363" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D363" s="7" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E363" s="7"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B364" s="7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C364" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D364" s="7" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E364" s="7"/>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B365" s="7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C365" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D365" s="7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E365" s="7"/>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B366" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C366" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D366" s="7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E366" s="7"/>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B367" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C367" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D367" s="7" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E367" s="7"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B368" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C368" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D368" s="7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E368" s="7"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B369" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C369" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D369" s="7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E369" s="7"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B370" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C370" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D370" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E370" s="7"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B371" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C371" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D371" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E371" s="7"/>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B372" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C372" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D372" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E372" s="7"/>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="11" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B373" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C373" s="7" t="n">
         <v>48</v>
@@ -9455,25 +9571,25 @@
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B374" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C374" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D374" s="7" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E374" s="7"/>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B375" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C375" s="7" t="n">
         <v>49</v>
@@ -9485,25 +9601,25 @@
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B376" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C376" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D376" s="7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E376" s="7"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B377" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C377" s="7" t="n">
         <v>49</v>
@@ -9515,25 +9631,25 @@
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B378" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C378" s="7" t="n">
         <v>49</v>
       </c>
       <c r="D378" s="7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E378" s="7"/>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B379" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C379" s="7" t="n">
         <v>49</v>
@@ -9545,10 +9661,10 @@
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B380" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C380" s="7" t="n">
         <v>49</v>
@@ -9560,580 +9676,580 @@
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B381" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C381" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D381" s="7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E381" s="7"/>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B382" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C382" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B382" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C382" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D382" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E382" s="7"/>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B383" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C383" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B383" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C383" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D383" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E383" s="7"/>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B384" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C384" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B384" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C384" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D384" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E384" s="7"/>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B385" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C385" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B385" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C385" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D385" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E385" s="7"/>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B386" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C386" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B386" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C386" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D386" s="7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E386" s="7"/>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B387" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C387" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B387" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C387" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D387" s="7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E387" s="7"/>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B388" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C388" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B388" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C388" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D388" s="7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E388" s="7"/>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B389" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C389" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B389" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C389" s="7" t="n">
-        <v>44</v>
-      </c>
       <c r="D389" s="7" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E389" s="7"/>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B390" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C390" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D390" s="7" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E390" s="7"/>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B391" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D391" s="7" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E391" s="7"/>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B392" s="7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C392" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D392" s="7" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E392" s="7"/>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B393" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D393" s="7" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E393" s="7"/>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B394" s="7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C394" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D394" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E394" s="7"/>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B395" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D395" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E395" s="7"/>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="11" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B396" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C396" s="7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D396" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E396" s="7"/>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B397" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D397" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E397" s="7"/>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B398" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B398" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C398" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D398" s="7" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E398" s="7"/>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B399" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C399" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B399" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C399" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D399" s="7" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E399" s="7"/>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B400" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C400" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B400" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C400" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D400" s="7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E400" s="7"/>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B401" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C401" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B401" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C401" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D401" s="7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E401" s="7"/>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B402" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C402" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B402" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C402" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D402" s="7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E402" s="7"/>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B403" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C403" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B403" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C403" s="7" t="n">
-        <v>45</v>
-      </c>
       <c r="D403" s="7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E403" s="7"/>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B404" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C404" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="B404" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C404" s="7" t="n">
-        <v>44</v>
-      </c>
       <c r="D404" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E404" s="7"/>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B405" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D405" s="7" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E405" s="7"/>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B406" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C406" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D406" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E406" s="7"/>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B407" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D407" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E407" s="7"/>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B408" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C408" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D408" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E408" s="7"/>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B409" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C409" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D409" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E409" s="7"/>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B410" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C410" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D410" s="7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E410" s="7"/>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B411" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C411" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D411" s="7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E411" s="7"/>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B412" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C412" s="7" t="n">
         <v>45</v>
       </c>
       <c r="D412" s="7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E412" s="7"/>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B413" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C413" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D413" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E413" s="7"/>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B414" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C414" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D414" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E414" s="7"/>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B415" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C415" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D415" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E415" s="7"/>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B416" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C416" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D416" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E416" s="7"/>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B417" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C417" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D417" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E417" s="7"/>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B418" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C418" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D418" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E418" s="7"/>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B419" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C419" s="7" t="n">
         <v>44</v>
@@ -10145,10 +10261,10 @@
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B420" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C420" s="7" t="n">
         <v>44</v>
@@ -10160,7 +10276,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B421" s="7" t="n">
         <v>1</v>
@@ -10175,7 +10291,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B422" s="7" t="n">
         <v>2</v>
@@ -10190,7 +10306,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B423" s="7" t="n">
         <v>3</v>
@@ -10205,7 +10321,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B424" s="7" t="n">
         <v>4</v>
@@ -10220,7 +10336,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B425" s="7" t="n">
         <v>5</v>
@@ -10235,7 +10351,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B426" s="7" t="n">
         <v>6</v>
@@ -10250,7 +10366,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B427" s="7" t="n">
         <v>7</v>
@@ -10265,7 +10381,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B428" s="7" t="n">
         <v>8</v>
@@ -10280,7 +10396,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B429" s="7" t="n">
         <v>9</v>
@@ -10295,554 +10411,530 @@
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B430" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C430" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D430" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E430" s="7"/>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B431" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C431" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D431" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E431" s="7"/>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B432" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C432" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D432" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E432" s="7"/>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B433" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C433" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D433" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E433" s="7"/>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B434" s="7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C434" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D434" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E434" s="7"/>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B435" s="7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C435" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D435" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E435" s="7"/>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B436" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C436" s="7" t="n">
         <v>45</v>
       </c>
       <c r="D436" s="7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E436" s="7"/>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B437" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C437" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D437" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E437" s="7"/>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B438" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C438" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D438" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E438" s="7"/>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B439" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C439" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D439" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D439" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E439" s="7"/>
-      <c r="F439" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M439" s="13"/>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B440" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C440" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D440" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D440" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E440" s="7"/>
-      <c r="F440" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B441" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C441" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D441" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D441" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E441" s="7"/>
-      <c r="F441" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B442" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C442" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="D442" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D442" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E442" s="7"/>
-      <c r="F442" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B443" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C443" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D443" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D443" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E443" s="7"/>
-      <c r="F443" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B444" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C444" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D444" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D444" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E444" s="7"/>
-      <c r="F444" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B445" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C445" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D445" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D445" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E445" s="7"/>
-      <c r="F445" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B446" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C446" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D446" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D446" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E446" s="7"/>
-      <c r="F446" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B447" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C447" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D447" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D447" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E447" s="7"/>
-      <c r="F447" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B448" s="7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C448" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D448" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D448" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E448" s="7"/>
-      <c r="F448" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B449" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C449" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D449" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D449" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E449" s="7"/>
-      <c r="F449" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B450" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C450" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D450" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D450" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E450" s="7"/>
-      <c r="F450" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B451" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C451" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D451" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D451" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E451" s="7"/>
-      <c r="F451" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B452" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C452" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D452" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D452" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E452" s="7"/>
-      <c r="F452" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B453" s="7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C453" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D453" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D453" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E453" s="7"/>
-      <c r="F453" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B454" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C454" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="D454" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D454" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E454" s="7"/>
-      <c r="F454" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B455" s="7" t="n">
         <v>2</v>
       </c>
       <c r="C455" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="D455" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D455" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E455" s="7"/>
-      <c r="F455" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B456" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C456" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="D456" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D456" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E456" s="7"/>
-      <c r="F456" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B457" s="7" t="n">
         <v>4</v>
       </c>
       <c r="C457" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="D457" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D457" s="7" t="n">
+        <v>90</v>
+      </c>
       <c r="E457" s="7"/>
-      <c r="F457" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B458" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C458" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D458" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D458" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E458" s="7"/>
-      <c r="F458" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B459" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C459" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D459" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D459" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E459" s="7"/>
-      <c r="F459" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B460" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C460" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D460" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="D460" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="E460" s="7"/>
-      <c r="F460" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B461" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C461" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D461" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D461" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E461" s="7"/>
-      <c r="F461" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B462" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C462" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D462" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="D462" s="7" t="n">
+        <v>70</v>
+      </c>
       <c r="E462" s="7"/>
-      <c r="F462" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B463" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C463" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D463" s="7"/>
       <c r="E463" s="7"/>
       <c r="F463" s="11" t="s">
-        <v>62</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="M463" s="13"/>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B464" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C464" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D464" s="7"/>
       <c r="E464" s="7"/>
       <c r="F464" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10850,15 +10942,15 @@
         <v>52</v>
       </c>
       <c r="B465" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C465" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D465" s="7"/>
       <c r="E465" s="7"/>
       <c r="F465" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10866,15 +10958,15 @@
         <v>52</v>
       </c>
       <c r="B466" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C466" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D466" s="7"/>
       <c r="E466" s="7"/>
       <c r="F466" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10882,15 +10974,15 @@
         <v>52</v>
       </c>
       <c r="B467" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C467" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D467" s="7"/>
       <c r="E467" s="7"/>
       <c r="F467" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10898,15 +10990,15 @@
         <v>52</v>
       </c>
       <c r="B468" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C468" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D468" s="7"/>
       <c r="E468" s="7"/>
       <c r="F468" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10914,15 +11006,15 @@
         <v>52</v>
       </c>
       <c r="B469" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C469" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D469" s="7"/>
       <c r="E469" s="7"/>
       <c r="F469" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10930,15 +11022,15 @@
         <v>52</v>
       </c>
       <c r="B470" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C470" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D470" s="7"/>
       <c r="E470" s="7"/>
       <c r="F470" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10946,15 +11038,15 @@
         <v>52</v>
       </c>
       <c r="B471" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C471" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D471" s="7"/>
       <c r="E471" s="7"/>
       <c r="F471" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10962,15 +11054,15 @@
         <v>52</v>
       </c>
       <c r="B472" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C472" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D472" s="7"/>
       <c r="E472" s="7"/>
       <c r="F472" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10978,15 +11070,15 @@
         <v>52</v>
       </c>
       <c r="B473" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C473" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D473" s="7"/>
       <c r="E473" s="7"/>
       <c r="F473" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10994,15 +11086,15 @@
         <v>52</v>
       </c>
       <c r="B474" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C474" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D474" s="7"/>
       <c r="E474" s="7"/>
       <c r="F474" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11010,15 +11102,15 @@
         <v>52</v>
       </c>
       <c r="B475" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C475" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D475" s="7"/>
       <c r="E475" s="7"/>
       <c r="F475" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11026,15 +11118,15 @@
         <v>52</v>
       </c>
       <c r="B476" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C476" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D476" s="7"/>
       <c r="E476" s="7"/>
       <c r="F476" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11042,15 +11134,15 @@
         <v>52</v>
       </c>
       <c r="B477" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C477" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D477" s="7"/>
       <c r="E477" s="7"/>
       <c r="F477" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11058,15 +11150,15 @@
         <v>52</v>
       </c>
       <c r="B478" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C478" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D478" s="7"/>
       <c r="E478" s="7"/>
       <c r="F478" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11074,15 +11166,15 @@
         <v>52</v>
       </c>
       <c r="B479" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C479" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D479" s="7"/>
       <c r="E479" s="7"/>
       <c r="F479" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11090,15 +11182,15 @@
         <v>52</v>
       </c>
       <c r="B480" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C480" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D480" s="7"/>
       <c r="E480" s="7"/>
       <c r="F480" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11106,15 +11198,15 @@
         <v>52</v>
       </c>
       <c r="B481" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C481" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D481" s="7"/>
       <c r="E481" s="7"/>
       <c r="F481" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11122,15 +11214,15 @@
         <v>52</v>
       </c>
       <c r="B482" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C482" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D482" s="7"/>
       <c r="E482" s="7"/>
       <c r="F482" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11138,399 +11230,399 @@
         <v>52</v>
       </c>
       <c r="B483" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C483" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D483" s="7"/>
       <c r="E483" s="7"/>
       <c r="F483" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B484" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C484" s="7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D484" s="7"/>
       <c r="E484" s="7"/>
       <c r="F484" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B485" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C485" s="7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D485" s="7"/>
       <c r="E485" s="7"/>
       <c r="F485" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B486" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C486" s="7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D486" s="7"/>
       <c r="E486" s="7"/>
       <c r="F486" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B487" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C487" s="7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D487" s="7"/>
       <c r="E487" s="7"/>
       <c r="F487" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B488" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C488" s="7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D488" s="7"/>
       <c r="E488" s="7"/>
       <c r="F488" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B489" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C489" s="7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D489" s="7"/>
       <c r="E489" s="7"/>
       <c r="F489" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B490" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C490" s="7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D490" s="7"/>
       <c r="E490" s="7"/>
       <c r="F490" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B491" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C491" s="7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D491" s="7"/>
       <c r="E491" s="7"/>
       <c r="F491" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B492" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C492" s="7" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D492" s="7"/>
       <c r="E492" s="7"/>
       <c r="F492" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B493" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C493" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D493" s="7"/>
       <c r="E493" s="7"/>
       <c r="F493" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B494" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C494" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D494" s="7"/>
       <c r="E494" s="7"/>
       <c r="F494" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B495" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C495" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D495" s="7"/>
       <c r="E495" s="7"/>
       <c r="F495" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B496" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C496" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D496" s="7"/>
       <c r="E496" s="7"/>
       <c r="F496" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B497" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C497" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D497" s="7"/>
       <c r="E497" s="7"/>
       <c r="F497" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B498" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C498" s="7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D498" s="7"/>
       <c r="E498" s="7"/>
       <c r="F498" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B499" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C499" s="7" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D499" s="7"/>
       <c r="E499" s="7"/>
       <c r="F499" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B500" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C500" s="7" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D500" s="7"/>
       <c r="E500" s="7"/>
       <c r="F500" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B501" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C501" s="7" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D501" s="7"/>
       <c r="E501" s="7"/>
       <c r="F501" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B502" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C502" s="7" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D502" s="7"/>
       <c r="E502" s="7"/>
       <c r="F502" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B503" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C503" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D503" s="7"/>
       <c r="E503" s="7"/>
       <c r="F503" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B504" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C504" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D504" s="7"/>
       <c r="E504" s="7"/>
       <c r="F504" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B505" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C505" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D505" s="7"/>
       <c r="E505" s="7"/>
       <c r="F505" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B506" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C506" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D506" s="7"/>
       <c r="E506" s="7"/>
       <c r="F506" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B507" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C507" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D507" s="7"/>
       <c r="E507" s="7"/>
       <c r="F507" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11538,15 +11630,15 @@
         <v>53</v>
       </c>
       <c r="B508" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C508" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D508" s="7"/>
       <c r="E508" s="7"/>
       <c r="F508" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11554,15 +11646,15 @@
         <v>53</v>
       </c>
       <c r="B509" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C509" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D509" s="7"/>
       <c r="E509" s="7"/>
       <c r="F509" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11570,15 +11662,15 @@
         <v>53</v>
       </c>
       <c r="B510" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C510" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D510" s="7"/>
       <c r="E510" s="7"/>
       <c r="F510" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11586,15 +11678,15 @@
         <v>53</v>
       </c>
       <c r="B511" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C511" s="7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D511" s="7"/>
       <c r="E511" s="7"/>
       <c r="F511" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11602,15 +11694,15 @@
         <v>53</v>
       </c>
       <c r="B512" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C512" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D512" s="7"/>
       <c r="E512" s="7"/>
       <c r="F512" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11618,15 +11710,15 @@
         <v>53</v>
       </c>
       <c r="B513" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C513" s="7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D513" s="7"/>
       <c r="E513" s="7"/>
       <c r="F513" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11634,15 +11726,15 @@
         <v>53</v>
       </c>
       <c r="B514" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C514" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D514" s="7"/>
       <c r="E514" s="7"/>
       <c r="F514" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11650,15 +11742,15 @@
         <v>53</v>
       </c>
       <c r="B515" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C515" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D515" s="7"/>
       <c r="E515" s="7"/>
       <c r="F515" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11666,15 +11758,15 @@
         <v>53</v>
       </c>
       <c r="B516" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C516" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D516" s="7"/>
       <c r="E516" s="7"/>
       <c r="F516" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11682,15 +11774,15 @@
         <v>53</v>
       </c>
       <c r="B517" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C517" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D517" s="7"/>
       <c r="E517" s="7"/>
       <c r="F517" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11698,15 +11790,15 @@
         <v>53</v>
       </c>
       <c r="B518" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C518" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D518" s="7"/>
       <c r="E518" s="7"/>
       <c r="F518" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11714,15 +11806,15 @@
         <v>53</v>
       </c>
       <c r="B519" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C519" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D519" s="7"/>
       <c r="E519" s="7"/>
       <c r="F519" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11730,15 +11822,15 @@
         <v>53</v>
       </c>
       <c r="B520" s="7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C520" s="7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D520" s="7"/>
       <c r="E520" s="7"/>
       <c r="F520" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11746,15 +11838,15 @@
         <v>53</v>
       </c>
       <c r="B521" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C521" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D521" s="7"/>
       <c r="E521" s="7"/>
       <c r="F521" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11762,15 +11854,15 @@
         <v>53</v>
       </c>
       <c r="B522" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C522" s="7" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D522" s="7"/>
       <c r="E522" s="7"/>
       <c r="F522" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11778,15 +11870,15 @@
         <v>53</v>
       </c>
       <c r="B523" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C523" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D523" s="7"/>
       <c r="E523" s="7"/>
       <c r="F523" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11794,15 +11886,15 @@
         <v>53</v>
       </c>
       <c r="B524" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C524" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D524" s="7"/>
       <c r="E524" s="7"/>
       <c r="F524" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11810,15 +11902,15 @@
         <v>53</v>
       </c>
       <c r="B525" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C525" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D525" s="7"/>
       <c r="E525" s="7"/>
       <c r="F525" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11826,15 +11918,15 @@
         <v>53</v>
       </c>
       <c r="B526" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C526" s="7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D526" s="7"/>
       <c r="E526" s="7"/>
       <c r="F526" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11842,15 +11934,15 @@
         <v>53</v>
       </c>
       <c r="B527" s="7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C527" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D527" s="7"/>
       <c r="E527" s="7"/>
       <c r="F527" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11858,14 +11950,398 @@
         <v>53</v>
       </c>
       <c r="B528" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C528" s="7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D528" s="7"/>
       <c r="E528" s="7"/>
       <c r="F528" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A529" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B529" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C529" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D529" s="7"/>
+      <c r="E529" s="7"/>
+      <c r="F529" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A530" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B530" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C530" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D530" s="7"/>
+      <c r="E530" s="7"/>
+      <c r="F530" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A531" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B531" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C531" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D531" s="7"/>
+      <c r="E531" s="7"/>
+      <c r="F531" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A532" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B532" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C532" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D532" s="7"/>
+      <c r="E532" s="7"/>
+      <c r="F532" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A533" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B533" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C533" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D533" s="7"/>
+      <c r="E533" s="7"/>
+      <c r="F533" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A534" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B534" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C534" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D534" s="7"/>
+      <c r="E534" s="7"/>
+      <c r="F534" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A535" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B535" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C535" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D535" s="7"/>
+      <c r="E535" s="7"/>
+      <c r="F535" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A536" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B536" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C536" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D536" s="7"/>
+      <c r="E536" s="7"/>
+      <c r="F536" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A537" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B537" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C537" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D537" s="7"/>
+      <c r="E537" s="7"/>
+      <c r="F537" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A538" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B538" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C538" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D538" s="7"/>
+      <c r="E538" s="7"/>
+      <c r="F538" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A539" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B539" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C539" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D539" s="7"/>
+      <c r="E539" s="7"/>
+      <c r="F539" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A540" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B540" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C540" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D540" s="7"/>
+      <c r="E540" s="7"/>
+      <c r="F540" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A541" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B541" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C541" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D541" s="7"/>
+      <c r="E541" s="7"/>
+      <c r="F541" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A542" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B542" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C542" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D542" s="7"/>
+      <c r="E542" s="7"/>
+      <c r="F542" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A543" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B543" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C543" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D543" s="7"/>
+      <c r="E543" s="7"/>
+      <c r="F543" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A544" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B544" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C544" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D544" s="7"/>
+      <c r="E544" s="7"/>
+      <c r="F544" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A545" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B545" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C545" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D545" s="7"/>
+      <c r="E545" s="7"/>
+      <c r="F545" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A546" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B546" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C546" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D546" s="7"/>
+      <c r="E546" s="7"/>
+      <c r="F546" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A547" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B547" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C547" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D547" s="7"/>
+      <c r="E547" s="7"/>
+      <c r="F547" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A548" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B548" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C548" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D548" s="7"/>
+      <c r="E548" s="7"/>
+      <c r="F548" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A549" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B549" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C549" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D549" s="7"/>
+      <c r="E549" s="7"/>
+      <c r="F549" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A550" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B550" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C550" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D550" s="7"/>
+      <c r="E550" s="7"/>
+      <c r="F550" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A551" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B551" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C551" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D551" s="7"/>
+      <c r="E551" s="7"/>
+      <c r="F551" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A552" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B552" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C552" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D552" s="7"/>
+      <c r="E552" s="7"/>
+      <c r="F552" s="11" t="s">
         <v>61</v>
       </c>
     </row>
@@ -12569,7 +13045,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="13.26"/>
@@ -12578,15 +13054,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="4.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="16" width="10.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="7.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="16" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="15.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="16" width="5.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="8.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="16" width="13.79"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="4.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="7.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="15.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="5.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="8.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="13.8"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="19" style="15" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12643,13 +13119,13 @@
       <c r="M2" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="16" t="n">
+      <c r="N2" s="15" t="n">
         <v>165</v>
       </c>
-      <c r="O2" s="16" t="n">
+      <c r="O2" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="R2" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12671,13 +13147,13 @@
       <c r="M3" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="16" t="n">
+      <c r="N3" s="15" t="n">
         <v>161</v>
       </c>
-      <c r="O3" s="16" t="n">
+      <c r="O3" s="15" t="n">
         <v>170</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12699,13 +13175,13 @@
       <c r="M4" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="16" t="n">
+      <c r="N4" s="15" t="n">
         <v>159</v>
       </c>
-      <c r="O4" s="16" t="n">
+      <c r="O4" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="R4" s="16" t="s">
+      <c r="R4" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12727,13 +13203,13 @@
       <c r="M5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="15" t="n">
         <v>155</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="R5" s="16" t="s">
+      <c r="R5" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12755,13 +13231,13 @@
       <c r="M6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="16" t="n">
+      <c r="N6" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O6" s="16" t="n">
+      <c r="O6" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12783,13 +13259,13 @@
       <c r="M7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="16" t="n">
+      <c r="N7" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R7" s="16" t="s">
+      <c r="R7" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12811,13 +13287,13 @@
       <c r="M8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="N8" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O8" s="16" t="n">
+      <c r="O8" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="R8" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12839,13 +13315,13 @@
       <c r="M9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="16" t="n">
+      <c r="N9" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O9" s="16" t="n">
+      <c r="O9" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12867,13 +13343,13 @@
       <c r="M10" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="N10" s="16" t="n">
+      <c r="N10" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O10" s="16" t="n">
+      <c r="O10" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -12895,13 +13371,13 @@
       <c r="M11" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="N11" s="15" t="n">
         <v>140</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O11" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="R11" s="15" t="s">
         <v>101</v>
       </c>
     </row>
@@ -13183,46 +13659,6 @@
       <c r="C36" s="15"/>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H42" s="0"/>
-      <c r="I42" s="0"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="0"/>
-      <c r="I43" s="0"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H44" s="0"/>
-      <c r="I44" s="0"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H45" s="0"/>
-      <c r="I45" s="0"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="0"/>
-      <c r="I46" s="0"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H47" s="0"/>
-      <c r="I47" s="0"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H48" s="0"/>
-      <c r="I48" s="0"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H49" s="0"/>
-      <c r="I49" s="0"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H50" s="0"/>
-      <c r="I50" s="0"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H51" s="0"/>
-      <c r="I51" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
